--- a/Luban/Config/Datas/Levels/L02/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L02/EnemyData.xlsx
@@ -1391,7 +1391,7 @@
         <v>1.10165</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>5.544</v>
+        <v>8.801983</v>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>1.10165</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>5.544</v>
+        <v>8.801983</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>1.1033</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>5.805122399999999</v>
+        <v>9.216556000000001</v>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>1.1033</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>5.805122399999999</v>
+        <v>9.216556000000001</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>1.10495</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>7.626868080971659</v>
+        <v>12.108868</v>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>1.10495</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>7.626868080971659</v>
+        <v>12.108868</v>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>1.054725</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>4.957464252631579</v>
+        <v>7.870764</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>1.1066</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>8.845863157894737</v>
+        <v>14.044216</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>1.1066</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>8.845863157894737</v>
+        <v>14.044216</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>1.0563</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>5.749811052631579</v>
+        <v>9.128741</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>1.10825</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>13.5862358016</v>
+        <v>21.570313</v>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>1.10825</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>13.5862358016</v>
+        <v>21.570313</v>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>1.057875</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>8.83105327104</v>
+        <v>14.020703</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>1.0075</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>21.2488727937024</v>
+        <v>33.735969</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>1.009</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>5.600000000000001</v>
+        <v>11.854522</v>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>1.1099</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>12.44444444444444</v>
+        <v>19.757537</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>1.1099</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>12.44444444444444</v>
+        <v>19.757537</v>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         <v>1.009</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>19.46311111111111</v>
+        <v>30.900788</v>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         <v>1.05945</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>8.088888888888889</v>
+        <v>12.842399</v>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>1.009</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>19.46311111111111</v>
+        <v>30.900788</v>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>1.0105</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>5.957122061610633</v>
+        <v>12.610506</v>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>1.11155</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>13.23804902580141</v>
+        <v>21.017511</v>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>1.11155</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>13.23804902580141</v>
+        <v>21.017511</v>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>1.0105</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>20.7043086763534</v>
+        <v>32.871387</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>1.061025</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>8.604731866770916</v>
+        <v>13.661382</v>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>1.0105</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>20.7043086763534</v>
+        <v>32.871387</v>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>1.012</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>7.087900273548388</v>
+        <v>15.004227</v>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>1.1132</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>15.7508894967742</v>
+        <v>25.007045</v>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>1.1132</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>15.7508894967742</v>
+        <v>25.007045</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>1.012</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>24.63439117295484</v>
+        <v>39.111019</v>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>1.0626</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>10.23807817290323</v>
+        <v>16.254579</v>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>1.012</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>24.63439117295484</v>
+        <v>39.111019</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>1.0135</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>8.424992680851064</v>
+        <v>17.83469</v>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>1.11485</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>18.72220595744681</v>
+        <v>29.724483</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>1.11485</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>18.72220595744681</v>
+        <v>29.724483</v>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>1.0135</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>29.2815301174468</v>
+        <v>46.489092</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>1.064175</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>12.16943387234042</v>
+        <v>19.320914</v>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>1.0135</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>29.2815301174468</v>
+        <v>46.489092</v>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>1.015</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>14.53975155279503</v>
+        <v>30.778894</v>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>1.1165</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>32.31055900621118</v>
+        <v>51.298157</v>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>1.1165</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>32.31055900621118</v>
+        <v>51.298157</v>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>1.015</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>50.53371428571429</v>
+        <v>80.230318</v>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>1.06575</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>21.00186335403727</v>
+        <v>33.343802</v>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>1.015</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>50.53371428571429</v>
+        <v>80.230318</v>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>1.11815</v>
       </c>
       <c r="D48" s="0" t="n">
-        <v>27.80513357778942</v>
+        <v>44.145077</v>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>1.11815</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>27.80513357778942</v>
+        <v>44.145077</v>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>1.6264</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>23.634363541121</v>
+        <v>37.523316</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>1.0165</v>
       </c>
       <c r="D51" s="0" t="n">
-        <v>43.48722891566265</v>
+        <v>69.042901</v>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>1.067325</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>18.07333682556312</v>
+        <v>28.6943</v>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>0.8132</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>51.99559979046621</v>
+        <v>82.551294</v>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>1.0165</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>43.48722891566265</v>
+        <v>69.042901</v>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>1.018</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>12.25569871159564</v>
+        <v>25.943831</v>
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>1.018</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>12.25569871159564</v>
+        <v>25.943831</v>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>1.1198</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>27.23488602576808</v>
+        <v>43.239718</v>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>1.1198</v>
       </c>
       <c r="D58" s="0" t="n">
-        <v>27.23488602576808</v>
+        <v>43.239718</v>
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
         <v>1.6288</v>
       </c>
       <c r="D59" s="0" t="n">
-        <v>23.14965312190287</v>
+        <v>36.753761</v>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>1.018</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>42.59536174430128</v>
+        <v>67.626919</v>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>1.0689</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>17.70267591674926</v>
+        <v>28.105817</v>
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>0.8144</v>
       </c>
       <c r="D62" s="0" t="n">
-        <v>50.92923686818632</v>
+        <v>80.858273</v>
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>1.018</v>
       </c>
       <c r="D63" s="0" t="n">
-        <v>42.59536174430128</v>
+        <v>67.626919</v>
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>1.0195</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>13.97730430754979</v>
+        <v>29.588262</v>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
         <v>1.0195</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>13.97730430754979</v>
+        <v>29.588262</v>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>1.12145</v>
       </c>
       <c r="D66" s="0" t="n">
-        <v>31.06067623899954</v>
+        <v>49.313769</v>
       </c>
       <c r="E66" s="0" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>1.12145</v>
       </c>
       <c r="D67" s="0" t="n">
-        <v>31.06067623899954</v>
+        <v>49.313769</v>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>1.6312</v>
       </c>
       <c r="D68" s="0" t="n">
-        <v>26.4015748031496</v>
+        <v>41.916704</v>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>1.0195</v>
       </c>
       <c r="D69" s="0" t="n">
-        <v>48.57889763779527</v>
+        <v>77.126735</v>
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>1.070475</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>20.1894395553497</v>
+        <v>32.05395</v>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>0.8156000000000001</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>58.08346456692914</v>
+        <v>92.21674899999999</v>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>1.0195</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>48.57889763779527</v>
+        <v>77.126735</v>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>1.021</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>15.87151567944251</v>
+        <v>33.598078</v>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>1.021</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>15.87151567944251</v>
+        <v>33.598078</v>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>1.1231</v>
       </c>
       <c r="D75" s="0" t="n">
-        <v>35.27003484320558</v>
+        <v>55.996797</v>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>1.1231</v>
       </c>
       <c r="D76" s="0" t="n">
-        <v>35.27003484320558</v>
+        <v>55.996797</v>
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>1.6336</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>29.97952961672474</v>
+        <v>47.597277</v>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>1.021</v>
       </c>
       <c r="D78" s="0" t="n">
-        <v>55.16233449477352</v>
+        <v>87.57899</v>
       </c>
       <c r="E78" s="0" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>1.07205</v>
       </c>
       <c r="D79" s="0" t="n">
-        <v>22.92552264808362</v>
+        <v>36.397918</v>
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>0.8168000000000002</v>
       </c>
       <c r="D80" s="0" t="n">
-        <v>65.95496515679443</v>
+        <v>104.714009</v>
       </c>
       <c r="E80" s="0" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>1.021</v>
       </c>
       <c r="D81" s="0" t="n">
-        <v>55.16233449477352</v>
+        <v>87.57899</v>
       </c>
       <c r="E81" s="0" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>1.0225</v>
       </c>
       <c r="D82" s="0" t="n">
-        <v>26.44241164241165</v>
+        <v>55.975385</v>
       </c>
       <c r="E82" s="0" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         <v>1.0225</v>
       </c>
       <c r="D83" s="0" t="n">
-        <v>26.44241164241165</v>
+        <v>55.975385</v>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         <v>1.12475</v>
       </c>
       <c r="D84" s="0" t="n">
-        <v>58.76091476091476</v>
+        <v>93.292309</v>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>1.12475</v>
       </c>
       <c r="D85" s="0" t="n">
-        <v>58.76091476091476</v>
+        <v>93.292309</v>
       </c>
       <c r="E85" s="0" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>1.636</v>
       </c>
       <c r="D86" s="0" t="n">
-        <v>49.94677754677754</v>
+        <v>79.298463</v>
       </c>
       <c r="E86" s="0" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>1.0225</v>
       </c>
       <c r="D87" s="0" t="n">
-        <v>91.90207068607067</v>
+        <v>145.909171</v>
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>1.073625</v>
       </c>
       <c r="D88" s="0" t="n">
-        <v>38.1945945945946</v>
+        <v>60.640001</v>
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>0.8180000000000001</v>
       </c>
       <c r="D89" s="0" t="n">
-        <v>109.8829106029106</v>
+        <v>174.456618</v>
       </c>
       <c r="E89" s="0" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>1.0225</v>
       </c>
       <c r="D90" s="0" t="n">
-        <v>91.90207068607067</v>
+        <v>145.909171</v>
       </c>
       <c r="E90" s="0" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>1.0225</v>
       </c>
       <c r="D91" s="0" t="n">
-        <v>91.90207068607067</v>
+        <v>145.909171</v>
       </c>
       <c r="E91" s="0" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>1.1264</v>
       </c>
       <c r="D92" s="0" t="n">
-        <v>56.86785009861933</v>
+        <v>90.286767</v>
       </c>
       <c r="E92" s="0" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>1.1264</v>
       </c>
       <c r="D93" s="0" t="n">
-        <v>56.86785009861933</v>
+        <v>90.286767</v>
       </c>
       <c r="E93" s="0" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>1.6384</v>
       </c>
       <c r="D94" s="0" t="n">
-        <v>48.33767258382643</v>
+        <v>76.743752</v>
       </c>
       <c r="E94" s="0" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>1.024</v>
       </c>
       <c r="D95" s="0" t="n">
-        <v>88.94131755424064</v>
+        <v>141.208504</v>
       </c>
       <c r="E95" s="0" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>1.0752</v>
       </c>
       <c r="D96" s="0" t="n">
-        <v>36.96410256410256</v>
+        <v>58.686399</v>
       </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>0.8192</v>
       </c>
       <c r="D97" s="0" t="n">
-        <v>106.3428796844182</v>
+        <v>168.836255</v>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>1.024</v>
       </c>
       <c r="D98" s="0" t="n">
-        <v>88.94131755424064</v>
+        <v>141.208504</v>
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>1.024</v>
       </c>
       <c r="D99" s="0" t="n">
-        <v>88.94131755424064</v>
+        <v>141.208504</v>
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>1.0255</v>
       </c>
       <c r="D100" s="0" t="n">
-        <v>24.88792779240316</v>
+        <v>52.684731</v>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>1.0255</v>
       </c>
       <c r="D101" s="0" t="n">
-        <v>24.88792779240316</v>
+        <v>52.684731</v>
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>1.0255</v>
       </c>
       <c r="D102" s="0" t="n">
-        <v>24.88792779240316</v>
+        <v>52.684731</v>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>1.12805</v>
       </c>
       <c r="D103" s="0" t="n">
-        <v>55.30650620534036</v>
+        <v>87.807885</v>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>1.12805</v>
       </c>
       <c r="D104" s="0" t="n">
-        <v>55.30650620534036</v>
+        <v>87.807885</v>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         <v>1.6408</v>
       </c>
       <c r="D105" s="0" t="n">
-        <v>47.01053027453931</v>
+        <v>74.636703</v>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>1.0255</v>
       </c>
       <c r="D106" s="0" t="n">
-        <v>86.49937570515233</v>
+        <v>137.331533</v>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>1.076775</v>
       </c>
       <c r="D107" s="0" t="n">
-        <v>35.94922903347123</v>
+        <v>57.075125</v>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>0.8204000000000001</v>
       </c>
       <c r="D108" s="0" t="n">
-        <v>103.4231666039865</v>
+        <v>164.200746</v>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>1.0255</v>
       </c>
       <c r="D109" s="0" t="n">
-        <v>86.49937570515233</v>
+        <v>137.331533</v>
       </c>
       <c r="E109" s="0" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>1.0255</v>
       </c>
       <c r="D110" s="0" t="n">
-        <v>86.49937570515233</v>
+        <v>137.331533</v>
       </c>
       <c r="E110" s="0" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>1.027</v>
       </c>
       <c r="D111" s="0" t="n">
-        <v>25.36070276084618</v>
+        <v>53.685539</v>
       </c>
       <c r="E111" s="0" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>1.027</v>
       </c>
       <c r="D112" s="0" t="n">
-        <v>25.36070276084618</v>
+        <v>53.685539</v>
       </c>
       <c r="E112" s="0" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         <v>1.027</v>
       </c>
       <c r="D113" s="0" t="n">
-        <v>25.36070276084618</v>
+        <v>53.685539</v>
       </c>
       <c r="E113" s="0" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>1.1297</v>
       </c>
       <c r="D114" s="0" t="n">
-        <v>56.35711724632485</v>
+        <v>89.475898</v>
       </c>
       <c r="E114" s="0" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>1.1297</v>
       </c>
       <c r="D115" s="0" t="n">
-        <v>56.35711724632485</v>
+        <v>89.475898</v>
       </c>
       <c r="E115" s="0" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>1.6432</v>
       </c>
       <c r="D116" s="0" t="n">
-        <v>47.90354965937613</v>
+        <v>76.054513</v>
       </c>
       <c r="E116" s="0" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>1.027</v>
       </c>
       <c r="D117" s="0" t="n">
-        <v>88.14253137325207</v>
+        <v>139.940304</v>
       </c>
       <c r="E117" s="0" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>1.07835</v>
       </c>
       <c r="D118" s="0" t="n">
-        <v>36.63212621011116</v>
+        <v>58.159333</v>
       </c>
       <c r="E118" s="0" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>0.8216000000000001</v>
       </c>
       <c r="D119" s="0" t="n">
-        <v>105.3878092506275</v>
+        <v>167.319929</v>
       </c>
       <c r="E119" s="0" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>1.027</v>
       </c>
       <c r="D120" s="0" t="n">
-        <v>88.14253137325207</v>
+        <v>139.940304</v>
       </c>
       <c r="E120" s="0" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>1.027</v>
       </c>
       <c r="D121" s="0" t="n">
-        <v>88.14253137325207</v>
+        <v>139.940304</v>
       </c>
       <c r="E121" s="0" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>1.0285</v>
       </c>
       <c r="D122" s="0" t="n">
-        <v>28.03182751540041</v>
+        <v>59.339986</v>
       </c>
       <c r="E122" s="0" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>1.0285</v>
       </c>
       <c r="D123" s="0" t="n">
-        <v>28.03182751540041</v>
+        <v>59.339986</v>
       </c>
       <c r="E123" s="0" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         <v>1.0285</v>
       </c>
       <c r="D124" s="0" t="n">
-        <v>28.03182751540041</v>
+        <v>59.339986</v>
       </c>
       <c r="E124" s="0" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>1.13135</v>
       </c>
       <c r="D125" s="0" t="n">
-        <v>62.29295003422314</v>
+        <v>98.89997700000001</v>
       </c>
       <c r="E125" s="0" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>1.13135</v>
       </c>
       <c r="D126" s="0" t="n">
-        <v>62.29295003422314</v>
+        <v>98.89997700000001</v>
       </c>
       <c r="E126" s="0" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>1.6456</v>
       </c>
       <c r="D127" s="0" t="n">
-        <v>52.94900752908966</v>
+        <v>84.064981</v>
       </c>
       <c r="E127" s="0" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>1.0285</v>
       </c>
       <c r="D128" s="0" t="n">
-        <v>97.42617385352499</v>
+        <v>154.679565</v>
       </c>
       <c r="E128" s="0" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>1.079925</v>
       </c>
       <c r="D129" s="0" t="n">
-        <v>40.49041752224505</v>
+        <v>64.28498500000001</v>
       </c>
       <c r="E129" s="0" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>0.8228</v>
       </c>
       <c r="D130" s="0" t="n">
-        <v>116.4878165639973</v>
+        <v>184.942958</v>
       </c>
       <c r="E130" s="0" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>1.0285</v>
       </c>
       <c r="D131" s="0" t="n">
-        <v>97.42617385352499</v>
+        <v>154.679565</v>
       </c>
       <c r="E131" s="0" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>1.0285</v>
       </c>
       <c r="D132" s="0" t="n">
-        <v>97.42617385352499</v>
+        <v>154.679565</v>
       </c>
       <c r="E132" s="0" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>1.03</v>
       </c>
       <c r="D133" s="0" t="n">
-        <v>45.54816285998014</v>
+        <v>96.419949</v>
       </c>
       <c r="E133" s="0" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>1.03</v>
       </c>
       <c r="D134" s="0" t="n">
-        <v>45.54816285998014</v>
+        <v>96.419949</v>
       </c>
       <c r="E134" s="0" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>1.03</v>
       </c>
       <c r="D135" s="0" t="n">
-        <v>45.54816285998014</v>
+        <v>96.419949</v>
       </c>
       <c r="E135" s="0" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>1.133</v>
       </c>
       <c r="D136" s="0" t="n">
-        <v>101.2181396888447</v>
+        <v>160.699914</v>
       </c>
       <c r="E136" s="0" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>1.133</v>
       </c>
       <c r="D137" s="0" t="n">
-        <v>101.2181396888447</v>
+        <v>160.699914</v>
       </c>
       <c r="E137" s="0" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>1.648</v>
       </c>
       <c r="D138" s="0" t="n">
-        <v>86.03541873551804</v>
+        <v>136.594927</v>
       </c>
       <c r="E138" s="0" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>1.03</v>
       </c>
       <c r="D139" s="0" t="n">
-        <v>158.3051704733532</v>
+        <v>251.334666</v>
       </c>
       <c r="E139" s="0" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>1.0815</v>
       </c>
       <c r="D140" s="0" t="n">
-        <v>65.79179079774909</v>
+        <v>104.454944</v>
       </c>
       <c r="E140" s="0" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>0.8240000000000001</v>
       </c>
       <c r="D141" s="0" t="n">
-        <v>189.2779212181397</v>
+        <v>300.50884</v>
       </c>
       <c r="E141" s="0" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>1.03</v>
       </c>
       <c r="D142" s="0" t="n">
-        <v>158.3051704733532</v>
+        <v>251.334666</v>
       </c>
       <c r="E142" s="0" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>1.03</v>
       </c>
       <c r="D143" s="0" t="n">
-        <v>158.3051704733532</v>
+        <v>251.334666</v>
       </c>
       <c r="E143" s="0" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>1.0075</v>
       </c>
       <c r="D144" s="0" t="n">
-        <v>21.2488727937024</v>
+        <v>33.735969</v>
       </c>
       <c r="E144" s="0" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>1.009</v>
       </c>
       <c r="D145" s="0" t="n">
-        <v>5.600000000000001</v>
+        <v>11.854522</v>
       </c>
       <c r="E145" s="0" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>1.0105</v>
       </c>
       <c r="D146" s="0" t="n">
-        <v>5.957122061610633</v>
+        <v>12.610506</v>
       </c>
       <c r="E146" s="0" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>1.012</v>
       </c>
       <c r="D147" s="0" t="n">
-        <v>7.087900273548388</v>
+        <v>15.004227</v>
       </c>
       <c r="E147" s="0" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>1.0135</v>
       </c>
       <c r="D148" s="0" t="n">
-        <v>8.424992680851064</v>
+        <v>17.83469</v>
       </c>
       <c r="E148" s="0" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>1.015</v>
       </c>
       <c r="D149" s="0" t="n">
-        <v>14.53975155279503</v>
+        <v>30.778894</v>
       </c>
       <c r="E149" s="0" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>1.018</v>
       </c>
       <c r="D150" s="0" t="n">
-        <v>12.25569871159564</v>
+        <v>25.943831</v>
       </c>
       <c r="E150" s="0" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>1.0195</v>
       </c>
       <c r="D151" s="0" t="n">
-        <v>13.97730430754979</v>
+        <v>29.588262</v>
       </c>
       <c r="E151" s="0" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>1.021</v>
       </c>
       <c r="D152" s="0" t="n">
-        <v>15.87151567944251</v>
+        <v>33.598078</v>
       </c>
       <c r="E152" s="0" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>1.0225</v>
       </c>
       <c r="D153" s="0" t="n">
-        <v>26.44241164241165</v>
+        <v>55.975385</v>
       </c>
       <c r="E153" s="0" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>1.0315</v>
       </c>
       <c r="D154" s="0" t="n">
-        <v>44.38804554079697</v>
+        <v>93.96412100000001</v>
       </c>
       <c r="E154" s="0" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>1.0315</v>
       </c>
       <c r="D155" s="0" t="n">
-        <v>44.38804554079697</v>
+        <v>93.96412100000001</v>
       </c>
       <c r="E155" s="0" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>1.0315</v>
       </c>
       <c r="D156" s="0" t="n">
-        <v>44.38804554079697</v>
+        <v>93.96412100000001</v>
       </c>
       <c r="E156" s="0" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>1.13465</v>
       </c>
       <c r="D157" s="0" t="n">
-        <v>98.64010120177103</v>
+        <v>156.606868</v>
       </c>
       <c r="E157" s="0" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>1.13465</v>
       </c>
       <c r="D158" s="0" t="n">
-        <v>98.64010120177103</v>
+        <v>156.606868</v>
       </c>
       <c r="E158" s="0" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>1.6504</v>
       </c>
       <c r="D159" s="0" t="n">
-        <v>83.84408602150538</v>
+        <v>133.115837</v>
       </c>
       <c r="E159" s="0" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.0315</v>
       </c>
       <c r="D160" s="0" t="n">
-        <v>154.2731182795699</v>
+        <v>244.933141</v>
       </c>
       <c r="E160" s="0" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>1.083075</v>
       </c>
       <c r="D161" s="0" t="n">
-        <v>64.11606578115118</v>
+        <v>101.794464</v>
       </c>
       <c r="E161" s="0" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>0.8252000000000002</v>
       </c>
       <c r="D162" s="0" t="n">
-        <v>184.4569892473118</v>
+        <v>292.854842</v>
       </c>
       <c r="E162" s="0" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>1.0315</v>
       </c>
       <c r="D163" s="0" t="n">
-        <v>154.2731182795699</v>
+        <v>244.933141</v>
       </c>
       <c r="E163" s="0" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>1.0315</v>
       </c>
       <c r="D164" s="0" t="n">
-        <v>154.2731182795699</v>
+        <v>244.933141</v>
       </c>
       <c r="E164" s="0" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>1.033</v>
       </c>
       <c r="D165" s="0" t="n">
-        <v>43.76734943442372</v>
+        <v>92.650182</v>
       </c>
       <c r="E165" s="0" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>1.033</v>
       </c>
       <c r="D166" s="0" t="n">
-        <v>43.76734943442372</v>
+        <v>92.650182</v>
       </c>
       <c r="E166" s="0" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>1.033</v>
       </c>
       <c r="D167" s="0" t="n">
-        <v>43.76734943442372</v>
+        <v>92.650182</v>
       </c>
       <c r="E167" s="0" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>1.1363</v>
       </c>
       <c r="D168" s="0" t="n">
-        <v>97.2607765209416</v>
+        <v>154.41697</v>
       </c>
       <c r="E168" s="0" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>1.1363</v>
       </c>
       <c r="D169" s="0" t="n">
-        <v>97.2607765209416</v>
+        <v>154.41697</v>
       </c>
       <c r="E169" s="0" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>1.6528</v>
       </c>
       <c r="D170" s="0" t="n">
-        <v>82.67166004280035</v>
+        <v>131.254424</v>
       </c>
       <c r="E170" s="0" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>1.033</v>
       </c>
       <c r="D171" s="0" t="n">
-        <v>152.1158544787527</v>
+        <v>241.508141</v>
       </c>
       <c r="E171" s="0" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>1.08465</v>
       </c>
       <c r="D172" s="0" t="n">
-        <v>63.21950473861205</v>
+        <v>100.37103</v>
       </c>
       <c r="E172" s="0" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>0.8264000000000001</v>
       </c>
       <c r="D173" s="0" t="n">
-        <v>181.8776520941608</v>
+        <v>288.759734</v>
       </c>
       <c r="E173" s="0" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>1.033</v>
       </c>
       <c r="D174" s="0" t="n">
-        <v>152.1158544787527</v>
+        <v>241.508141</v>
       </c>
       <c r="E174" s="0" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>1.033</v>
       </c>
       <c r="D175" s="0" t="n">
-        <v>152.1158544787527</v>
+        <v>241.508141</v>
       </c>
       <c r="E175" s="0" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>1.0345</v>
       </c>
       <c r="D176" s="0" t="n">
-        <v>42.85035211267606</v>
+        <v>90.70901000000001</v>
       </c>
       <c r="E176" s="0" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>1.0345</v>
       </c>
       <c r="D177" s="0" t="n">
-        <v>42.85035211267606</v>
+        <v>90.70901000000001</v>
       </c>
       <c r="E177" s="0" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>1.0345</v>
       </c>
       <c r="D178" s="0" t="n">
-        <v>42.85035211267606</v>
+        <v>90.70901000000001</v>
       </c>
       <c r="E178" s="0" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>1.13795</v>
       </c>
       <c r="D179" s="0" t="n">
-        <v>95.22300469483568</v>
+        <v>151.181683</v>
       </c>
       <c r="E179" s="0" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>1.13795</v>
       </c>
       <c r="D180" s="0" t="n">
-        <v>95.22300469483568</v>
+        <v>151.181683</v>
       </c>
       <c r="E180" s="0" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>1.6552</v>
       </c>
       <c r="D181" s="0" t="n">
-        <v>80.93955399061034</v>
+        <v>128.50443</v>
       </c>
       <c r="E181" s="0" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>1.0345</v>
       </c>
       <c r="D182" s="0" t="n">
-        <v>148.928779342723</v>
+        <v>236.448152</v>
       </c>
       <c r="E182" s="0" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>1.086225</v>
       </c>
       <c r="D183" s="0" t="n">
-        <v>61.89495305164318</v>
+        <v>98.268094</v>
       </c>
       <c r="E183" s="0" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>0.8276</v>
       </c>
       <c r="D184" s="0" t="n">
-        <v>178.0670187793427</v>
+        <v>282.709747</v>
       </c>
       <c r="E184" s="0" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>1.0345</v>
       </c>
       <c r="D185" s="0" t="n">
-        <v>148.928779342723</v>
+        <v>236.448152</v>
       </c>
       <c r="E185" s="0" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>1.0345</v>
       </c>
       <c r="D186" s="0" t="n">
-        <v>148.928779342723</v>
+        <v>236.448152</v>
       </c>
       <c r="E186" s="0" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>1.036</v>
       </c>
       <c r="D187" s="0" t="n">
-        <v>44.06170752324599</v>
+        <v>93.273302</v>
       </c>
       <c r="E187" s="0" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>1.036</v>
       </c>
       <c r="D188" s="0" t="n">
-        <v>44.06170752324599</v>
+        <v>93.273302</v>
       </c>
       <c r="E188" s="0" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>1.036</v>
       </c>
       <c r="D189" s="0" t="n">
-        <v>44.06170752324599</v>
+        <v>93.273302</v>
       </c>
       <c r="E189" s="0" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>1.1396</v>
       </c>
       <c r="D190" s="0" t="n">
-        <v>97.9149056072133</v>
+        <v>155.455504</v>
       </c>
       <c r="E190" s="0" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>1.1396</v>
       </c>
       <c r="D191" s="0" t="n">
-        <v>97.9149056072133</v>
+        <v>155.455504</v>
       </c>
       <c r="E191" s="0" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>1.6576</v>
       </c>
       <c r="D192" s="0" t="n">
-        <v>83.22766976613131</v>
+        <v>132.137178</v>
       </c>
       <c r="E192" s="0" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>1.036</v>
       </c>
       <c r="D193" s="0" t="n">
-        <v>153.1389123696816</v>
+        <v>243.132408</v>
       </c>
       <c r="E193" s="0" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>1.0878</v>
       </c>
       <c r="D194" s="0" t="n">
-        <v>63.64468864468865</v>
+        <v>101.046078</v>
       </c>
       <c r="E194" s="0" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D195" s="0" t="n">
-        <v>183.1008734854889</v>
+        <v>290.701793</v>
       </c>
       <c r="E195" s="0" t="inlineStr">
         <is>
@@ -11183,7 +11183,7 @@
         <v>1.036</v>
       </c>
       <c r="D196" s="0" t="n">
-        <v>153.1389123696816</v>
+        <v>243.132408</v>
       </c>
       <c r="E196" s="0" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>1.036</v>
       </c>
       <c r="D197" s="0" t="n">
-        <v>153.1389123696816</v>
+        <v>243.132408</v>
       </c>
       <c r="E197" s="0" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>1.0375</v>
       </c>
       <c r="D198" s="0" t="n">
-        <v>83.6751541141785</v>
+        <v>177.130175</v>
       </c>
       <c r="E198" s="0" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>1.0375</v>
       </c>
       <c r="D199" s="0" t="n">
-        <v>83.6751541141785</v>
+        <v>177.130175</v>
       </c>
       <c r="E199" s="0" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>1.0375</v>
       </c>
       <c r="D200" s="0" t="n">
-        <v>83.6751541141785</v>
+        <v>177.130175</v>
       </c>
       <c r="E200" s="0" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>1.14125</v>
       </c>
       <c r="D201" s="0" t="n">
-        <v>185.9447869203967</v>
+        <v>295.216958</v>
       </c>
       <c r="E201" s="0" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>1.14125</v>
       </c>
       <c r="D202" s="0" t="n">
-        <v>185.9447869203967</v>
+        <v>295.216958</v>
       </c>
       <c r="E202" s="0" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>1.66</v>
       </c>
       <c r="D203" s="0" t="n">
-        <v>158.0530688823372</v>
+        <v>250.934414</v>
       </c>
       <c r="E203" s="0" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>1.0375</v>
       </c>
       <c r="D204" s="0" t="n">
-        <v>290.8176467435004</v>
+        <v>461.719322</v>
       </c>
       <c r="E204" s="0" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>1.089375</v>
       </c>
       <c r="D205" s="0" t="n">
-        <v>120.8641114982578</v>
+        <v>191.891023</v>
       </c>
       <c r="E205" s="0" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D206" s="0" t="n">
-        <v>347.7167515411418</v>
+        <v>552.055712</v>
       </c>
       <c r="E206" s="0" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>1.0375</v>
       </c>
       <c r="D207" s="0" t="n">
-        <v>290.8176467435004</v>
+        <v>461.719322</v>
       </c>
       <c r="E207" s="0" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>0.7781250000000001</v>
       </c>
       <c r="D208" s="0" t="n">
-        <v>696.177282229965</v>
+        <v>1105.292291</v>
       </c>
       <c r="E208" s="0" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>0.22</v>
       </c>
       <c r="J208" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K208" s="0" t="n">
         <v>2</v>
@@ -11846,7 +11846,7 @@
         <v>1.0375</v>
       </c>
       <c r="D209" s="0" t="n">
-        <v>290.8176467435004</v>
+        <v>461.719322</v>
       </c>
       <c r="E209" s="0" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>1.015</v>
       </c>
       <c r="D210" s="0" t="n">
-        <v>14.53975155279503</v>
+        <v>30.778894</v>
       </c>
       <c r="E210" s="0" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>1.009</v>
       </c>
       <c r="D211" s="0" t="n">
-        <v>5.600000000000001</v>
+        <v>11.854522</v>
       </c>
       <c r="E211" s="0" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>1.0105</v>
       </c>
       <c r="D212" s="0" t="n">
-        <v>5.957122061610633</v>
+        <v>12.610506</v>
       </c>
       <c r="E212" s="0" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>1.012</v>
       </c>
       <c r="D213" s="0" t="n">
-        <v>7.087900273548388</v>
+        <v>15.004227</v>
       </c>
       <c r="E213" s="0" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>1.0135</v>
       </c>
       <c r="D214" s="0" t="n">
-        <v>8.424992680851064</v>
+        <v>17.83469</v>
       </c>
       <c r="E214" s="0" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>1.0045</v>
       </c>
       <c r="D215" s="0" t="n">
-        <v>3.432090636437247</v>
+        <v>7.265321</v>
       </c>
       <c r="E215" s="0" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>1.0045</v>
       </c>
       <c r="D216" s="0" t="n">
-        <v>3.432090636437247</v>
+        <v>7.265321</v>
       </c>
       <c r="E216" s="0" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>1.0045</v>
       </c>
       <c r="D217" s="0" t="n">
-        <v>3.432090636437247</v>
+        <v>7.265321</v>
       </c>
       <c r="E217" s="0" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>1.0045</v>
       </c>
       <c r="D218" s="0" t="n">
-        <v>3.432090636437247</v>
+        <v>7.265321</v>
       </c>
       <c r="E218" s="0" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>1.0045</v>
       </c>
       <c r="D219" s="0" t="n">
-        <v>3.432090636437247</v>
+        <v>7.265321</v>
       </c>
       <c r="E219" s="0" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>1.006</v>
       </c>
       <c r="D220" s="0" t="n">
-        <v>3.980638421052632</v>
+        <v>8.42653</v>
       </c>
       <c r="E220" s="0" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>1.006</v>
       </c>
       <c r="D221" s="0" t="n">
-        <v>3.980638421052632</v>
+        <v>8.42653</v>
       </c>
       <c r="E221" s="0" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>1.006</v>
       </c>
       <c r="D222" s="0" t="n">
-        <v>3.980638421052632</v>
+        <v>8.42653</v>
       </c>
       <c r="E222" s="0" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>1.006</v>
       </c>
       <c r="D223" s="0" t="n">
-        <v>3.980638421052632</v>
+        <v>8.42653</v>
       </c>
       <c r="E223" s="0" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>1.006</v>
       </c>
       <c r="D224" s="0" t="n">
-        <v>3.980638421052632</v>
+        <v>8.42653</v>
       </c>
       <c r="E224" s="0" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>1.0075</v>
       </c>
       <c r="D225" s="0" t="n">
-        <v>6.11380611072</v>
+        <v>12.942188</v>
       </c>
       <c r="E225" s="0" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>1.0075</v>
       </c>
       <c r="D226" s="0" t="n">
-        <v>6.11380611072</v>
+        <v>12.942188</v>
       </c>
       <c r="E226" s="0" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         <v>1.0075</v>
       </c>
       <c r="D227" s="0" t="n">
-        <v>6.11380611072</v>
+        <v>12.942188</v>
       </c>
       <c r="E227" s="0" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>1.0075</v>
       </c>
       <c r="D228" s="0" t="n">
-        <v>6.11380611072</v>
+        <v>12.942188</v>
       </c>
       <c r="E228" s="0" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>1.0075</v>
       </c>
       <c r="D229" s="0" t="n">
-        <v>6.11380611072</v>
+        <v>12.942188</v>
       </c>
       <c r="E229" s="0" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>1.009</v>
       </c>
       <c r="D230" s="0" t="n">
-        <v>5.600000000000001</v>
+        <v>11.854522</v>
       </c>
       <c r="E230" s="0" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>1.009</v>
       </c>
       <c r="D231" s="0" t="n">
-        <v>5.600000000000001</v>
+        <v>11.854522</v>
       </c>
       <c r="E231" s="0" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>1.0105</v>
       </c>
       <c r="D232" s="0" t="n">
-        <v>5.957122061610633</v>
+        <v>12.610506</v>
       </c>
       <c r="E232" s="0" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>1.0105</v>
       </c>
       <c r="D233" s="0" t="n">
-        <v>5.957122061610633</v>
+        <v>12.610506</v>
       </c>
       <c r="E233" s="0" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>1.012</v>
       </c>
       <c r="D234" s="0" t="n">
-        <v>7.087900273548388</v>
+        <v>15.004227</v>
       </c>
       <c r="E234" s="0" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>1.012</v>
       </c>
       <c r="D235" s="0" t="n">
-        <v>7.087900273548388</v>
+        <v>15.004227</v>
       </c>
       <c r="E235" s="0" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>1.0135</v>
       </c>
       <c r="D236" s="0" t="n">
-        <v>8.424992680851064</v>
+        <v>17.83469</v>
       </c>
       <c r="E236" s="0" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>1.0135</v>
       </c>
       <c r="D237" s="0" t="n">
-        <v>8.424992680851064</v>
+        <v>17.83469</v>
       </c>
       <c r="E237" s="0" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>1.015</v>
       </c>
       <c r="D238" s="0" t="n">
-        <v>14.53975155279503</v>
+        <v>30.778894</v>
       </c>
       <c r="E238" s="0" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>1.015</v>
       </c>
       <c r="D239" s="0" t="n">
-        <v>14.53975155279503</v>
+        <v>30.778894</v>
       </c>
       <c r="E239" s="0" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>1.0165</v>
       </c>
       <c r="D240" s="0" t="n">
-        <v>12.51231011000524</v>
+        <v>26.487046</v>
       </c>
       <c r="E240" s="0" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>1.0165</v>
       </c>
       <c r="D241" s="0" t="n">
-        <v>12.51231011000524</v>
+        <v>26.487046</v>
       </c>
       <c r="E241" s="0" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>1.0165</v>
       </c>
       <c r="D242" s="0" t="n">
-        <v>12.51231011000524</v>
+        <v>26.487046</v>
       </c>
       <c r="E242" s="0" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>1.0165</v>
       </c>
       <c r="D243" s="0" t="n">
-        <v>12.51231011000524</v>
+        <v>26.487046</v>
       </c>
       <c r="E243" s="0" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>1.0165</v>
       </c>
       <c r="D244" s="0" t="n">
-        <v>12.51231011000524</v>
+        <v>26.487046</v>
       </c>
       <c r="E244" s="0" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>1.018</v>
       </c>
       <c r="D245" s="0" t="n">
-        <v>12.25569871159564</v>
+        <v>25.943831</v>
       </c>
       <c r="E245" s="0" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>1.018</v>
       </c>
       <c r="D246" s="0" t="n">
-        <v>12.25569871159564</v>
+        <v>25.943831</v>
       </c>
       <c r="E246" s="0" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>1.0195</v>
       </c>
       <c r="D247" s="0" t="n">
-        <v>13.97730430754979</v>
+        <v>29.588262</v>
       </c>
       <c r="E247" s="0" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>1.0195</v>
       </c>
       <c r="D248" s="0" t="n">
-        <v>13.97730430754979</v>
+        <v>29.588262</v>
       </c>
       <c r="E248" s="0" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>1.021</v>
       </c>
       <c r="D249" s="0" t="n">
-        <v>15.87151567944251</v>
+        <v>33.598078</v>
       </c>
       <c r="E249" s="0" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>1.021</v>
       </c>
       <c r="D250" s="0" t="n">
-        <v>15.87151567944251</v>
+        <v>33.598078</v>
       </c>
       <c r="E250" s="0" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>1.0225</v>
       </c>
       <c r="D251" s="0" t="n">
-        <v>26.44241164241165</v>
+        <v>55.975385</v>
       </c>
       <c r="E251" s="0" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>1.0225</v>
       </c>
       <c r="D252" s="0" t="n">
-        <v>26.44241164241165</v>
+        <v>55.975385</v>
       </c>
       <c r="E252" s="0" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>1.024</v>
       </c>
       <c r="D253" s="0" t="n">
-        <v>25.5905325443787</v>
+        <v>54.17206</v>
       </c>
       <c r="E253" s="0" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>1.024</v>
       </c>
       <c r="D254" s="0" t="n">
-        <v>25.5905325443787</v>
+        <v>54.17206</v>
       </c>
       <c r="E254" s="0" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>1.024</v>
       </c>
       <c r="D255" s="0" t="n">
-        <v>25.5905325443787</v>
+        <v>54.17206</v>
       </c>
       <c r="E255" s="0" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>1.024</v>
       </c>
       <c r="D256" s="0" t="n">
-        <v>25.5905325443787</v>
+        <v>54.17206</v>
       </c>
       <c r="E256" s="0" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>1.024</v>
       </c>
       <c r="D257" s="0" t="n">
-        <v>25.5905325443787</v>
+        <v>54.17206</v>
       </c>
       <c r="E257" s="0" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>1.0255</v>
       </c>
       <c r="D258" s="0" t="n">
-        <v>24.88792779240316</v>
+        <v>52.684731</v>
       </c>
       <c r="E258" s="0" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>1.0255</v>
       </c>
       <c r="D259" s="0" t="n">
-        <v>24.88792779240316</v>
+        <v>52.684731</v>
       </c>
       <c r="E259" s="0" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>1.027</v>
       </c>
       <c r="D260" s="0" t="n">
-        <v>25.36070276084618</v>
+        <v>53.685539</v>
       </c>
       <c r="E260" s="0" t="inlineStr">
         <is>
@@ -14498,7 +14498,7 @@
         <v>1.027</v>
       </c>
       <c r="D261" s="0" t="n">
-        <v>25.36070276084618</v>
+        <v>53.685539</v>
       </c>
       <c r="E261" s="0" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>1.0285</v>
       </c>
       <c r="D262" s="0" t="n">
-        <v>28.03182751540041</v>
+        <v>59.339986</v>
       </c>
       <c r="E262" s="0" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>1.0285</v>
       </c>
       <c r="D263" s="0" t="n">
-        <v>28.03182751540041</v>
+        <v>59.339986</v>
       </c>
       <c r="E263" s="0" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>1.03</v>
       </c>
       <c r="D264" s="0" t="n">
-        <v>45.54816285998014</v>
+        <v>96.419949</v>
       </c>
       <c r="E264" s="0" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>1.03</v>
       </c>
       <c r="D265" s="0" t="n">
-        <v>45.54816285998014</v>
+        <v>96.419949</v>
       </c>
       <c r="E265" s="0" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>1.0315</v>
       </c>
       <c r="D266" s="0" t="n">
-        <v>44.38804554079697</v>
+        <v>93.96412100000001</v>
       </c>
       <c r="E266" s="0" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>1.0315</v>
       </c>
       <c r="D267" s="0" t="n">
-        <v>44.38804554079697</v>
+        <v>93.96412100000001</v>
       </c>
       <c r="E267" s="0" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>1.033</v>
       </c>
       <c r="D268" s="0" t="n">
-        <v>43.76734943442372</v>
+        <v>92.650182</v>
       </c>
       <c r="E268" s="0" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>1.033</v>
       </c>
       <c r="D269" s="0" t="n">
-        <v>43.76734943442372</v>
+        <v>92.650182</v>
       </c>
       <c r="E269" s="0" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>1.0345</v>
       </c>
       <c r="D270" s="0" t="n">
-        <v>42.85035211267606</v>
+        <v>90.70901000000001</v>
       </c>
       <c r="E270" s="0" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>1.0345</v>
       </c>
       <c r="D271" s="0" t="n">
-        <v>42.85035211267606</v>
+        <v>90.70901000000001</v>
       </c>
       <c r="E271" s="0" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>1.036</v>
       </c>
       <c r="D272" s="0" t="n">
-        <v>44.06170752324599</v>
+        <v>93.273302</v>
       </c>
       <c r="E272" s="0" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>1.036</v>
       </c>
       <c r="D273" s="0" t="n">
-        <v>44.06170752324599</v>
+        <v>93.273302</v>
       </c>
       <c r="E273" s="0" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>1.0375</v>
       </c>
       <c r="D274" s="0" t="n">
-        <v>83.6751541141785</v>
+        <v>177.130175</v>
       </c>
       <c r="E274" s="0" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>1.0375</v>
       </c>
       <c r="D275" s="0" t="n">
-        <v>83.6751541141785</v>
+        <v>177.130175</v>
       </c>
       <c r="E275" s="0" t="inlineStr">
         <is>

--- a/Luban/Config/Datas/Levels/L02/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L02/EnemyData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25920" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1388,10 +1388,10 @@
         <v>3140136</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>1.10165</v>
+        <v>1.1</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>8.801983</v>
+        <v>8.5</v>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
@@ -1439,10 +1439,10 @@
         <v>3140144</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>1.10165</v>
+        <v>1.1</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>8.801983</v>
+        <v>8.5</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
@@ -1490,10 +1490,10 @@
         <v>3142136</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>1.1033</v>
+        <v>1.1</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>9.216556000000001</v>
+        <v>9.5</v>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
@@ -1541,10 +1541,10 @@
         <v>3142144</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>1.1033</v>
+        <v>1.1</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>9.216556000000001</v>
+        <v>9.5</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>1.10495</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>12.108868</v>
+        <v>12</v>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>1.10495</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>12.108868</v>
+        <v>12</v>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>1.054725</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>7.870764</v>
+        <v>7</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>1.1066</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>14.044216</v>
+        <v>13.5</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>1.1066</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>14.044216</v>
+        <v>13.5</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>1.0563</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>9.128741</v>
+        <v>9</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
@@ -2102,10 +2102,10 @@
         <v>3150107</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>1.009</v>
+        <v>1.04</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>11.854522</v>
+        <v>12</v>
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
@@ -2408,10 +2408,10 @@
         <v>3152091</v>
       </c>
       <c r="C24" s="0" t="n">
-        <v>1.0105</v>
+        <v>1.12</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>12.610506</v>
+        <v>16</v>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
@@ -2714,10 +2714,10 @@
         <v>3154115</v>
       </c>
       <c r="C30" s="0" t="n">
-        <v>1.012</v>
+        <v>1.06</v>
       </c>
       <c r="D30" s="0" t="n">
-        <v>15.004227</v>
+        <v>16</v>
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
@@ -3020,10 +3020,10 @@
         <v>3156107</v>
       </c>
       <c r="C36" s="0" t="n">
-        <v>1.0135</v>
+        <v>1.1</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>17.83469</v>
+        <v>18</v>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
@@ -3326,10 +3326,10 @@
         <v>3158091</v>
       </c>
       <c r="C42" s="0" t="n">
-        <v>1.015</v>
+        <v>1.12</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>30.778894</v>
+        <v>32</v>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
         <v>3162091</v>
       </c>
       <c r="C55" s="0" t="n">
-        <v>1.018</v>
+        <v>1.05</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>25.943831</v>
+        <v>26</v>
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
@@ -4040,10 +4040,10 @@
         <v>3162107</v>
       </c>
       <c r="C56" s="0" t="n">
-        <v>1.018</v>
+        <v>1.05</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>25.943831</v>
+        <v>26</v>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
@@ -4448,10 +4448,10 @@
         <v>3164091</v>
       </c>
       <c r="C64" s="0" t="n">
-        <v>1.0195</v>
+        <v>1.1</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>29.588262</v>
+        <v>31</v>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
@@ -4499,10 +4499,10 @@
         <v>3164115</v>
       </c>
       <c r="C65" s="0" t="n">
-        <v>1.0195</v>
+        <v>1.1</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>29.588262</v>
+        <v>31</v>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
@@ -4907,10 +4907,10 @@
         <v>3166107</v>
       </c>
       <c r="C73" s="0" t="n">
-        <v>1.021</v>
+        <v>1.14</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>33.598078</v>
+        <v>35</v>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
@@ -4958,10 +4958,10 @@
         <v>3166115</v>
       </c>
       <c r="C74" s="0" t="n">
-        <v>1.021</v>
+        <v>1.14</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>33.598078</v>
+        <v>35</v>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
@@ -5366,10 +5366,10 @@
         <v>3168091</v>
       </c>
       <c r="C82" s="0" t="n">
-        <v>1.0225</v>
+        <v>1.13</v>
       </c>
       <c r="D82" s="0" t="n">
-        <v>55.975385</v>
+        <v>56</v>
       </c>
       <c r="E82" s="0" t="inlineStr">
         <is>
@@ -5417,10 +5417,10 @@
         <v>3168107</v>
       </c>
       <c r="C83" s="0" t="n">
-        <v>1.0225</v>
+        <v>1.13</v>
       </c>
       <c r="D83" s="0" t="n">
-        <v>55.975385</v>
+        <v>56</v>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
@@ -6284,10 +6284,10 @@
         <v>3172091</v>
       </c>
       <c r="C100" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.12</v>
       </c>
       <c r="D100" s="0" t="n">
-        <v>52.684731</v>
+        <v>53</v>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
@@ -6335,10 +6335,10 @@
         <v>3172107</v>
       </c>
       <c r="C101" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.12</v>
       </c>
       <c r="D101" s="0" t="n">
-        <v>52.684731</v>
+        <v>53</v>
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
@@ -6386,10 +6386,10 @@
         <v>3172115</v>
       </c>
       <c r="C102" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.12</v>
       </c>
       <c r="D102" s="0" t="n">
-        <v>52.684731</v>
+        <v>53</v>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
@@ -6845,10 +6845,10 @@
         <v>3174091</v>
       </c>
       <c r="C111" s="0" t="n">
-        <v>1.027</v>
+        <v>1.12</v>
       </c>
       <c r="D111" s="0" t="n">
-        <v>53.685539</v>
+        <v>57</v>
       </c>
       <c r="E111" s="0" t="inlineStr">
         <is>
@@ -6896,10 +6896,10 @@
         <v>3174107</v>
       </c>
       <c r="C112" s="0" t="n">
-        <v>1.027</v>
+        <v>1.12</v>
       </c>
       <c r="D112" s="0" t="n">
-        <v>53.685539</v>
+        <v>57</v>
       </c>
       <c r="E112" s="0" t="inlineStr">
         <is>
@@ -6947,10 +6947,10 @@
         <v>3174115</v>
       </c>
       <c r="C113" s="0" t="n">
-        <v>1.027</v>
+        <v>1.12</v>
       </c>
       <c r="D113" s="0" t="n">
-        <v>53.685539</v>
+        <v>57</v>
       </c>
       <c r="E113" s="0" t="inlineStr">
         <is>
@@ -7406,10 +7406,10 @@
         <v>3176091</v>
       </c>
       <c r="C122" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.16</v>
       </c>
       <c r="D122" s="0" t="n">
-        <v>59.339986</v>
+        <v>61</v>
       </c>
       <c r="E122" s="0" t="inlineStr">
         <is>
@@ -7457,10 +7457,10 @@
         <v>3176107</v>
       </c>
       <c r="C123" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.16</v>
       </c>
       <c r="D123" s="0" t="n">
-        <v>59.339986</v>
+        <v>61</v>
       </c>
       <c r="E123" s="0" t="inlineStr">
         <is>
@@ -7508,10 +7508,10 @@
         <v>3176115</v>
       </c>
       <c r="C124" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.16</v>
       </c>
       <c r="D124" s="0" t="n">
-        <v>59.339986</v>
+        <v>61</v>
       </c>
       <c r="E124" s="0" t="inlineStr">
         <is>
@@ -7967,10 +7967,10 @@
         <v>3178091</v>
       </c>
       <c r="C133" s="0" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="D133" s="0" t="n">
-        <v>96.419949</v>
+        <v>98</v>
       </c>
       <c r="E133" s="0" t="inlineStr">
         <is>
@@ -8018,10 +8018,10 @@
         <v>3178107</v>
       </c>
       <c r="C134" s="0" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="D134" s="0" t="n">
-        <v>96.419949</v>
+        <v>98</v>
       </c>
       <c r="E134" s="0" t="inlineStr">
         <is>
@@ -8069,10 +8069,10 @@
         <v>3178115</v>
       </c>
       <c r="C135" s="0" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="D135" s="0" t="n">
-        <v>96.419949</v>
+        <v>98</v>
       </c>
       <c r="E135" s="0" t="inlineStr">
         <is>
@@ -8579,10 +8579,10 @@
         <v>3150091</v>
       </c>
       <c r="C145" s="0" t="n">
-        <v>1.009</v>
+        <v>1.04</v>
       </c>
       <c r="D145" s="0" t="n">
-        <v>11.854522</v>
+        <v>12</v>
       </c>
       <c r="E145" s="0" t="inlineStr">
         <is>
@@ -8630,10 +8630,10 @@
         <v>3152115</v>
       </c>
       <c r="C146" s="0" t="n">
-        <v>1.0105</v>
+        <v>1.12</v>
       </c>
       <c r="D146" s="0" t="n">
-        <v>12.610506</v>
+        <v>16</v>
       </c>
       <c r="E146" s="0" t="inlineStr">
         <is>
@@ -8681,10 +8681,10 @@
         <v>3154107</v>
       </c>
       <c r="C147" s="0" t="n">
-        <v>1.012</v>
+        <v>1.06</v>
       </c>
       <c r="D147" s="0" t="n">
-        <v>15.004227</v>
+        <v>16</v>
       </c>
       <c r="E147" s="0" t="inlineStr">
         <is>
@@ -8732,10 +8732,10 @@
         <v>3156091</v>
       </c>
       <c r="C148" s="0" t="n">
-        <v>1.0135</v>
+        <v>1.1</v>
       </c>
       <c r="D148" s="0" t="n">
-        <v>17.83469</v>
+        <v>18</v>
       </c>
       <c r="E148" s="0" t="inlineStr">
         <is>
@@ -8783,10 +8783,10 @@
         <v>3158115</v>
       </c>
       <c r="C149" s="0" t="n">
-        <v>1.015</v>
+        <v>1.12</v>
       </c>
       <c r="D149" s="0" t="n">
-        <v>30.778894</v>
+        <v>32</v>
       </c>
       <c r="E149" s="0" t="inlineStr">
         <is>
@@ -8834,10 +8834,10 @@
         <v>3162115</v>
       </c>
       <c r="C150" s="0" t="n">
-        <v>1.018</v>
+        <v>1.05</v>
       </c>
       <c r="D150" s="0" t="n">
-        <v>25.943831</v>
+        <v>26</v>
       </c>
       <c r="E150" s="0" t="inlineStr">
         <is>
@@ -8885,10 +8885,10 @@
         <v>3164107</v>
       </c>
       <c r="C151" s="0" t="n">
-        <v>1.0195</v>
+        <v>1.1</v>
       </c>
       <c r="D151" s="0" t="n">
-        <v>29.588262</v>
+        <v>31</v>
       </c>
       <c r="E151" s="0" t="inlineStr">
         <is>
@@ -8936,10 +8936,10 @@
         <v>3166091</v>
       </c>
       <c r="C152" s="0" t="n">
-        <v>1.021</v>
+        <v>1.14</v>
       </c>
       <c r="D152" s="0" t="n">
-        <v>33.598078</v>
+        <v>35</v>
       </c>
       <c r="E152" s="0" t="inlineStr">
         <is>
@@ -8987,10 +8987,10 @@
         <v>3168115</v>
       </c>
       <c r="C153" s="0" t="n">
-        <v>1.0225</v>
+        <v>1.13</v>
       </c>
       <c r="D153" s="0" t="n">
-        <v>55.975385</v>
+        <v>56</v>
       </c>
       <c r="E153" s="0" t="inlineStr">
         <is>
@@ -9038,10 +9038,10 @@
         <v>10016785</v>
       </c>
       <c r="C154" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.08</v>
       </c>
       <c r="D154" s="0" t="n">
-        <v>93.96412100000001</v>
+        <v>90</v>
       </c>
       <c r="E154" s="0" t="inlineStr">
         <is>
@@ -9089,10 +9089,10 @@
         <v>10016786</v>
       </c>
       <c r="C155" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.08</v>
       </c>
       <c r="D155" s="0" t="n">
-        <v>93.96412100000001</v>
+        <v>90</v>
       </c>
       <c r="E155" s="0" t="inlineStr">
         <is>
@@ -9140,10 +9140,10 @@
         <v>10016787</v>
       </c>
       <c r="C156" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.08</v>
       </c>
       <c r="D156" s="0" t="n">
-        <v>93.96412100000001</v>
+        <v>90</v>
       </c>
       <c r="E156" s="0" t="inlineStr">
         <is>
@@ -9599,10 +9599,10 @@
         <v>10016796</v>
       </c>
       <c r="C165" s="0" t="n">
-        <v>1.033</v>
+        <v>1.12</v>
       </c>
       <c r="D165" s="0" t="n">
-        <v>92.650182</v>
+        <v>94</v>
       </c>
       <c r="E165" s="0" t="inlineStr">
         <is>
@@ -9650,10 +9650,10 @@
         <v>10016797</v>
       </c>
       <c r="C166" s="0" t="n">
-        <v>1.033</v>
+        <v>1.12</v>
       </c>
       <c r="D166" s="0" t="n">
-        <v>92.650182</v>
+        <v>94</v>
       </c>
       <c r="E166" s="0" t="inlineStr">
         <is>
@@ -9701,10 +9701,10 @@
         <v>10016798</v>
       </c>
       <c r="C167" s="0" t="n">
-        <v>1.033</v>
+        <v>1.12</v>
       </c>
       <c r="D167" s="0" t="n">
-        <v>92.650182</v>
+        <v>94</v>
       </c>
       <c r="E167" s="0" t="inlineStr">
         <is>
@@ -10160,10 +10160,10 @@
         <v>10016807</v>
       </c>
       <c r="C176" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.18</v>
       </c>
       <c r="D176" s="0" t="n">
-        <v>90.70901000000001</v>
+        <v>96</v>
       </c>
       <c r="E176" s="0" t="inlineStr">
         <is>
@@ -10211,10 +10211,10 @@
         <v>10016808</v>
       </c>
       <c r="C177" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.18</v>
       </c>
       <c r="D177" s="0" t="n">
-        <v>90.70901000000001</v>
+        <v>96</v>
       </c>
       <c r="E177" s="0" t="inlineStr">
         <is>
@@ -10262,10 +10262,10 @@
         <v>10016809</v>
       </c>
       <c r="C178" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.18</v>
       </c>
       <c r="D178" s="0" t="n">
-        <v>90.70901000000001</v>
+        <v>96</v>
       </c>
       <c r="E178" s="0" t="inlineStr">
         <is>
@@ -10721,10 +10721,10 @@
         <v>10016818</v>
       </c>
       <c r="C187" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D187" s="0" t="n">
-        <v>93.273302</v>
+        <v>92</v>
       </c>
       <c r="E187" s="0" t="inlineStr">
         <is>
@@ -10772,10 +10772,10 @@
         <v>10016819</v>
       </c>
       <c r="C188" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D188" s="0" t="n">
-        <v>93.273302</v>
+        <v>92</v>
       </c>
       <c r="E188" s="0" t="inlineStr">
         <is>
@@ -10823,10 +10823,10 @@
         <v>10016820</v>
       </c>
       <c r="C189" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D189" s="0" t="n">
-        <v>93.273302</v>
+        <v>92</v>
       </c>
       <c r="E189" s="0" t="inlineStr">
         <is>
@@ -11282,10 +11282,10 @@
         <v>10016829</v>
       </c>
       <c r="C198" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.12</v>
       </c>
       <c r="D198" s="0" t="n">
-        <v>177.130175</v>
+        <v>168</v>
       </c>
       <c r="E198" s="0" t="inlineStr">
         <is>
@@ -11333,10 +11333,10 @@
         <v>10016830</v>
       </c>
       <c r="C199" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.12</v>
       </c>
       <c r="D199" s="0" t="n">
-        <v>177.130175</v>
+        <v>168</v>
       </c>
       <c r="E199" s="0" t="inlineStr">
         <is>
@@ -11384,10 +11384,10 @@
         <v>10016831</v>
       </c>
       <c r="C200" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.12</v>
       </c>
       <c r="D200" s="0" t="n">
-        <v>177.130175</v>
+        <v>168</v>
       </c>
       <c r="E200" s="0" t="inlineStr">
         <is>
@@ -11894,10 +11894,10 @@
         <v>3158107</v>
       </c>
       <c r="C210" s="0" t="n">
-        <v>1.015</v>
+        <v>1.12</v>
       </c>
       <c r="D210" s="0" t="n">
-        <v>30.778894</v>
+        <v>32</v>
       </c>
       <c r="E210" s="0" t="inlineStr">
         <is>
@@ -11945,10 +11945,10 @@
         <v>3150115</v>
       </c>
       <c r="C211" s="0" t="n">
-        <v>1.009</v>
+        <v>1.04</v>
       </c>
       <c r="D211" s="0" t="n">
-        <v>11.854522</v>
+        <v>12</v>
       </c>
       <c r="E211" s="0" t="inlineStr">
         <is>
@@ -11996,10 +11996,10 @@
         <v>3152107</v>
       </c>
       <c r="C212" s="0" t="n">
-        <v>1.0105</v>
+        <v>1.12</v>
       </c>
       <c r="D212" s="0" t="n">
-        <v>12.610506</v>
+        <v>16</v>
       </c>
       <c r="E212" s="0" t="inlineStr">
         <is>
@@ -12047,10 +12047,10 @@
         <v>3154091</v>
       </c>
       <c r="C213" s="0" t="n">
-        <v>1.012</v>
+        <v>1.06</v>
       </c>
       <c r="D213" s="0" t="n">
-        <v>15.004227</v>
+        <v>16</v>
       </c>
       <c r="E213" s="0" t="inlineStr">
         <is>
@@ -12098,10 +12098,10 @@
         <v>3156115</v>
       </c>
       <c r="C214" s="0" t="n">
-        <v>1.0135</v>
+        <v>1.1</v>
       </c>
       <c r="D214" s="0" t="n">
-        <v>17.83469</v>
+        <v>18</v>
       </c>
       <c r="E214" s="0" t="inlineStr">
         <is>
@@ -12659,10 +12659,10 @@
         <v>3148019</v>
       </c>
       <c r="C225" s="0" t="n">
-        <v>1.0075</v>
+        <v>1.08</v>
       </c>
       <c r="D225" s="0" t="n">
-        <v>12.942188</v>
+        <v>13</v>
       </c>
       <c r="E225" s="0" t="inlineStr">
         <is>
@@ -12710,10 +12710,10 @@
         <v>3148091</v>
       </c>
       <c r="C226" s="0" t="n">
-        <v>1.0075</v>
+        <v>1.08</v>
       </c>
       <c r="D226" s="0" t="n">
-        <v>12.942188</v>
+        <v>13</v>
       </c>
       <c r="E226" s="0" t="inlineStr">
         <is>
@@ -12761,10 +12761,10 @@
         <v>3148099</v>
       </c>
       <c r="C227" s="0" t="n">
-        <v>1.0075</v>
+        <v>1.08</v>
       </c>
       <c r="D227" s="0" t="n">
-        <v>12.942188</v>
+        <v>13</v>
       </c>
       <c r="E227" s="0" t="inlineStr">
         <is>
@@ -12812,10 +12812,10 @@
         <v>3148107</v>
       </c>
       <c r="C228" s="0" t="n">
-        <v>1.0075</v>
+        <v>1.08</v>
       </c>
       <c r="D228" s="0" t="n">
-        <v>12.942188</v>
+        <v>13</v>
       </c>
       <c r="E228" s="0" t="inlineStr">
         <is>
@@ -12863,10 +12863,10 @@
         <v>3148115</v>
       </c>
       <c r="C229" s="0" t="n">
-        <v>1.0075</v>
+        <v>1.08</v>
       </c>
       <c r="D229" s="0" t="n">
-        <v>12.942188</v>
+        <v>13</v>
       </c>
       <c r="E229" s="0" t="inlineStr">
         <is>
@@ -12914,10 +12914,10 @@
         <v>3150019</v>
       </c>
       <c r="C230" s="0" t="n">
-        <v>1.009</v>
+        <v>1.04</v>
       </c>
       <c r="D230" s="0" t="n">
-        <v>11.854522</v>
+        <v>12</v>
       </c>
       <c r="E230" s="0" t="inlineStr">
         <is>
@@ -12965,10 +12965,10 @@
         <v>3150099</v>
       </c>
       <c r="C231" s="0" t="n">
-        <v>1.009</v>
+        <v>1.04</v>
       </c>
       <c r="D231" s="0" t="n">
-        <v>11.854522</v>
+        <v>12</v>
       </c>
       <c r="E231" s="0" t="inlineStr">
         <is>
@@ -13016,10 +13016,10 @@
         <v>3152019</v>
       </c>
       <c r="C232" s="0" t="n">
-        <v>1.0105</v>
+        <v>1.12</v>
       </c>
       <c r="D232" s="0" t="n">
-        <v>12.610506</v>
+        <v>16</v>
       </c>
       <c r="E232" s="0" t="inlineStr">
         <is>
@@ -13067,10 +13067,10 @@
         <v>3152099</v>
       </c>
       <c r="C233" s="0" t="n">
-        <v>1.0105</v>
+        <v>1.12</v>
       </c>
       <c r="D233" s="0" t="n">
-        <v>12.610506</v>
+        <v>16</v>
       </c>
       <c r="E233" s="0" t="inlineStr">
         <is>
@@ -13118,10 +13118,10 @@
         <v>3154019</v>
       </c>
       <c r="C234" s="0" t="n">
-        <v>1.012</v>
+        <v>1.06</v>
       </c>
       <c r="D234" s="0" t="n">
-        <v>15.004227</v>
+        <v>16</v>
       </c>
       <c r="E234" s="0" t="inlineStr">
         <is>
@@ -13169,10 +13169,10 @@
         <v>3154099</v>
       </c>
       <c r="C235" s="0" t="n">
-        <v>1.012</v>
+        <v>1.06</v>
       </c>
       <c r="D235" s="0" t="n">
-        <v>15.004227</v>
+        <v>16</v>
       </c>
       <c r="E235" s="0" t="inlineStr">
         <is>
@@ -13220,10 +13220,10 @@
         <v>3156019</v>
       </c>
       <c r="C236" s="0" t="n">
-        <v>1.0135</v>
+        <v>1.1</v>
       </c>
       <c r="D236" s="0" t="n">
-        <v>17.83469</v>
+        <v>18</v>
       </c>
       <c r="E236" s="0" t="inlineStr">
         <is>
@@ -13271,10 +13271,10 @@
         <v>3156099</v>
       </c>
       <c r="C237" s="0" t="n">
-        <v>1.0135</v>
+        <v>1.1</v>
       </c>
       <c r="D237" s="0" t="n">
-        <v>17.83469</v>
+        <v>18</v>
       </c>
       <c r="E237" s="0" t="inlineStr">
         <is>
@@ -13322,10 +13322,10 @@
         <v>3158019</v>
       </c>
       <c r="C238" s="0" t="n">
-        <v>1.015</v>
+        <v>1.12</v>
       </c>
       <c r="D238" s="0" t="n">
-        <v>30.778894</v>
+        <v>32</v>
       </c>
       <c r="E238" s="0" t="inlineStr">
         <is>
@@ -13373,10 +13373,10 @@
         <v>3158099</v>
       </c>
       <c r="C239" s="0" t="n">
-        <v>1.015</v>
+        <v>1.12</v>
       </c>
       <c r="D239" s="0" t="n">
-        <v>30.778894</v>
+        <v>32</v>
       </c>
       <c r="E239" s="0" t="inlineStr">
         <is>
@@ -13424,10 +13424,10 @@
         <v>3160019</v>
       </c>
       <c r="C240" s="0" t="n">
-        <v>1.0165</v>
+        <v>1.08</v>
       </c>
       <c r="D240" s="0" t="n">
-        <v>26.487046</v>
+        <v>27</v>
       </c>
       <c r="E240" s="0" t="inlineStr">
         <is>
@@ -13475,10 +13475,10 @@
         <v>3160091</v>
       </c>
       <c r="C241" s="0" t="n">
-        <v>1.0165</v>
+        <v>1.08</v>
       </c>
       <c r="D241" s="0" t="n">
-        <v>26.487046</v>
+        <v>27</v>
       </c>
       <c r="E241" s="0" t="inlineStr">
         <is>
@@ -13526,10 +13526,10 @@
         <v>3160099</v>
       </c>
       <c r="C242" s="0" t="n">
-        <v>1.0165</v>
+        <v>1.08</v>
       </c>
       <c r="D242" s="0" t="n">
-        <v>26.487046</v>
+        <v>27</v>
       </c>
       <c r="E242" s="0" t="inlineStr">
         <is>
@@ -13577,10 +13577,10 @@
         <v>3160107</v>
       </c>
       <c r="C243" s="0" t="n">
-        <v>1.0165</v>
+        <v>1.08</v>
       </c>
       <c r="D243" s="0" t="n">
-        <v>26.487046</v>
+        <v>27</v>
       </c>
       <c r="E243" s="0" t="inlineStr">
         <is>
@@ -13628,10 +13628,10 @@
         <v>3160115</v>
       </c>
       <c r="C244" s="0" t="n">
-        <v>1.0165</v>
+        <v>1.08</v>
       </c>
       <c r="D244" s="0" t="n">
-        <v>26.487046</v>
+        <v>27</v>
       </c>
       <c r="E244" s="0" t="inlineStr">
         <is>
@@ -13679,10 +13679,10 @@
         <v>3162019</v>
       </c>
       <c r="C245" s="0" t="n">
-        <v>1.018</v>
+        <v>1.05</v>
       </c>
       <c r="D245" s="0" t="n">
-        <v>25.943831</v>
+        <v>26</v>
       </c>
       <c r="E245" s="0" t="inlineStr">
         <is>
@@ -13730,10 +13730,10 @@
         <v>3162099</v>
       </c>
       <c r="C246" s="0" t="n">
-        <v>1.018</v>
+        <v>1.05</v>
       </c>
       <c r="D246" s="0" t="n">
-        <v>25.943831</v>
+        <v>26</v>
       </c>
       <c r="E246" s="0" t="inlineStr">
         <is>
@@ -13781,10 +13781,10 @@
         <v>3164019</v>
       </c>
       <c r="C247" s="0" t="n">
-        <v>1.0195</v>
+        <v>1.1</v>
       </c>
       <c r="D247" s="0" t="n">
-        <v>29.588262</v>
+        <v>31</v>
       </c>
       <c r="E247" s="0" t="inlineStr">
         <is>
@@ -13832,10 +13832,10 @@
         <v>3164099</v>
       </c>
       <c r="C248" s="0" t="n">
-        <v>1.0195</v>
+        <v>1.1</v>
       </c>
       <c r="D248" s="0" t="n">
-        <v>29.588262</v>
+        <v>31</v>
       </c>
       <c r="E248" s="0" t="inlineStr">
         <is>
@@ -13883,10 +13883,10 @@
         <v>3166019</v>
       </c>
       <c r="C249" s="0" t="n">
-        <v>1.021</v>
+        <v>1.14</v>
       </c>
       <c r="D249" s="0" t="n">
-        <v>33.598078</v>
+        <v>35</v>
       </c>
       <c r="E249" s="0" t="inlineStr">
         <is>
@@ -13934,10 +13934,10 @@
         <v>3166099</v>
       </c>
       <c r="C250" s="0" t="n">
-        <v>1.021</v>
+        <v>1.14</v>
       </c>
       <c r="D250" s="0" t="n">
-        <v>33.598078</v>
+        <v>35</v>
       </c>
       <c r="E250" s="0" t="inlineStr">
         <is>
@@ -13985,10 +13985,10 @@
         <v>3168019</v>
       </c>
       <c r="C251" s="0" t="n">
-        <v>1.0225</v>
+        <v>1.13</v>
       </c>
       <c r="D251" s="0" t="n">
-        <v>55.975385</v>
+        <v>56</v>
       </c>
       <c r="E251" s="0" t="inlineStr">
         <is>
@@ -14036,10 +14036,10 @@
         <v>3168099</v>
       </c>
       <c r="C252" s="0" t="n">
-        <v>1.0225</v>
+        <v>1.13</v>
       </c>
       <c r="D252" s="0" t="n">
-        <v>55.975385</v>
+        <v>56</v>
       </c>
       <c r="E252" s="0" t="inlineStr">
         <is>
@@ -14087,10 +14087,10 @@
         <v>3170019</v>
       </c>
       <c r="C253" s="0" t="n">
-        <v>1.024</v>
+        <v>1.08</v>
       </c>
       <c r="D253" s="0" t="n">
-        <v>54.17206</v>
+        <v>50</v>
       </c>
       <c r="E253" s="0" t="inlineStr">
         <is>
@@ -14138,10 +14138,10 @@
         <v>3170091</v>
       </c>
       <c r="C254" s="0" t="n">
-        <v>1.024</v>
+        <v>1.08</v>
       </c>
       <c r="D254" s="0" t="n">
-        <v>54.17206</v>
+        <v>50</v>
       </c>
       <c r="E254" s="0" t="inlineStr">
         <is>
@@ -14189,10 +14189,10 @@
         <v>3170099</v>
       </c>
       <c r="C255" s="0" t="n">
-        <v>1.024</v>
+        <v>1.08</v>
       </c>
       <c r="D255" s="0" t="n">
-        <v>54.17206</v>
+        <v>50</v>
       </c>
       <c r="E255" s="0" t="inlineStr">
         <is>
@@ -14240,10 +14240,10 @@
         <v>3170107</v>
       </c>
       <c r="C256" s="0" t="n">
-        <v>1.024</v>
+        <v>1.08</v>
       </c>
       <c r="D256" s="0" t="n">
-        <v>54.17206</v>
+        <v>50</v>
       </c>
       <c r="E256" s="0" t="inlineStr">
         <is>
@@ -14291,10 +14291,10 @@
         <v>3170115</v>
       </c>
       <c r="C257" s="0" t="n">
-        <v>1.024</v>
+        <v>1.08</v>
       </c>
       <c r="D257" s="0" t="n">
-        <v>54.17206</v>
+        <v>50</v>
       </c>
       <c r="E257" s="0" t="inlineStr">
         <is>
@@ -14342,10 +14342,10 @@
         <v>3172019</v>
       </c>
       <c r="C258" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.12</v>
       </c>
       <c r="D258" s="0" t="n">
-        <v>52.684731</v>
+        <v>53</v>
       </c>
       <c r="E258" s="0" t="inlineStr">
         <is>
@@ -14393,10 +14393,10 @@
         <v>3172099</v>
       </c>
       <c r="C259" s="0" t="n">
-        <v>1.0255</v>
+        <v>1.12</v>
       </c>
       <c r="D259" s="0" t="n">
-        <v>52.684731</v>
+        <v>53</v>
       </c>
       <c r="E259" s="0" t="inlineStr">
         <is>
@@ -14444,10 +14444,10 @@
         <v>3174019</v>
       </c>
       <c r="C260" s="0" t="n">
-        <v>1.027</v>
+        <v>1.12</v>
       </c>
       <c r="D260" s="0" t="n">
-        <v>53.685539</v>
+        <v>57</v>
       </c>
       <c r="E260" s="0" t="inlineStr">
         <is>
@@ -14495,10 +14495,10 @@
         <v>3174099</v>
       </c>
       <c r="C261" s="0" t="n">
-        <v>1.027</v>
+        <v>1.12</v>
       </c>
       <c r="D261" s="0" t="n">
-        <v>53.685539</v>
+        <v>57</v>
       </c>
       <c r="E261" s="0" t="inlineStr">
         <is>
@@ -14546,10 +14546,10 @@
         <v>3176019</v>
       </c>
       <c r="C262" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.16</v>
       </c>
       <c r="D262" s="0" t="n">
-        <v>59.339986</v>
+        <v>61</v>
       </c>
       <c r="E262" s="0" t="inlineStr">
         <is>
@@ -14597,10 +14597,10 @@
         <v>3176099</v>
       </c>
       <c r="C263" s="0" t="n">
-        <v>1.0285</v>
+        <v>1.16</v>
       </c>
       <c r="D263" s="0" t="n">
-        <v>59.339986</v>
+        <v>61</v>
       </c>
       <c r="E263" s="0" t="inlineStr">
         <is>
@@ -14648,10 +14648,10 @@
         <v>3178019</v>
       </c>
       <c r="C264" s="0" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="D264" s="0" t="n">
-        <v>96.419949</v>
+        <v>98</v>
       </c>
       <c r="E264" s="0" t="inlineStr">
         <is>
@@ -14699,10 +14699,10 @@
         <v>3178099</v>
       </c>
       <c r="C265" s="0" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="D265" s="0" t="n">
-        <v>96.419949</v>
+        <v>98</v>
       </c>
       <c r="E265" s="0" t="inlineStr">
         <is>
@@ -14750,10 +14750,10 @@
         <v>10048480</v>
       </c>
       <c r="C266" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.08</v>
       </c>
       <c r="D266" s="0" t="n">
-        <v>93.96412100000001</v>
+        <v>90</v>
       </c>
       <c r="E266" s="0" t="inlineStr">
         <is>
@@ -14801,10 +14801,10 @@
         <v>10048481</v>
       </c>
       <c r="C267" s="0" t="n">
-        <v>1.0315</v>
+        <v>1.08</v>
       </c>
       <c r="D267" s="0" t="n">
-        <v>93.96412100000001</v>
+        <v>90</v>
       </c>
       <c r="E267" s="0" t="inlineStr">
         <is>
@@ -14852,10 +14852,10 @@
         <v>10048482</v>
       </c>
       <c r="C268" s="0" t="n">
-        <v>1.033</v>
+        <v>1.12</v>
       </c>
       <c r="D268" s="0" t="n">
-        <v>92.650182</v>
+        <v>94</v>
       </c>
       <c r="E268" s="0" t="inlineStr">
         <is>
@@ -14903,10 +14903,10 @@
         <v>10048483</v>
       </c>
       <c r="C269" s="0" t="n">
-        <v>1.033</v>
+        <v>1.12</v>
       </c>
       <c r="D269" s="0" t="n">
-        <v>92.650182</v>
+        <v>94</v>
       </c>
       <c r="E269" s="0" t="inlineStr">
         <is>
@@ -14954,10 +14954,10 @@
         <v>10048484</v>
       </c>
       <c r="C270" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.18</v>
       </c>
       <c r="D270" s="0" t="n">
-        <v>90.70901000000001</v>
+        <v>96</v>
       </c>
       <c r="E270" s="0" t="inlineStr">
         <is>
@@ -15005,10 +15005,10 @@
         <v>10048485</v>
       </c>
       <c r="C271" s="0" t="n">
-        <v>1.0345</v>
+        <v>1.18</v>
       </c>
       <c r="D271" s="0" t="n">
-        <v>90.70901000000001</v>
+        <v>96</v>
       </c>
       <c r="E271" s="0" t="inlineStr">
         <is>
@@ -15056,10 +15056,10 @@
         <v>10048486</v>
       </c>
       <c r="C272" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D272" s="0" t="n">
-        <v>93.273302</v>
+        <v>92</v>
       </c>
       <c r="E272" s="0" t="inlineStr">
         <is>
@@ -15107,10 +15107,10 @@
         <v>10048487</v>
       </c>
       <c r="C273" s="0" t="n">
-        <v>1.036</v>
+        <v>1.1</v>
       </c>
       <c r="D273" s="0" t="n">
-        <v>93.273302</v>
+        <v>92</v>
       </c>
       <c r="E273" s="0" t="inlineStr">
         <is>
@@ -15158,10 +15158,10 @@
         <v>10048488</v>
       </c>
       <c r="C274" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.12</v>
       </c>
       <c r="D274" s="0" t="n">
-        <v>177.130175</v>
+        <v>168</v>
       </c>
       <c r="E274" s="0" t="inlineStr">
         <is>
@@ -15209,10 +15209,10 @@
         <v>10048489</v>
       </c>
       <c r="C275" s="0" t="n">
-        <v>1.0375</v>
+        <v>1.12</v>
       </c>
       <c r="D275" s="0" t="n">
-        <v>177.130175</v>
+        <v>168</v>
       </c>
       <c r="E275" s="0" t="inlineStr">
         <is>

--- a/Luban/Config/Datas/Levels/L02/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L02/EnemyData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25920" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1122,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P275"/>
+  <dimension ref="A1:Q275"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" style="2" min="1" max="1"/>
@@ -1140,6 +1140,7 @@
     <col width="9" customWidth="1" style="2" min="13" max="14"/>
     <col width="17.3333333333333" customWidth="1" style="2" min="15" max="15"/>
     <col width="9" customWidth="1" style="2" min="16" max="16384"/>
+    <col width="10" customWidth="1" style="2" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1223,6 +1224,11 @@
           <t>desc</t>
         </is>
       </c>
+      <c r="Q1" s="0" t="inlineStr">
+        <is>
+          <t>levelId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1272,37 +1278,42 @@
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K2" s="0" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="N2" s="0" t="inlineStr">
+      <c r="O2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q2" s="0" t="inlineStr">
         <is>
           <t>int</t>
-        </is>
-      </c>
-      <c r="O2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="P2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
     </row>
@@ -1380,6 +1391,11 @@
       <c r="P3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+      <c r="Q3" s="0" t="inlineStr">
+        <is>
+          <t>所属关卡 id（本表每关独立一份，2026-10-30 拆分）</t>
         </is>
       </c>
     </row>
@@ -1433,6 +1449,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=1</t>
         </is>
       </c>
+      <c r="Q4" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="0" t="n">
@@ -1484,6 +1503,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=1</t>
         </is>
       </c>
+      <c r="Q5" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="0" t="n">
@@ -1535,6 +1557,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=2</t>
         </is>
       </c>
+      <c r="Q6" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" customFormat="1" s="1">
       <c r="B7" s="0" t="n">
@@ -1586,6 +1611,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=2</t>
         </is>
       </c>
+      <c r="Q7" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" customFormat="1" s="1">
       <c r="B8" s="0" t="n">
@@ -1637,6 +1665,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=3</t>
         </is>
       </c>
+      <c r="Q8" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" customFormat="1" s="1">
       <c r="B9" s="0" t="n">
@@ -1688,6 +1719,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=3</t>
         </is>
       </c>
+      <c r="Q9" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" customFormat="1" s="1">
       <c r="B10" s="0" t="n">
@@ -1739,6 +1773,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=3</t>
         </is>
       </c>
+      <c r="Q10" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" customFormat="1" s="1">
       <c r="B11" s="0" t="n">
@@ -1790,6 +1827,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=4</t>
         </is>
       </c>
+      <c r="Q11" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="n">
@@ -1841,6 +1881,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=4</t>
         </is>
       </c>
+      <c r="Q12" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="n">
@@ -1892,6 +1935,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=4</t>
         </is>
       </c>
+      <c r="Q13" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="n">
@@ -1943,6 +1989,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=5</t>
         </is>
       </c>
+      <c r="Q14" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="n">
@@ -1994,6 +2043,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=5</t>
         </is>
       </c>
+      <c r="Q15" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="0" t="n">
@@ -2045,6 +2097,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=5</t>
         </is>
       </c>
+      <c r="Q16" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="0" t="n">
@@ -2096,6 +2151,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=5</t>
         </is>
       </c>
+      <c r="Q17" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="0" t="n">
@@ -2147,6 +2205,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=6</t>
         </is>
       </c>
+      <c r="Q18" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="0" t="n">
@@ -2198,6 +2259,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=6</t>
         </is>
       </c>
+      <c r="Q19" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="n">
@@ -2249,6 +2313,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=6</t>
         </is>
       </c>
+      <c r="Q20" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="n">
@@ -2300,6 +2367,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=6</t>
         </is>
       </c>
+      <c r="Q21" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="0" t="n">
@@ -2351,6 +2421,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=6</t>
         </is>
       </c>
+      <c r="Q22" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="0" t="n">
@@ -2402,6 +2475,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=6</t>
         </is>
       </c>
+      <c r="Q23" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="0" t="n">
@@ -2453,6 +2529,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=7</t>
         </is>
       </c>
+      <c r="Q24" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="n">
@@ -2504,6 +2583,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=7</t>
         </is>
       </c>
+      <c r="Q25" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="n">
@@ -2555,6 +2637,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=7</t>
         </is>
       </c>
+      <c r="Q26" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="n">
@@ -2606,6 +2691,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=7</t>
         </is>
       </c>
+      <c r="Q27" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="n">
@@ -2657,6 +2745,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=7</t>
         </is>
       </c>
+      <c r="Q28" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="0" t="n">
@@ -2708,6 +2799,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=7</t>
         </is>
       </c>
+      <c r="Q29" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="0" t="n">
@@ -2759,6 +2853,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=8</t>
         </is>
       </c>
+      <c r="Q30" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="0" t="n">
@@ -2810,6 +2907,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=8</t>
         </is>
       </c>
+      <c r="Q31" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="0" t="n">
@@ -2861,6 +2961,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=8</t>
         </is>
       </c>
+      <c r="Q32" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="0" t="n">
@@ -2912,6 +3015,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=8</t>
         </is>
       </c>
+      <c r="Q33" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="0" t="n">
@@ -2963,6 +3069,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=8</t>
         </is>
       </c>
+      <c r="Q34" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="0" t="n">
@@ -3014,6 +3123,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=8</t>
         </is>
       </c>
+      <c r="Q35" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="36">
       <c r="B36" s="0" t="n">
@@ -3065,6 +3177,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=9</t>
         </is>
       </c>
+      <c r="Q36" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="n">
@@ -3116,6 +3231,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=9</t>
         </is>
       </c>
+      <c r="Q37" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="n">
@@ -3167,6 +3285,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=9</t>
         </is>
       </c>
+      <c r="Q38" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="0" t="n">
@@ -3218,6 +3339,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=9</t>
         </is>
       </c>
+      <c r="Q39" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="0" t="n">
@@ -3269,6 +3393,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=9</t>
         </is>
       </c>
+      <c r="Q40" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="41">
       <c r="B41" s="0" t="n">
@@ -3320,6 +3447,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=9</t>
         </is>
       </c>
+      <c r="Q41" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="42">
       <c r="B42" s="0" t="n">
@@ -3371,6 +3501,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=10</t>
         </is>
       </c>
+      <c r="Q42" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="0" t="n">
@@ -3422,6 +3555,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=10</t>
         </is>
       </c>
+      <c r="Q43" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="B44" s="0" t="n">
@@ -3473,6 +3609,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=10</t>
         </is>
       </c>
+      <c r="Q44" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="0" t="n">
@@ -3524,6 +3663,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=10</t>
         </is>
       </c>
+      <c r="Q45" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="46">
       <c r="B46" s="0" t="n">
@@ -3575,6 +3717,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=10</t>
         </is>
       </c>
+      <c r="Q46" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="47">
       <c r="B47" s="0" t="n">
@@ -3626,6 +3771,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=10</t>
         </is>
       </c>
+      <c r="Q47" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="48">
       <c r="B48" s="0" t="n">
@@ -3677,6 +3825,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=11</t>
         </is>
       </c>
+      <c r="Q48" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="0" t="n">
@@ -3728,6 +3879,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=11</t>
         </is>
       </c>
+      <c r="Q49" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="50">
       <c r="B50" s="0" t="n">
@@ -3779,6 +3933,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=11</t>
         </is>
       </c>
+      <c r="Q50" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="51">
       <c r="B51" s="0" t="n">
@@ -3830,6 +3987,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=11</t>
         </is>
       </c>
+      <c r="Q51" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="52">
       <c r="B52" s="0" t="n">
@@ -3881,6 +4041,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=11</t>
         </is>
       </c>
+      <c r="Q52" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="53">
       <c r="B53" s="0" t="n">
@@ -3932,6 +4095,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=11</t>
         </is>
       </c>
+      <c r="Q53" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="54">
       <c r="B54" s="0" t="n">
@@ -3983,6 +4149,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=11</t>
         </is>
       </c>
+      <c r="Q54" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="55">
       <c r="B55" s="0" t="n">
@@ -4034,6 +4203,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=12</t>
         </is>
       </c>
+      <c r="Q55" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="56">
       <c r="B56" s="0" t="n">
@@ -4085,6 +4257,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=12</t>
         </is>
       </c>
+      <c r="Q56" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="57">
       <c r="B57" s="0" t="n">
@@ -4136,6 +4311,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=12</t>
         </is>
       </c>
+      <c r="Q57" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="58">
       <c r="B58" s="0" t="n">
@@ -4187,6 +4365,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=12</t>
         </is>
       </c>
+      <c r="Q58" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="59">
       <c r="B59" s="0" t="n">
@@ -4238,6 +4419,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=12</t>
         </is>
       </c>
+      <c r="Q59" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="60">
       <c r="B60" s="0" t="n">
@@ -4289,6 +4473,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=12</t>
         </is>
       </c>
+      <c r="Q60" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="61">
       <c r="B61" s="0" t="n">
@@ -4340,6 +4527,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=12</t>
         </is>
       </c>
+      <c r="Q61" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="62">
       <c r="B62" s="0" t="n">
@@ -4391,6 +4581,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=12</t>
         </is>
       </c>
+      <c r="Q62" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="63">
       <c r="B63" s="0" t="n">
@@ -4442,6 +4635,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=12</t>
         </is>
       </c>
+      <c r="Q63" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="64">
       <c r="B64" s="0" t="n">
@@ -4493,6 +4689,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=13</t>
         </is>
       </c>
+      <c r="Q64" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="65">
       <c r="B65" s="0" t="n">
@@ -4544,6 +4743,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=13</t>
         </is>
       </c>
+      <c r="Q65" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="66">
       <c r="B66" s="0" t="n">
@@ -4595,6 +4797,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=13</t>
         </is>
       </c>
+      <c r="Q66" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="67">
       <c r="B67" s="0" t="n">
@@ -4646,6 +4851,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=13</t>
         </is>
       </c>
+      <c r="Q67" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="68">
       <c r="B68" s="0" t="n">
@@ -4697,6 +4905,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=13</t>
         </is>
       </c>
+      <c r="Q68" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="69">
       <c r="B69" s="0" t="n">
@@ -4748,6 +4959,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=13</t>
         </is>
       </c>
+      <c r="Q69" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="70">
       <c r="B70" s="0" t="n">
@@ -4799,6 +5013,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=13</t>
         </is>
       </c>
+      <c r="Q70" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="71">
       <c r="B71" s="0" t="n">
@@ -4850,6 +5067,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=13</t>
         </is>
       </c>
+      <c r="Q71" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="72">
       <c r="B72" s="0" t="n">
@@ -4901,6 +5121,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=13</t>
         </is>
       </c>
+      <c r="Q72" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="73">
       <c r="B73" s="0" t="n">
@@ -4952,6 +5175,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=14</t>
         </is>
       </c>
+      <c r="Q73" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="74">
       <c r="B74" s="0" t="n">
@@ -5003,6 +5229,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=14</t>
         </is>
       </c>
+      <c r="Q74" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="75">
       <c r="B75" s="0" t="n">
@@ -5054,6 +5283,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=14</t>
         </is>
       </c>
+      <c r="Q75" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="76">
       <c r="B76" s="0" t="n">
@@ -5105,6 +5337,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=14</t>
         </is>
       </c>
+      <c r="Q76" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="77">
       <c r="B77" s="0" t="n">
@@ -5156,6 +5391,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=14</t>
         </is>
       </c>
+      <c r="Q77" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="78">
       <c r="B78" s="0" t="n">
@@ -5207,6 +5445,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=14</t>
         </is>
       </c>
+      <c r="Q78" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="79">
       <c r="B79" s="0" t="n">
@@ -5258,6 +5499,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=14</t>
         </is>
       </c>
+      <c r="Q79" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="80">
       <c r="B80" s="0" t="n">
@@ -5309,6 +5553,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=14</t>
         </is>
       </c>
+      <c r="Q80" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="81">
       <c r="B81" s="0" t="n">
@@ -5360,6 +5607,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=14</t>
         </is>
       </c>
+      <c r="Q81" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="82">
       <c r="B82" s="0" t="n">
@@ -5411,6 +5661,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=15</t>
         </is>
       </c>
+      <c r="Q82" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="83">
       <c r="B83" s="0" t="n">
@@ -5462,6 +5715,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=15</t>
         </is>
       </c>
+      <c r="Q83" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="84">
       <c r="B84" s="0" t="n">
@@ -5513,6 +5769,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=15</t>
         </is>
       </c>
+      <c r="Q84" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="85">
       <c r="B85" s="0" t="n">
@@ -5564,6 +5823,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=15</t>
         </is>
       </c>
+      <c r="Q85" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="86">
       <c r="B86" s="0" t="n">
@@ -5615,6 +5877,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=15</t>
         </is>
       </c>
+      <c r="Q86" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="87">
       <c r="B87" s="0" t="n">
@@ -5666,6 +5931,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=15</t>
         </is>
       </c>
+      <c r="Q87" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="88">
       <c r="B88" s="0" t="n">
@@ -5717,6 +5985,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=15</t>
         </is>
       </c>
+      <c r="Q88" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="89">
       <c r="B89" s="0" t="n">
@@ -5768,6 +6039,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=15</t>
         </is>
       </c>
+      <c r="Q89" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="90">
       <c r="B90" s="0" t="n">
@@ -5819,6 +6093,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=2; wave=15</t>
         </is>
       </c>
+      <c r="Q90" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="91">
       <c r="B91" s="0" t="n">
@@ -5870,6 +6147,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=15</t>
         </is>
       </c>
+      <c r="Q91" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="92">
       <c r="B92" s="0" t="n">
@@ -5921,6 +6201,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=16</t>
         </is>
       </c>
+      <c r="Q92" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="93">
       <c r="B93" s="0" t="n">
@@ -5972,6 +6255,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=16</t>
         </is>
       </c>
+      <c r="Q93" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="94">
       <c r="B94" s="0" t="n">
@@ -6023,6 +6309,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=16</t>
         </is>
       </c>
+      <c r="Q94" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="95">
       <c r="B95" s="0" t="n">
@@ -6074,6 +6363,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=16</t>
         </is>
       </c>
+      <c r="Q95" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="96">
       <c r="B96" s="0" t="n">
@@ -6125,6 +6417,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=16</t>
         </is>
       </c>
+      <c r="Q96" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="97">
       <c r="B97" s="0" t="n">
@@ -6176,6 +6471,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=16</t>
         </is>
       </c>
+      <c r="Q97" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="98">
       <c r="B98" s="0" t="n">
@@ -6227,6 +6525,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=2; wave=16</t>
         </is>
       </c>
+      <c r="Q98" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="99">
       <c r="B99" s="0" t="n">
@@ -6278,6 +6579,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=16</t>
         </is>
       </c>
+      <c r="Q99" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="100">
       <c r="B100" s="0" t="n">
@@ -6329,6 +6633,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=17</t>
         </is>
       </c>
+      <c r="Q100" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="101">
       <c r="B101" s="0" t="n">
@@ -6380,6 +6687,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=17</t>
         </is>
       </c>
+      <c r="Q101" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="102">
       <c r="B102" s="0" t="n">
@@ -6431,6 +6741,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=17</t>
         </is>
       </c>
+      <c r="Q102" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="103">
       <c r="B103" s="0" t="n">
@@ -6482,6 +6795,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=17</t>
         </is>
       </c>
+      <c r="Q103" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="104">
       <c r="B104" s="0" t="n">
@@ -6533,6 +6849,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=17</t>
         </is>
       </c>
+      <c r="Q104" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="105">
       <c r="B105" s="0" t="n">
@@ -6584,6 +6903,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=17</t>
         </is>
       </c>
+      <c r="Q105" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="106">
       <c r="B106" s="0" t="n">
@@ -6635,6 +6957,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=17</t>
         </is>
       </c>
+      <c r="Q106" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="107">
       <c r="B107" s="0" t="n">
@@ -6686,6 +7011,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=17</t>
         </is>
       </c>
+      <c r="Q107" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="108">
       <c r="B108" s="0" t="n">
@@ -6737,6 +7065,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=17</t>
         </is>
       </c>
+      <c r="Q108" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="109">
       <c r="B109" s="0" t="n">
@@ -6788,6 +7119,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=2; wave=17</t>
         </is>
       </c>
+      <c r="Q109" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="110">
       <c r="B110" s="0" t="n">
@@ -6839,6 +7173,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=17</t>
         </is>
       </c>
+      <c r="Q110" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="111">
       <c r="B111" s="0" t="n">
@@ -6890,6 +7227,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=18</t>
         </is>
       </c>
+      <c r="Q111" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="112">
       <c r="B112" s="0" t="n">
@@ -6941,6 +7281,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=18</t>
         </is>
       </c>
+      <c r="Q112" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="113">
       <c r="B113" s="0" t="n">
@@ -6992,6 +7335,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=18</t>
         </is>
       </c>
+      <c r="Q113" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="114">
       <c r="B114" s="0" t="n">
@@ -7043,6 +7389,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=18</t>
         </is>
       </c>
+      <c r="Q114" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="115">
       <c r="B115" s="0" t="n">
@@ -7094,6 +7443,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=18</t>
         </is>
       </c>
+      <c r="Q115" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="116">
       <c r="B116" s="0" t="n">
@@ -7145,6 +7497,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=18</t>
         </is>
       </c>
+      <c r="Q116" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="117">
       <c r="B117" s="0" t="n">
@@ -7196,6 +7551,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=18</t>
         </is>
       </c>
+      <c r="Q117" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="118">
       <c r="B118" s="0" t="n">
@@ -7247,6 +7605,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=18</t>
         </is>
       </c>
+      <c r="Q118" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="119">
       <c r="B119" s="0" t="n">
@@ -7298,6 +7659,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=18</t>
         </is>
       </c>
+      <c r="Q119" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="120">
       <c r="B120" s="0" t="n">
@@ -7349,6 +7713,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=2; wave=18</t>
         </is>
       </c>
+      <c r="Q120" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="121">
       <c r="B121" s="0" t="n">
@@ -7400,6 +7767,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=18</t>
         </is>
       </c>
+      <c r="Q121" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="122">
       <c r="B122" s="0" t="n">
@@ -7451,6 +7821,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=19</t>
         </is>
       </c>
+      <c r="Q122" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="123">
       <c r="B123" s="0" t="n">
@@ -7502,6 +7875,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=19</t>
         </is>
       </c>
+      <c r="Q123" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="124">
       <c r="B124" s="0" t="n">
@@ -7553,6 +7929,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=19</t>
         </is>
       </c>
+      <c r="Q124" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="125">
       <c r="B125" s="0" t="n">
@@ -7604,6 +7983,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=19</t>
         </is>
       </c>
+      <c r="Q125" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="126">
       <c r="B126" s="0" t="n">
@@ -7655,6 +8037,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=19</t>
         </is>
       </c>
+      <c r="Q126" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="127">
       <c r="B127" s="0" t="n">
@@ -7706,6 +8091,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=19</t>
         </is>
       </c>
+      <c r="Q127" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="128">
       <c r="B128" s="0" t="n">
@@ -7757,6 +8145,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=19</t>
         </is>
       </c>
+      <c r="Q128" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="129">
       <c r="B129" s="0" t="n">
@@ -7808,6 +8199,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=19</t>
         </is>
       </c>
+      <c r="Q129" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="130">
       <c r="B130" s="0" t="n">
@@ -7859,6 +8253,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=19</t>
         </is>
       </c>
+      <c r="Q130" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="131">
       <c r="B131" s="0" t="n">
@@ -7910,6 +8307,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=2; wave=19</t>
         </is>
       </c>
+      <c r="Q131" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="132">
       <c r="B132" s="0" t="n">
@@ -7961,6 +8361,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=19</t>
         </is>
       </c>
+      <c r="Q132" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="133">
       <c r="B133" s="0" t="n">
@@ -8012,6 +8415,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=20</t>
         </is>
       </c>
+      <c r="Q133" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="134">
       <c r="B134" s="0" t="n">
@@ -8063,6 +8469,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=20</t>
         </is>
       </c>
+      <c r="Q134" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="135">
       <c r="B135" s="0" t="n">
@@ -8114,6 +8523,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=20</t>
         </is>
       </c>
+      <c r="Q135" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="136">
       <c r="B136" s="0" t="n">
@@ -8165,6 +8577,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=20</t>
         </is>
       </c>
+      <c r="Q136" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="137">
       <c r="B137" s="0" t="n">
@@ -8216,6 +8631,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=20</t>
         </is>
       </c>
+      <c r="Q137" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="138">
       <c r="B138" s="0" t="n">
@@ -8267,6 +8685,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=20</t>
         </is>
       </c>
+      <c r="Q138" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="139">
       <c r="B139" s="0" t="n">
@@ -8318,6 +8739,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=20</t>
         </is>
       </c>
+      <c r="Q139" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="140">
       <c r="B140" s="0" t="n">
@@ -8369,6 +8793,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=20</t>
         </is>
       </c>
+      <c r="Q140" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="141">
       <c r="B141" s="0" t="n">
@@ -8420,6 +8847,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=20</t>
         </is>
       </c>
+      <c r="Q141" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="142">
       <c r="B142" s="0" t="n">
@@ -8471,6 +8901,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=2; wave=20</t>
         </is>
       </c>
+      <c r="Q142" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="143">
       <c r="B143" s="0" t="n">
@@ -8522,6 +8955,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=20</t>
         </is>
       </c>
+      <c r="Q143" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="144">
       <c r="B144" s="0" t="n">
@@ -8573,6 +9009,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=5</t>
         </is>
       </c>
+      <c r="Q144" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="145">
       <c r="B145" s="0" t="n">
@@ -8624,6 +9063,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=6</t>
         </is>
       </c>
+      <c r="Q145" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="146">
       <c r="B146" s="0" t="n">
@@ -8675,6 +9117,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=7</t>
         </is>
       </c>
+      <c r="Q146" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="147">
       <c r="B147" s="0" t="n">
@@ -8726,6 +9171,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=8</t>
         </is>
       </c>
+      <c r="Q147" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="148">
       <c r="B148" s="0" t="n">
@@ -8777,6 +9225,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=9</t>
         </is>
       </c>
+      <c r="Q148" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="149">
       <c r="B149" s="0" t="n">
@@ -8828,6 +9279,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=10</t>
         </is>
       </c>
+      <c r="Q149" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="150">
       <c r="B150" s="0" t="n">
@@ -8879,6 +9333,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=12</t>
         </is>
       </c>
+      <c r="Q150" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="151">
       <c r="B151" s="0" t="n">
@@ -8930,6 +9387,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=13</t>
         </is>
       </c>
+      <c r="Q151" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="152">
       <c r="B152" s="0" t="n">
@@ -8981,6 +9441,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=14</t>
         </is>
       </c>
+      <c r="Q152" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="153">
       <c r="B153" s="0" t="n">
@@ -9032,6 +9495,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=15</t>
         </is>
       </c>
+      <c r="Q153" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="154">
       <c r="B154" s="0" t="n">
@@ -9083,6 +9549,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=21</t>
         </is>
       </c>
+      <c r="Q154" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="155">
       <c r="B155" s="0" t="n">
@@ -9134,6 +9603,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=21</t>
         </is>
       </c>
+      <c r="Q155" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="156">
       <c r="B156" s="0" t="n">
@@ -9185,6 +9657,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=21</t>
         </is>
       </c>
+      <c r="Q156" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="157">
       <c r="B157" s="0" t="n">
@@ -9236,6 +9711,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=21</t>
         </is>
       </c>
+      <c r="Q157" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="158">
       <c r="B158" s="0" t="n">
@@ -9287,6 +9765,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=21</t>
         </is>
       </c>
+      <c r="Q158" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="159">
       <c r="B159" s="0" t="n">
@@ -9338,6 +9819,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=21</t>
         </is>
       </c>
+      <c r="Q159" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="160">
       <c r="B160" s="0" t="n">
@@ -9389,6 +9873,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=21</t>
         </is>
       </c>
+      <c r="Q160" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="161">
       <c r="B161" s="0" t="n">
@@ -9440,6 +9927,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=21</t>
         </is>
       </c>
+      <c r="Q161" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="162">
       <c r="B162" s="0" t="n">
@@ -9491,6 +9981,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=21</t>
         </is>
       </c>
+      <c r="Q162" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="163">
       <c r="B163" s="0" t="n">
@@ -9542,6 +10035,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=2; wave=21</t>
         </is>
       </c>
+      <c r="Q163" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="164">
       <c r="B164" s="0" t="n">
@@ -9593,6 +10089,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=21</t>
         </is>
       </c>
+      <c r="Q164" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="165">
       <c r="B165" s="0" t="n">
@@ -9644,6 +10143,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=22</t>
         </is>
       </c>
+      <c r="Q165" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="166">
       <c r="B166" s="0" t="n">
@@ -9695,6 +10197,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=22</t>
         </is>
       </c>
+      <c r="Q166" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="167">
       <c r="B167" s="0" t="n">
@@ -9746,6 +10251,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=22</t>
         </is>
       </c>
+      <c r="Q167" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="168">
       <c r="B168" s="0" t="n">
@@ -9797,6 +10305,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=22</t>
         </is>
       </c>
+      <c r="Q168" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="169">
       <c r="B169" s="0" t="n">
@@ -9848,6 +10359,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=22</t>
         </is>
       </c>
+      <c r="Q169" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="170">
       <c r="B170" s="0" t="n">
@@ -9899,6 +10413,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=22</t>
         </is>
       </c>
+      <c r="Q170" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="171">
       <c r="B171" s="0" t="n">
@@ -9950,6 +10467,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=22</t>
         </is>
       </c>
+      <c r="Q171" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="172">
       <c r="B172" s="0" t="n">
@@ -10001,6 +10521,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=22</t>
         </is>
       </c>
+      <c r="Q172" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="173">
       <c r="B173" s="0" t="n">
@@ -10052,6 +10575,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=22</t>
         </is>
       </c>
+      <c r="Q173" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="174">
       <c r="B174" s="0" t="n">
@@ -10103,6 +10629,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=2; wave=22</t>
         </is>
       </c>
+      <c r="Q174" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="175">
       <c r="B175" s="0" t="n">
@@ -10154,6 +10683,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=22</t>
         </is>
       </c>
+      <c r="Q175" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="176">
       <c r="B176" s="0" t="n">
@@ -10205,6 +10737,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=23</t>
         </is>
       </c>
+      <c r="Q176" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="177">
       <c r="B177" s="0" t="n">
@@ -10256,6 +10791,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=23</t>
         </is>
       </c>
+      <c r="Q177" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="178">
       <c r="B178" s="0" t="n">
@@ -10307,6 +10845,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=23</t>
         </is>
       </c>
+      <c r="Q178" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="179">
       <c r="B179" s="0" t="n">
@@ -10358,6 +10899,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=23</t>
         </is>
       </c>
+      <c r="Q179" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="180">
       <c r="B180" s="0" t="n">
@@ -10409,6 +10953,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=23</t>
         </is>
       </c>
+      <c r="Q180" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="181">
       <c r="B181" s="0" t="n">
@@ -10460,6 +11007,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=23</t>
         </is>
       </c>
+      <c r="Q181" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="182">
       <c r="B182" s="0" t="n">
@@ -10511,6 +11061,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=23</t>
         </is>
       </c>
+      <c r="Q182" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="183">
       <c r="B183" s="0" t="n">
@@ -10562,6 +11115,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=23</t>
         </is>
       </c>
+      <c r="Q183" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="184">
       <c r="B184" s="0" t="n">
@@ -10613,6 +11169,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=23</t>
         </is>
       </c>
+      <c r="Q184" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="185">
       <c r="B185" s="0" t="n">
@@ -10664,6 +11223,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=2; wave=23</t>
         </is>
       </c>
+      <c r="Q185" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="186">
       <c r="B186" s="0" t="n">
@@ -10715,6 +11277,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=23</t>
         </is>
       </c>
+      <c r="Q186" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="187">
       <c r="B187" s="0" t="n">
@@ -10766,6 +11331,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=24</t>
         </is>
       </c>
+      <c r="Q187" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="188">
       <c r="B188" s="0" t="n">
@@ -10817,6 +11385,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=24</t>
         </is>
       </c>
+      <c r="Q188" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="189">
       <c r="B189" s="0" t="n">
@@ -10868,6 +11439,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=24</t>
         </is>
       </c>
+      <c r="Q189" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="190">
       <c r="B190" s="0" t="n">
@@ -10919,6 +11493,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=24</t>
         </is>
       </c>
+      <c r="Q190" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="191">
       <c r="B191" s="0" t="n">
@@ -10970,6 +11547,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=24</t>
         </is>
       </c>
+      <c r="Q191" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="192">
       <c r="B192" s="0" t="n">
@@ -11021,6 +11601,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=24</t>
         </is>
       </c>
+      <c r="Q192" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="193">
       <c r="B193" s="0" t="n">
@@ -11072,6 +11655,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=24</t>
         </is>
       </c>
+      <c r="Q193" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="194">
       <c r="B194" s="0" t="n">
@@ -11123,6 +11709,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=24</t>
         </is>
       </c>
+      <c r="Q194" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="195">
       <c r="B195" s="0" t="n">
@@ -11174,6 +11763,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=24</t>
         </is>
       </c>
+      <c r="Q195" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="196">
       <c r="B196" s="0" t="n">
@@ -11225,6 +11817,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=2; wave=24</t>
         </is>
       </c>
+      <c r="Q196" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="197">
       <c r="B197" s="0" t="n">
@@ -11276,6 +11871,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=24</t>
         </is>
       </c>
+      <c r="Q197" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="198">
       <c r="B198" s="0" t="n">
@@ -11327,6 +11925,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=25</t>
         </is>
       </c>
+      <c r="Q198" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="199">
       <c r="B199" s="0" t="n">
@@ -11378,6 +11979,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=25</t>
         </is>
       </c>
+      <c r="Q199" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="200">
       <c r="B200" s="0" t="n">
@@ -11429,6 +12033,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=25</t>
         </is>
       </c>
+      <c r="Q200" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="201">
       <c r="B201" s="0" t="n">
@@ -11480,6 +12087,9 @@
           <t>Balance variant; canonical=17; role=normal; profile=D04; level=2; wave=25</t>
         </is>
       </c>
+      <c r="Q201" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="202">
       <c r="B202" s="0" t="n">
@@ -11531,6 +12141,9 @@
           <t>Balance variant; canonical=18; role=normal; profile=D04; level=2; wave=25</t>
         </is>
       </c>
+      <c r="Q202" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="203">
       <c r="B203" s="0" t="n">
@@ -11582,6 +12195,9 @@
           <t>Balance variant; canonical=30; role=fast; profile=D04; level=2; wave=25</t>
         </is>
       </c>
+      <c r="Q203" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="204">
       <c r="B204" s="0" t="n">
@@ -11633,6 +12249,9 @@
           <t>Balance variant; canonical=83; role=medium; profile=D04; level=2; wave=25</t>
         </is>
       </c>
+      <c r="Q204" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="205">
       <c r="B205" s="0" t="n">
@@ -11684,6 +12303,9 @@
           <t>Balance variant; canonical=84; role=swarm; profile=D04; level=2; wave=25</t>
         </is>
       </c>
+      <c r="Q205" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="206">
       <c r="B206" s="0" t="n">
@@ -11735,6 +12357,9 @@
           <t>Balance variant; canonical=88; role=heavy; profile=D04; level=2; wave=25</t>
         </is>
       </c>
+      <c r="Q206" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="207">
       <c r="B207" s="0" t="n">
@@ -11786,6 +12411,9 @@
           <t>Balance variant; canonical=108; role=medium; profile=D04; level=2; wave=25</t>
         </is>
       </c>
+      <c r="Q207" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="208">
       <c r="B208" s="0" t="n">
@@ -11837,6 +12465,9 @@
           <t>Balance variant; canonical=123; role=elite; profile=D04; level=2; wave=25</t>
         </is>
       </c>
+      <c r="Q208" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="209">
       <c r="B209" s="0" t="n">
@@ -11888,6 +12519,9 @@
           <t>Balance variant; canonical=123; role=medium; profile=D04; level=2; wave=25</t>
         </is>
       </c>
+      <c r="Q209" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="210">
       <c r="B210" s="0" t="n">
@@ -11939,6 +12573,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=10</t>
         </is>
       </c>
+      <c r="Q210" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="211">
       <c r="B211" s="0" t="n">
@@ -11990,6 +12627,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=6</t>
         </is>
       </c>
+      <c r="Q211" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="212">
       <c r="B212" s="0" t="n">
@@ -12041,6 +12681,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=7</t>
         </is>
       </c>
+      <c r="Q212" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="213">
       <c r="B213" s="0" t="n">
@@ -12092,6 +12735,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=8</t>
         </is>
       </c>
+      <c r="Q213" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="214">
       <c r="B214" s="0" t="n">
@@ -12143,6 +12789,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=9</t>
         </is>
       </c>
+      <c r="Q214" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="215">
       <c r="B215" s="0" t="n">
@@ -12194,6 +12843,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=3</t>
         </is>
       </c>
+      <c r="Q215" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="216">
       <c r="B216" s="0" t="n">
@@ -12245,6 +12897,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=3</t>
         </is>
       </c>
+      <c r="Q216" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="217">
       <c r="B217" s="0" t="n">
@@ -12296,6 +12951,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=3</t>
         </is>
       </c>
+      <c r="Q217" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="218">
       <c r="B218" s="0" t="n">
@@ -12347,6 +13005,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=3</t>
         </is>
       </c>
+      <c r="Q218" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="219">
       <c r="B219" s="0" t="n">
@@ -12398,6 +13059,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=3</t>
         </is>
       </c>
+      <c r="Q219" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="220">
       <c r="B220" s="0" t="n">
@@ -12449,6 +13113,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=4</t>
         </is>
       </c>
+      <c r="Q220" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="221">
       <c r="B221" s="0" t="n">
@@ -12500,6 +13167,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=4</t>
         </is>
       </c>
+      <c r="Q221" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="222">
       <c r="B222" s="0" t="n">
@@ -12551,6 +13221,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=4</t>
         </is>
       </c>
+      <c r="Q222" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="223">
       <c r="B223" s="0" t="n">
@@ -12602,6 +13275,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=4</t>
         </is>
       </c>
+      <c r="Q223" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="224">
       <c r="B224" s="0" t="n">
@@ -12653,6 +13329,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=4</t>
         </is>
       </c>
+      <c r="Q224" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="225">
       <c r="B225" s="0" t="n">
@@ -12704,6 +13383,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=5</t>
         </is>
       </c>
+      <c r="Q225" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="226">
       <c r="B226" s="0" t="n">
@@ -12755,6 +13437,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=5</t>
         </is>
       </c>
+      <c r="Q226" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="227">
       <c r="B227" s="0" t="n">
@@ -12806,6 +13491,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=5</t>
         </is>
       </c>
+      <c r="Q227" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="228">
       <c r="B228" s="0" t="n">
@@ -12857,6 +13545,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=5</t>
         </is>
       </c>
+      <c r="Q228" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="229">
       <c r="B229" s="0" t="n">
@@ -12908,6 +13599,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=5</t>
         </is>
       </c>
+      <c r="Q229" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="230">
       <c r="B230" s="0" t="n">
@@ -12959,6 +13653,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=6</t>
         </is>
       </c>
+      <c r="Q230" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="231">
       <c r="B231" s="0" t="n">
@@ -13010,6 +13707,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=6</t>
         </is>
       </c>
+      <c r="Q231" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="232">
       <c r="B232" s="0" t="n">
@@ -13061,6 +13761,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=7</t>
         </is>
       </c>
+      <c r="Q232" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="233">
       <c r="B233" s="0" t="n">
@@ -13112,6 +13815,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=7</t>
         </is>
       </c>
+      <c r="Q233" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="234">
       <c r="B234" s="0" t="n">
@@ -13163,6 +13869,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=8</t>
         </is>
       </c>
+      <c r="Q234" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="235">
       <c r="B235" s="0" t="n">
@@ -13214,6 +13923,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=8</t>
         </is>
       </c>
+      <c r="Q235" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="236">
       <c r="B236" s="0" t="n">
@@ -13265,6 +13977,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=9</t>
         </is>
       </c>
+      <c r="Q236" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="237">
       <c r="B237" s="0" t="n">
@@ -13316,6 +14031,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=9</t>
         </is>
       </c>
+      <c r="Q237" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="238">
       <c r="B238" s="0" t="n">
@@ -13367,6 +14085,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=10</t>
         </is>
       </c>
+      <c r="Q238" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="239">
       <c r="B239" s="0" t="n">
@@ -13418,6 +14139,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=10</t>
         </is>
       </c>
+      <c r="Q239" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="240">
       <c r="B240" s="0" t="n">
@@ -13469,6 +14193,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=11</t>
         </is>
       </c>
+      <c r="Q240" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="241">
       <c r="B241" s="0" t="n">
@@ -13520,6 +14247,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=11</t>
         </is>
       </c>
+      <c r="Q241" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="242">
       <c r="B242" s="0" t="n">
@@ -13571,6 +14301,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=11</t>
         </is>
       </c>
+      <c r="Q242" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="243">
       <c r="B243" s="0" t="n">
@@ -13622,6 +14355,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=11</t>
         </is>
       </c>
+      <c r="Q243" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="244">
       <c r="B244" s="0" t="n">
@@ -13673,6 +14409,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=11</t>
         </is>
       </c>
+      <c r="Q244" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="245">
       <c r="B245" s="0" t="n">
@@ -13724,6 +14463,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=12</t>
         </is>
       </c>
+      <c r="Q245" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="246">
       <c r="B246" s="0" t="n">
@@ -13775,6 +14517,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=12</t>
         </is>
       </c>
+      <c r="Q246" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="247">
       <c r="B247" s="0" t="n">
@@ -13826,6 +14571,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=13</t>
         </is>
       </c>
+      <c r="Q247" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="248">
       <c r="B248" s="0" t="n">
@@ -13877,6 +14625,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=13</t>
         </is>
       </c>
+      <c r="Q248" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="249">
       <c r="B249" s="0" t="n">
@@ -13928,6 +14679,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=14</t>
         </is>
       </c>
+      <c r="Q249" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="250">
       <c r="B250" s="0" t="n">
@@ -13979,6 +14733,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=14</t>
         </is>
       </c>
+      <c r="Q250" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="251">
       <c r="B251" s="0" t="n">
@@ -14030,6 +14787,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=15</t>
         </is>
       </c>
+      <c r="Q251" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="252">
       <c r="B252" s="0" t="n">
@@ -14081,6 +14841,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=15</t>
         </is>
       </c>
+      <c r="Q252" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="253">
       <c r="B253" s="0" t="n">
@@ -14132,6 +14895,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=16</t>
         </is>
       </c>
+      <c r="Q253" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="254">
       <c r="B254" s="0" t="n">
@@ -14183,6 +14949,9 @@
           <t>Balance variant; canonical=11; role=air; profile=D04; level=2; wave=16</t>
         </is>
       </c>
+      <c r="Q254" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="255">
       <c r="B255" s="0" t="n">
@@ -14234,6 +15003,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=16</t>
         </is>
       </c>
+      <c r="Q255" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="256">
       <c r="B256" s="0" t="n">
@@ -14285,6 +15057,9 @@
           <t>Balance variant; canonical=13; role=air; profile=D04; level=2; wave=16</t>
         </is>
       </c>
+      <c r="Q256" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="257">
       <c r="B257" s="0" t="n">
@@ -14336,6 +15111,9 @@
           <t>Balance variant; canonical=14; role=air; profile=D04; level=2; wave=16</t>
         </is>
       </c>
+      <c r="Q257" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="258">
       <c r="B258" s="0" t="n">
@@ -14387,6 +15165,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=17</t>
         </is>
       </c>
+      <c r="Q258" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="259">
       <c r="B259" s="0" t="n">
@@ -14438,6 +15219,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=17</t>
         </is>
       </c>
+      <c r="Q259" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="260">
       <c r="B260" s="0" t="n">
@@ -14489,6 +15273,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=18</t>
         </is>
       </c>
+      <c r="Q260" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="261">
       <c r="B261" s="0" t="n">
@@ -14540,6 +15327,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=18</t>
         </is>
       </c>
+      <c r="Q261" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="262">
       <c r="B262" s="0" t="n">
@@ -14591,6 +15381,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=19</t>
         </is>
       </c>
+      <c r="Q262" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="263">
       <c r="B263" s="0" t="n">
@@ -14642,6 +15435,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=19</t>
         </is>
       </c>
+      <c r="Q263" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="264">
       <c r="B264" s="0" t="n">
@@ -14693,6 +15489,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=20</t>
         </is>
       </c>
+      <c r="Q264" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="265">
       <c r="B265" s="0" t="n">
@@ -14744,6 +15543,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=20</t>
         </is>
       </c>
+      <c r="Q265" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="266">
       <c r="B266" s="0" t="n">
@@ -14795,6 +15597,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=21</t>
         </is>
       </c>
+      <c r="Q266" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="267">
       <c r="B267" s="0" t="n">
@@ -14846,6 +15651,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=21</t>
         </is>
       </c>
+      <c r="Q267" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="268">
       <c r="B268" s="0" t="n">
@@ -14897,6 +15705,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=22</t>
         </is>
       </c>
+      <c r="Q268" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="269">
       <c r="B269" s="0" t="n">
@@ -14948,6 +15759,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=22</t>
         </is>
       </c>
+      <c r="Q269" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="270">
       <c r="B270" s="0" t="n">
@@ -14999,6 +15813,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=23</t>
         </is>
       </c>
+      <c r="Q270" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="271">
       <c r="B271" s="0" t="n">
@@ -15050,6 +15867,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=23</t>
         </is>
       </c>
+      <c r="Q271" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="272">
       <c r="B272" s="0" t="n">
@@ -15101,6 +15921,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=24</t>
         </is>
       </c>
+      <c r="Q272" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="273">
       <c r="B273" s="0" t="n">
@@ -15152,6 +15975,9 @@
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=24</t>
         </is>
       </c>
+      <c r="Q273" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="274">
       <c r="B274" s="0" t="n">
@@ -15203,6 +16029,9 @@
           <t>Balance variant; canonical=2; role=air; profile=D04; level=2; wave=25</t>
         </is>
       </c>
+      <c r="Q274" s="0" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="275">
       <c r="B275" s="0" t="n">
@@ -15253,6 +16082,9 @@
         <is>
           <t>Balance variant; canonical=12; role=air; profile=D04; level=2; wave=25</t>
         </is>
+      </c>
+      <c r="Q275" s="0" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/Config/Datas/Levels/L02/EnemyData.xlsx
+++ b/Luban/Config/Datas/Levels/L02/EnemyData.xlsx
@@ -1407,7 +1407,7 @@
         <v>1.1</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>8.5</v>
+        <v>19.504763</v>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>2</v>
+        <v>4.428571</v>
       </c>
       <c r="K4" s="0" t="n">
         <v>1</v>
@@ -1461,7 +1461,7 @@
         <v>1.1</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>8.5</v>
+        <v>19.504763</v>
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>2</v>
+        <v>4.428571</v>
       </c>
       <c r="K5" s="0" t="n">
         <v>1</v>
@@ -1515,7 +1515,7 @@
         <v>1.1</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>9.5</v>
+        <v>19.692308</v>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>2</v>
+        <v>4.269231</v>
       </c>
       <c r="K6" s="0" t="n">
         <v>1</v>
@@ -1569,7 +1569,7 @@
         <v>1.1</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>9.5</v>
+        <v>19.692308</v>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>2</v>
+        <v>4.269231</v>
       </c>
       <c r="K7" s="0" t="n">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>1.10495</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>12</v>
+        <v>28.288001</v>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>2</v>
+        <v>4.44</v>
       </c>
       <c r="K8" s="0" t="n">
         <v>1</v>
@@ -1677,7 +1677,7 @@
         <v>1.10495</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>12</v>
+        <v>28.288001</v>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>2</v>
+        <v>4.44</v>
       </c>
       <c r="K9" s="0" t="n">
         <v>1</v>
@@ -1731,7 +1731,7 @@
         <v>1.054725</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>7</v>
+        <v>16.501333</v>
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>1</v>
+        <v>2.59</v>
       </c>
       <c r="K10" s="0" t="n">
         <v>1</v>
@@ -1785,7 +1785,7 @@
         <v>1.1066</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>13.5</v>
+        <v>31.745454</v>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>2</v>
+        <v>4.295454</v>
       </c>
       <c r="K11" s="0" t="n">
         <v>1</v>
@@ -1839,7 +1839,7 @@
         <v>1.1066</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>13.5</v>
+        <v>31.745454</v>
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>2</v>
+        <v>4.295454</v>
       </c>
       <c r="K12" s="0" t="n">
         <v>1</v>
@@ -1893,7 +1893,7 @@
         <v>1.0563</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>9</v>
+        <v>21.163638</v>
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>1</v>
+        <v>2.863637</v>
       </c>
       <c r="K13" s="0" t="n">
         <v>1</v>
@@ -1947,7 +1947,7 @@
         <v>1.10825</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>21.570313</v>
+        <v>279.513651</v>
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>2</v>
+        <v>0.5087699999999999</v>
       </c>
       <c r="K14" s="0" t="n">
         <v>1</v>
@@ -2001,7 +2001,7 @@
         <v>1.10825</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>21.570313</v>
+        <v>279.513651</v>
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>2</v>
+        <v>0.5087699999999999</v>
       </c>
       <c r="K15" s="0" t="n">
         <v>1</v>
@@ -2055,7 +2055,7 @@
         <v>1.057875</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>14.020703</v>
+        <v>181.683876</v>
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>1</v>
+        <v>0.330701</v>
       </c>
       <c r="K16" s="0" t="n">
         <v>1</v>
@@ -2109,7 +2109,7 @@
         <v>1.0075</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>33.735969</v>
+        <v>437.159392</v>
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>0.08</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>2</v>
+        <v>0.795717</v>
       </c>
       <c r="K17" s="0" t="n">
         <v>1</v>
@@ -2217,7 +2217,7 @@
         <v>1.1099</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>19.757537</v>
+        <v>288.491556</v>
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>2</v>
+        <v>0.518087</v>
       </c>
       <c r="K19" s="0" t="n">
         <v>1</v>
@@ -2271,7 +2271,7 @@
         <v>1.1099</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>19.757537</v>
+        <v>288.491556</v>
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="0" t="n">
-        <v>2</v>
+        <v>0.518087</v>
       </c>
       <c r="K20" s="0" t="n">
         <v>1</v>
@@ -2325,7 +2325,7 @@
         <v>1.009</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>30.900788</v>
+        <v>451.200734</v>
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>0.08</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>2</v>
+        <v>0.810288</v>
       </c>
       <c r="K21" s="0" t="n">
         <v>1</v>
@@ -2379,7 +2379,7 @@
         <v>1.05945</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>12.842399</v>
+        <v>187.519485</v>
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>1</v>
+        <v>0.336757</v>
       </c>
       <c r="K22" s="0" t="n">
         <v>1</v>
@@ -2433,7 +2433,7 @@
         <v>1.009</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>30.900788</v>
+        <v>451.200734</v>
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>0.08</v>
       </c>
       <c r="J23" s="0" t="n">
-        <v>2</v>
+        <v>0.810288</v>
       </c>
       <c r="K23" s="0" t="n">
         <v>1</v>
@@ -2487,7 +2487,7 @@
         <v>1.12</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>16</v>
+        <v>154.175902</v>
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="0" t="n">
-        <v>1</v>
+        <v>0.343035</v>
       </c>
       <c r="K24" s="0" t="n">
         <v>1</v>
@@ -2541,7 +2541,7 @@
         <v>1.11155</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>21.017511</v>
+        <v>303.7869</v>
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="0" t="n">
-        <v>2</v>
+        <v>0.5182</v>
       </c>
       <c r="K25" s="0" t="n">
         <v>1</v>
@@ -2595,7 +2595,7 @@
         <v>1.11155</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>21.017511</v>
+        <v>303.7869</v>
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="0" t="n">
-        <v>2</v>
+        <v>0.5182</v>
       </c>
       <c r="K26" s="0" t="n">
         <v>1</v>
@@ -2649,7 +2649,7 @@
         <v>1.0105</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>32.871387</v>
+        <v>475.122751</v>
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>0.08</v>
       </c>
       <c r="J27" s="0" t="n">
-        <v>2</v>
+        <v>0.810465</v>
       </c>
       <c r="K27" s="0" t="n">
         <v>1</v>
@@ -2703,7 +2703,7 @@
         <v>1.061025</v>
       </c>
       <c r="D28" s="0" t="n">
-        <v>13.661382</v>
+        <v>197.461494</v>
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="0" t="n">
-        <v>1</v>
+        <v>0.33683</v>
       </c>
       <c r="K28" s="0" t="n">
         <v>1</v>
@@ -2757,7 +2757,7 @@
         <v>1.0105</v>
       </c>
       <c r="D29" s="0" t="n">
-        <v>32.871387</v>
+        <v>475.122751</v>
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>0.08</v>
       </c>
       <c r="J29" s="0" t="n">
-        <v>2</v>
+        <v>0.810465</v>
       </c>
       <c r="K29" s="0" t="n">
         <v>1</v>
@@ -2865,7 +2865,7 @@
         <v>1.1132</v>
       </c>
       <c r="D31" s="0" t="n">
-        <v>25.007045</v>
+        <v>364.16979</v>
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="0" t="n">
-        <v>2</v>
+        <v>0.523408</v>
       </c>
       <c r="K31" s="0" t="n">
         <v>1</v>
@@ -2919,7 +2919,7 @@
         <v>1.1132</v>
       </c>
       <c r="D32" s="0" t="n">
-        <v>25.007045</v>
+        <v>364.16979</v>
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="0" t="n">
-        <v>2</v>
+        <v>0.523408</v>
       </c>
       <c r="K32" s="0" t="n">
         <v>1</v>
@@ -2973,7 +2973,7 @@
         <v>1.012</v>
       </c>
       <c r="D33" s="0" t="n">
-        <v>39.111019</v>
+        <v>569.561535</v>
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>0.08</v>
       </c>
       <c r="J33" s="0" t="n">
-        <v>2</v>
+        <v>0.8186099999999999</v>
       </c>
       <c r="K33" s="0" t="n">
         <v>1</v>
@@ -3027,7 +3027,7 @@
         <v>1.0626</v>
       </c>
       <c r="D34" s="0" t="n">
-        <v>16.254579</v>
+        <v>236.710356</v>
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="0" t="n">
-        <v>1</v>
+        <v>0.340215</v>
       </c>
       <c r="K34" s="0" t="n">
         <v>1</v>
@@ -3081,7 +3081,7 @@
         <v>1.012</v>
       </c>
       <c r="D35" s="0" t="n">
-        <v>39.111019</v>
+        <v>569.561535</v>
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>0.08</v>
       </c>
       <c r="J35" s="0" t="n">
-        <v>2</v>
+        <v>0.8186099999999999</v>
       </c>
       <c r="K35" s="0" t="n">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>1.1</v>
       </c>
       <c r="D36" s="0" t="n">
-        <v>18</v>
+        <v>174.600778</v>
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="0" t="n">
-        <v>1</v>
+        <v>0.278464</v>
       </c>
       <c r="K36" s="0" t="n">
         <v>1</v>
@@ -3189,7 +3189,7 @@
         <v>1.11485</v>
       </c>
       <c r="D37" s="0" t="n">
-        <v>29.724483</v>
+        <v>432.493154</v>
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="0" t="n">
-        <v>2</v>
+        <v>0.528821</v>
       </c>
       <c r="K37" s="0" t="n">
         <v>1</v>
@@ -3243,7 +3243,7 @@
         <v>1.11485</v>
       </c>
       <c r="D38" s="0" t="n">
-        <v>29.724483</v>
+        <v>432.493154</v>
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="J38" s="0" t="n">
-        <v>2</v>
+        <v>0.528821</v>
       </c>
       <c r="K38" s="0" t="n">
         <v>1</v>
@@ -3297,7 +3297,7 @@
         <v>1.0135</v>
       </c>
       <c r="D39" s="0" t="n">
-        <v>46.489092</v>
+        <v>676.419343</v>
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>0.08</v>
       </c>
       <c r="J39" s="0" t="n">
-        <v>2</v>
+        <v>0.827077</v>
       </c>
       <c r="K39" s="0" t="n">
         <v>1</v>
@@ -3351,7 +3351,7 @@
         <v>1.064175</v>
       </c>
       <c r="D40" s="0" t="n">
-        <v>19.320914</v>
+        <v>281.120529</v>
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="J40" s="0" t="n">
-        <v>1</v>
+        <v>0.343734</v>
       </c>
       <c r="K40" s="0" t="n">
         <v>1</v>
@@ -3405,7 +3405,7 @@
         <v>1.0135</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>46.489092</v>
+        <v>676.419343</v>
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>0.08</v>
       </c>
       <c r="J41" s="0" t="n">
-        <v>2</v>
+        <v>0.827077</v>
       </c>
       <c r="K41" s="0" t="n">
         <v>1</v>
@@ -3459,7 +3459,7 @@
         <v>1.12</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>32</v>
+        <v>243.503532</v>
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="0" t="n">
-        <v>1</v>
+        <v>0.291707</v>
       </c>
       <c r="K42" s="0" t="n">
         <v>1</v>
@@ -3513,7 +3513,7 @@
         <v>1.1165</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>51.298157</v>
+        <v>585.528881</v>
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="0" t="n">
-        <v>2</v>
+        <v>0.5377690000000001</v>
       </c>
       <c r="K43" s="0" t="n">
         <v>1</v>
@@ -3567,7 +3567,7 @@
         <v>1.1165</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>51.298157</v>
+        <v>585.528881</v>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="0" t="n">
-        <v>2</v>
+        <v>0.5377690000000001</v>
       </c>
       <c r="K44" s="0" t="n">
         <v>1</v>
@@ -3621,7 +3621,7 @@
         <v>1.015</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>80.230318</v>
+        <v>915.767155</v>
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>0.08</v>
       </c>
       <c r="J45" s="0" t="n">
-        <v>2</v>
+        <v>0.841071</v>
       </c>
       <c r="K45" s="0" t="n">
         <v>1</v>
@@ -3675,7 +3675,7 @@
         <v>1.06575</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>33.343802</v>
+        <v>380.593767</v>
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="0" t="n">
-        <v>1</v>
+        <v>0.349549</v>
       </c>
       <c r="K46" s="0" t="n">
         <v>1</v>
@@ -3729,7 +3729,7 @@
         <v>1.015</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>80.230318</v>
+        <v>915.767155</v>
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>0.08</v>
       </c>
       <c r="J47" s="0" t="n">
-        <v>2</v>
+        <v>0.841071</v>
       </c>
       <c r="K47" s="0" t="n">
         <v>1</v>
@@ -3783,7 +3783,7 @@
         <v>1.11815</v>
       </c>
       <c r="D48" s="0" t="n">
-        <v>44.145077</v>
+        <v>541.400713</v>
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="0" t="n">
-        <v>2</v>
+        <v>0.5532820000000001</v>
       </c>
       <c r="K48" s="0" t="n">
         <v>1</v>
@@ -3837,7 +3837,7 @@
         <v>1.11815</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>44.145077</v>
+        <v>541.400713</v>
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="J49" s="0" t="n">
-        <v>2</v>
+        <v>0.5532820000000001</v>
       </c>
       <c r="K49" s="0" t="n">
         <v>1</v>
@@ -3891,7 +3891,7 @@
         <v>1.6264</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>37.523316</v>
+        <v>460.190628</v>
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="0" t="n">
-        <v>1</v>
+        <v>0.470289</v>
       </c>
       <c r="K50" s="0" t="n">
         <v>1</v>
@@ -3945,7 +3945,7 @@
         <v>1.0165</v>
       </c>
       <c r="D51" s="0" t="n">
-        <v>69.042901</v>
+        <v>846.750762</v>
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>0.08</v>
       </c>
       <c r="J51" s="0" t="n">
-        <v>2</v>
+        <v>0.865332</v>
       </c>
       <c r="K51" s="0" t="n">
         <v>1</v>
@@ -3999,7 +3999,7 @@
         <v>1.067325</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>28.6943</v>
+        <v>351.910471</v>
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="0" t="n">
-        <v>1</v>
+        <v>0.359633</v>
       </c>
       <c r="K52" s="0" t="n">
         <v>1</v>
@@ -4053,7 +4053,7 @@
         <v>0.8132</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>82.551294</v>
+        <v>1012.419319</v>
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>0.15</v>
       </c>
       <c r="J53" s="0" t="n">
-        <v>3</v>
+        <v>1.034637</v>
       </c>
       <c r="K53" s="0" t="n">
         <v>2</v>
@@ -4107,7 +4107,7 @@
         <v>1.0165</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>69.042901</v>
+        <v>846.750762</v>
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>0.08</v>
       </c>
       <c r="J54" s="0" t="n">
-        <v>2</v>
+        <v>0.865332</v>
       </c>
       <c r="K54" s="0" t="n">
         <v>1</v>
@@ -4161,7 +4161,7 @@
         <v>1.05</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>26</v>
+        <v>213.254156</v>
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="0" t="n">
-        <v>1</v>
+        <v>0.295922</v>
       </c>
       <c r="K55" s="0" t="n">
         <v>1</v>
@@ -4215,7 +4215,7 @@
         <v>1.05</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>26</v>
+        <v>213.254156</v>
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="0" t="n">
-        <v>1</v>
+        <v>0.295922</v>
       </c>
       <c r="K56" s="0" t="n">
         <v>1</v>
@@ -4269,7 +4269,7 @@
         <v>1.1198</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>43.239718</v>
+        <v>531.98371</v>
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="0" t="n">
-        <v>2</v>
+        <v>0.565959</v>
       </c>
       <c r="K57" s="0" t="n">
         <v>1</v>
@@ -4323,7 +4323,7 @@
         <v>1.1198</v>
       </c>
       <c r="D58" s="0" t="n">
-        <v>43.239718</v>
+        <v>531.98371</v>
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="0" t="n">
-        <v>2</v>
+        <v>0.565959</v>
       </c>
       <c r="K58" s="0" t="n">
         <v>1</v>
@@ -4377,7 +4377,7 @@
         <v>1.6288</v>
       </c>
       <c r="D59" s="0" t="n">
-        <v>36.753761</v>
+        <v>452.186093</v>
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="0" t="n">
-        <v>1</v>
+        <v>0.481065</v>
       </c>
       <c r="K59" s="0" t="n">
         <v>1</v>
@@ -4431,7 +4431,7 @@
         <v>1.018</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>67.626919</v>
+        <v>832.022481</v>
       </c>
       <c r="E60" s="0" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>0.08</v>
       </c>
       <c r="J60" s="0" t="n">
-        <v>2</v>
+        <v>0.8851599999999999</v>
       </c>
       <c r="K60" s="0" t="n">
         <v>1</v>
@@ -4485,7 +4485,7 @@
         <v>1.0689</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>28.105817</v>
+        <v>345.789392</v>
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="0" t="n">
-        <v>1</v>
+        <v>0.367873</v>
       </c>
       <c r="K61" s="0" t="n">
         <v>1</v>
@@ -4539,7 +4539,7 @@
         <v>0.8144</v>
       </c>
       <c r="D62" s="0" t="n">
-        <v>80.858273</v>
+        <v>994.809524</v>
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>0.15</v>
       </c>
       <c r="J62" s="0" t="n">
-        <v>3</v>
+        <v>1.058344</v>
       </c>
       <c r="K62" s="0" t="n">
         <v>2</v>
@@ -4593,7 +4593,7 @@
         <v>1.018</v>
       </c>
       <c r="D63" s="0" t="n">
-        <v>67.626919</v>
+        <v>832.022481</v>
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>0.08</v>
       </c>
       <c r="J63" s="0" t="n">
-        <v>2</v>
+        <v>0.8851599999999999</v>
       </c>
       <c r="K63" s="0" t="n">
         <v>1</v>
@@ -4647,7 +4647,7 @@
         <v>1.1</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>31</v>
+        <v>252.748048</v>
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         <v>0</v>
       </c>
       <c r="J64" s="0" t="n">
-        <v>1</v>
+        <v>0.306392</v>
       </c>
       <c r="K64" s="0" t="n">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>1.1</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>31</v>
+        <v>252.748048</v>
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="0" t="n">
-        <v>1</v>
+        <v>0.306392</v>
       </c>
       <c r="K65" s="0" t="n">
         <v>1</v>
@@ -4755,7 +4755,7 @@
         <v>1.12145</v>
       </c>
       <c r="D66" s="0" t="n">
-        <v>49.313769</v>
+        <v>603.09477</v>
       </c>
       <c r="E66" s="0" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>0</v>
       </c>
       <c r="J66" s="0" t="n">
-        <v>2</v>
+        <v>0.560509</v>
       </c>
       <c r="K66" s="0" t="n">
         <v>1</v>
@@ -4809,7 +4809,7 @@
         <v>1.12145</v>
       </c>
       <c r="D67" s="0" t="n">
-        <v>49.313769</v>
+        <v>603.09477</v>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>0</v>
       </c>
       <c r="J67" s="0" t="n">
-        <v>2</v>
+        <v>0.560509</v>
       </c>
       <c r="K67" s="0" t="n">
         <v>1</v>
@@ -4863,7 +4863,7 @@
         <v>1.6312</v>
       </c>
       <c r="D68" s="0" t="n">
-        <v>41.916704</v>
+        <v>512.630527</v>
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="0" t="n">
-        <v>1</v>
+        <v>0.476432</v>
       </c>
       <c r="K68" s="0" t="n">
         <v>1</v>
@@ -4917,7 +4917,7 @@
         <v>1.0195</v>
       </c>
       <c r="D69" s="0" t="n">
-        <v>77.126735</v>
+        <v>943.24013</v>
       </c>
       <c r="E69" s="0" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>0.08</v>
       </c>
       <c r="J69" s="0" t="n">
-        <v>2</v>
+        <v>0.876636</v>
       </c>
       <c r="K69" s="0" t="n">
         <v>1</v>
@@ -4971,7 +4971,7 @@
         <v>1.070475</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>32.05395</v>
+        <v>392.011606</v>
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="0" t="n">
-        <v>1</v>
+        <v>0.36433</v>
       </c>
       <c r="K70" s="0" t="n">
         <v>1</v>
@@ -5025,7 +5025,7 @@
         <v>0.8156000000000001</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>92.21674899999999</v>
+        <v>1127.787223</v>
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>0.15</v>
       </c>
       <c r="J71" s="0" t="n">
-        <v>3</v>
+        <v>1.048151</v>
       </c>
       <c r="K71" s="0" t="n">
         <v>2</v>
@@ -5079,7 +5079,7 @@
         <v>1.0195</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>77.126735</v>
+        <v>943.24013</v>
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
@@ -5101,7 +5101,7 @@
         <v>0.08</v>
       </c>
       <c r="J72" s="0" t="n">
-        <v>2</v>
+        <v>0.876636</v>
       </c>
       <c r="K72" s="0" t="n">
         <v>1</v>
@@ -5133,7 +5133,7 @@
         <v>1.14</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>35</v>
+        <v>286.206583</v>
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="J73" s="0" t="n">
-        <v>1</v>
+        <v>0.30235</v>
       </c>
       <c r="K73" s="0" t="n">
         <v>1</v>
@@ -5187,7 +5187,7 @@
         <v>1.14</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>35</v>
+        <v>286.206583</v>
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="0" t="n">
-        <v>1</v>
+        <v>0.30235</v>
       </c>
       <c r="K74" s="0" t="n">
         <v>1</v>
@@ -5241,7 +5241,7 @@
         <v>1.1231</v>
       </c>
       <c r="D75" s="0" t="n">
-        <v>55.996797</v>
+        <v>686.856458</v>
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="0" t="n">
-        <v>2</v>
+        <v>0.556292</v>
       </c>
       <c r="K75" s="0" t="n">
         <v>1</v>
@@ -5295,7 +5295,7 @@
         <v>1.1231</v>
       </c>
       <c r="D76" s="0" t="n">
-        <v>55.996797</v>
+        <v>686.856458</v>
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="J76" s="0" t="n">
-        <v>2</v>
+        <v>0.556292</v>
       </c>
       <c r="K76" s="0" t="n">
         <v>1</v>
@@ -5349,7 +5349,7 @@
         <v>1.6336</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>47.597277</v>
+        <v>583.828036</v>
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>0</v>
       </c>
       <c r="J77" s="0" t="n">
-        <v>1</v>
+        <v>0.472848</v>
       </c>
       <c r="K77" s="0" t="n">
         <v>1</v>
@@ -5403,7 +5403,7 @@
         <v>1.021</v>
       </c>
       <c r="D78" s="0" t="n">
-        <v>87.57899</v>
+        <v>1074.243479</v>
       </c>
       <c r="E78" s="0" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>0.08</v>
       </c>
       <c r="J78" s="0" t="n">
-        <v>2</v>
+        <v>0.870041</v>
       </c>
       <c r="K78" s="0" t="n">
         <v>1</v>
@@ -5457,7 +5457,7 @@
         <v>1.07205</v>
       </c>
       <c r="D79" s="0" t="n">
-        <v>36.397918</v>
+        <v>446.456725</v>
       </c>
       <c r="E79" s="0" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="J79" s="0" t="n">
-        <v>1</v>
+        <v>0.36159</v>
       </c>
       <c r="K79" s="0" t="n">
         <v>1</v>
@@ -5511,7 +5511,7 @@
         <v>0.8168000000000002</v>
       </c>
       <c r="D80" s="0" t="n">
-        <v>104.714009</v>
+        <v>1284.421561</v>
       </c>
       <c r="E80" s="0" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>0.15</v>
       </c>
       <c r="J80" s="0" t="n">
-        <v>3</v>
+        <v>1.040266</v>
       </c>
       <c r="K80" s="0" t="n">
         <v>2</v>
@@ -5565,7 +5565,7 @@
         <v>1.021</v>
       </c>
       <c r="D81" s="0" t="n">
-        <v>87.57899</v>
+        <v>1074.243479</v>
       </c>
       <c r="E81" s="0" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>0.08</v>
       </c>
       <c r="J81" s="0" t="n">
-        <v>2</v>
+        <v>0.870041</v>
       </c>
       <c r="K81" s="0" t="n">
         <v>1</v>
@@ -5619,7 +5619,7 @@
         <v>1.13</v>
       </c>
       <c r="D82" s="0" t="n">
-        <v>56</v>
+        <v>357.952618</v>
       </c>
       <c r="E82" s="0" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="J82" s="0" t="n">
-        <v>1</v>
+        <v>0.293343</v>
       </c>
       <c r="K82" s="0" t="n">
         <v>1</v>
@@ -5673,7 +5673,7 @@
         <v>1.13</v>
       </c>
       <c r="D83" s="0" t="n">
-        <v>56</v>
+        <v>357.952618</v>
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="0" t="n">
-        <v>1</v>
+        <v>0.293343</v>
       </c>
       <c r="K83" s="0" t="n">
         <v>1</v>
@@ -5727,7 +5727,7 @@
         <v>1.12475</v>
       </c>
       <c r="D84" s="0" t="n">
-        <v>93.292309</v>
+        <v>894.4882710000001</v>
       </c>
       <c r="E84" s="0" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="J84" s="0" t="n">
-        <v>2</v>
+        <v>0.561992</v>
       </c>
       <c r="K84" s="0" t="n">
         <v>1</v>
@@ -5781,7 +5781,7 @@
         <v>1.12475</v>
       </c>
       <c r="D85" s="0" t="n">
-        <v>93.292309</v>
+        <v>894.4882710000001</v>
       </c>
       <c r="E85" s="0" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="J85" s="0" t="n">
-        <v>2</v>
+        <v>0.561992</v>
       </c>
       <c r="K85" s="0" t="n">
         <v>1</v>
@@ -5835,7 +5835,7 @@
         <v>1.636</v>
       </c>
       <c r="D86" s="0" t="n">
-        <v>79.298463</v>
+        <v>760.314969</v>
       </c>
       <c r="E86" s="0" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="J86" s="0" t="n">
-        <v>1</v>
+        <v>0.477694</v>
       </c>
       <c r="K86" s="0" t="n">
         <v>1</v>
@@ -5889,7 +5889,7 @@
         <v>1.0225</v>
       </c>
       <c r="D87" s="0" t="n">
-        <v>145.909171</v>
+        <v>1398.979462</v>
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>0.08</v>
       </c>
       <c r="J87" s="0" t="n">
-        <v>2</v>
+        <v>0.878957</v>
       </c>
       <c r="K87" s="0" t="n">
         <v>1</v>
@@ -5943,7 +5943,7 @@
         <v>1.073625</v>
       </c>
       <c r="D88" s="0" t="n">
-        <v>60.640001</v>
+        <v>581.417334</v>
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>0</v>
       </c>
       <c r="J88" s="0" t="n">
-        <v>1</v>
+        <v>0.365295</v>
       </c>
       <c r="K88" s="0" t="n">
         <v>1</v>
@@ -5997,7 +5997,7 @@
         <v>0.8180000000000001</v>
       </c>
       <c r="D89" s="0" t="n">
-        <v>174.456618</v>
+        <v>1672.693071</v>
       </c>
       <c r="E89" s="0" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>0.15</v>
       </c>
       <c r="J89" s="0" t="n">
-        <v>3</v>
+        <v>1.050926</v>
       </c>
       <c r="K89" s="0" t="n">
         <v>2</v>
@@ -6051,7 +6051,7 @@
         <v>1.0225</v>
       </c>
       <c r="D90" s="0" t="n">
-        <v>145.909171</v>
+        <v>1398.979462</v>
       </c>
       <c r="E90" s="0" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>0.08</v>
       </c>
       <c r="J90" s="0" t="n">
-        <v>2</v>
+        <v>0.878957</v>
       </c>
       <c r="K90" s="0" t="n">
         <v>1</v>
@@ -6105,7 +6105,7 @@
         <v>1.0225</v>
       </c>
       <c r="D91" s="0" t="n">
-        <v>145.909171</v>
+        <v>1398.979462</v>
       </c>
       <c r="E91" s="0" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>0.08</v>
       </c>
       <c r="J91" s="0" t="n">
-        <v>2</v>
+        <v>0.878957</v>
       </c>
       <c r="K91" s="0" t="n">
         <v>1</v>
@@ -6159,7 +6159,7 @@
         <v>1.1264</v>
       </c>
       <c r="D92" s="0" t="n">
-        <v>90.286767</v>
+        <v>968.948519</v>
       </c>
       <c r="E92" s="0" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="0" t="n">
-        <v>2</v>
+        <v>0.56403</v>
       </c>
       <c r="K92" s="0" t="n">
         <v>1</v>
@@ -6213,7 +6213,7 @@
         <v>1.1264</v>
       </c>
       <c r="D93" s="0" t="n">
-        <v>90.286767</v>
+        <v>968.948519</v>
       </c>
       <c r="E93" s="0" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="0" t="n">
-        <v>2</v>
+        <v>0.56403</v>
       </c>
       <c r="K93" s="0" t="n">
         <v>1</v>
@@ -6267,7 +6267,7 @@
         <v>1.6384</v>
       </c>
       <c r="D94" s="0" t="n">
-        <v>76.743752</v>
+        <v>823.606242</v>
       </c>
       <c r="E94" s="0" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="0" t="n">
-        <v>1</v>
+        <v>0.479426</v>
       </c>
       <c r="K94" s="0" t="n">
         <v>1</v>
@@ -6321,7 +6321,7 @@
         <v>1.024</v>
       </c>
       <c r="D95" s="0" t="n">
-        <v>141.208504</v>
+        <v>1515.435501</v>
       </c>
       <c r="E95" s="0" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>0.08</v>
       </c>
       <c r="J95" s="0" t="n">
-        <v>2</v>
+        <v>0.882143</v>
       </c>
       <c r="K95" s="0" t="n">
         <v>1</v>
@@ -6375,7 +6375,7 @@
         <v>1.0752</v>
       </c>
       <c r="D96" s="0" t="n">
-        <v>58.686399</v>
+        <v>629.816565</v>
       </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>0</v>
       </c>
       <c r="J96" s="0" t="n">
-        <v>1</v>
+        <v>0.36662</v>
       </c>
       <c r="K96" s="0" t="n">
         <v>1</v>
@@ -6429,7 +6429,7 @@
         <v>0.8192</v>
       </c>
       <c r="D97" s="0" t="n">
-        <v>168.836255</v>
+        <v>1811.933813</v>
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>0.15</v>
       </c>
       <c r="J97" s="0" t="n">
-        <v>3</v>
+        <v>1.054736</v>
       </c>
       <c r="K97" s="0" t="n">
         <v>2</v>
@@ -6483,7 +6483,7 @@
         <v>1.024</v>
       </c>
       <c r="D98" s="0" t="n">
-        <v>141.208504</v>
+        <v>1515.435501</v>
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>0.08</v>
       </c>
       <c r="J98" s="0" t="n">
-        <v>2</v>
+        <v>0.882143</v>
       </c>
       <c r="K98" s="0" t="n">
         <v>1</v>
@@ -6537,7 +6537,7 @@
         <v>1.024</v>
       </c>
       <c r="D99" s="0" t="n">
-        <v>141.208504</v>
+        <v>1515.435501</v>
       </c>
       <c r="E99" s="0" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>0.08</v>
       </c>
       <c r="J99" s="0" t="n">
-        <v>2</v>
+        <v>0.882143</v>
       </c>
       <c r="K99" s="0" t="n">
         <v>1</v>
@@ -6591,7 +6591,7 @@
         <v>1.12</v>
       </c>
       <c r="D100" s="0" t="n">
-        <v>53</v>
+        <v>381.811017</v>
       </c>
       <c r="E100" s="0" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>0</v>
       </c>
       <c r="J100" s="0" t="n">
-        <v>1</v>
+        <v>0.300436</v>
       </c>
       <c r="K100" s="0" t="n">
         <v>1</v>
@@ -6645,7 +6645,7 @@
         <v>1.12</v>
       </c>
       <c r="D101" s="0" t="n">
-        <v>53</v>
+        <v>381.811017</v>
       </c>
       <c r="E101" s="0" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="J101" s="0" t="n">
-        <v>1</v>
+        <v>0.300436</v>
       </c>
       <c r="K101" s="0" t="n">
         <v>1</v>
@@ -6699,7 +6699,7 @@
         <v>1.12</v>
       </c>
       <c r="D102" s="0" t="n">
-        <v>53</v>
+        <v>381.811017</v>
       </c>
       <c r="E102" s="0" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>0</v>
       </c>
       <c r="J102" s="0" t="n">
-        <v>1</v>
+        <v>0.300436</v>
       </c>
       <c r="K102" s="0" t="n">
         <v>1</v>
@@ -6753,7 +6753,7 @@
         <v>1.12805</v>
       </c>
       <c r="D103" s="0" t="n">
-        <v>87.807885</v>
+        <v>948.849488</v>
       </c>
       <c r="E103" s="0" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="0" t="n">
-        <v>2</v>
+        <v>0.57241</v>
       </c>
       <c r="K103" s="0" t="n">
         <v>1</v>
@@ -6807,7 +6807,7 @@
         <v>1.12805</v>
       </c>
       <c r="D104" s="0" t="n">
-        <v>87.807885</v>
+        <v>948.849488</v>
       </c>
       <c r="E104" s="0" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="J104" s="0" t="n">
-        <v>2</v>
+        <v>0.57241</v>
       </c>
       <c r="K104" s="0" t="n">
         <v>1</v>
@@ -6861,7 +6861,7 @@
         <v>1.6408</v>
       </c>
       <c r="D105" s="0" t="n">
-        <v>74.636703</v>
+        <v>806.522072</v>
       </c>
       <c r="E105" s="0" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>0</v>
       </c>
       <c r="J105" s="0" t="n">
-        <v>1</v>
+        <v>0.486549</v>
       </c>
       <c r="K105" s="0" t="n">
         <v>1</v>
@@ -6915,7 +6915,7 @@
         <v>1.0255</v>
       </c>
       <c r="D106" s="0" t="n">
-        <v>137.331533</v>
+        <v>1484.00069</v>
       </c>
       <c r="E106" s="0" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>0.08</v>
       </c>
       <c r="J106" s="0" t="n">
-        <v>2</v>
+        <v>0.89525</v>
       </c>
       <c r="K106" s="0" t="n">
         <v>1</v>
@@ -6969,7 +6969,7 @@
         <v>1.076775</v>
       </c>
       <c r="D107" s="0" t="n">
-        <v>57.075125</v>
+        <v>616.7522290000001</v>
       </c>
       <c r="E107" s="0" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="J107" s="0" t="n">
-        <v>1</v>
+        <v>0.372066</v>
       </c>
       <c r="K107" s="0" t="n">
         <v>1</v>
@@ -7023,7 +7023,7 @@
         <v>0.8204000000000001</v>
       </c>
       <c r="D108" s="0" t="n">
-        <v>164.200746</v>
+        <v>1774.34853</v>
       </c>
       <c r="E108" s="0" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>0.15</v>
       </c>
       <c r="J108" s="0" t="n">
-        <v>3</v>
+        <v>1.070407</v>
       </c>
       <c r="K108" s="0" t="n">
         <v>2</v>
@@ -7077,7 +7077,7 @@
         <v>1.0255</v>
       </c>
       <c r="D109" s="0" t="n">
-        <v>137.331533</v>
+        <v>1484.00069</v>
       </c>
       <c r="E109" s="0" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>0.08</v>
       </c>
       <c r="J109" s="0" t="n">
-        <v>2</v>
+        <v>0.89525</v>
       </c>
       <c r="K109" s="0" t="n">
         <v>1</v>
@@ -7131,7 +7131,7 @@
         <v>1.0255</v>
       </c>
       <c r="D110" s="0" t="n">
-        <v>137.331533</v>
+        <v>1484.00069</v>
       </c>
       <c r="E110" s="0" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>0.08</v>
       </c>
       <c r="J110" s="0" t="n">
-        <v>2</v>
+        <v>0.89525</v>
       </c>
       <c r="K110" s="0" t="n">
         <v>1</v>
@@ -7185,7 +7185,7 @@
         <v>1.12</v>
       </c>
       <c r="D111" s="0" t="n">
-        <v>57</v>
+        <v>406.265625</v>
       </c>
       <c r="E111" s="0" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>0</v>
       </c>
       <c r="J111" s="0" t="n">
-        <v>1</v>
+        <v>0.314056</v>
       </c>
       <c r="K111" s="0" t="n">
         <v>1</v>
@@ -7239,7 +7239,7 @@
         <v>1.12</v>
       </c>
       <c r="D112" s="0" t="n">
-        <v>57</v>
+        <v>406.265625</v>
       </c>
       <c r="E112" s="0" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="0" t="n">
-        <v>1</v>
+        <v>0.314056</v>
       </c>
       <c r="K112" s="0" t="n">
         <v>1</v>
@@ -7293,7 +7293,7 @@
         <v>1.12</v>
       </c>
       <c r="D113" s="0" t="n">
-        <v>57</v>
+        <v>406.265625</v>
       </c>
       <c r="E113" s="0" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         <v>0</v>
       </c>
       <c r="J113" s="0" t="n">
-        <v>1</v>
+        <v>0.314056</v>
       </c>
       <c r="K113" s="0" t="n">
         <v>1</v>
@@ -7347,7 +7347,7 @@
         <v>1.1297</v>
       </c>
       <c r="D114" s="0" t="n">
-        <v>89.475898</v>
+        <v>956.604782</v>
       </c>
       <c r="E114" s="0" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="J114" s="0" t="n">
-        <v>2</v>
+        <v>0.5669380000000001</v>
       </c>
       <c r="K114" s="0" t="n">
         <v>1</v>
@@ -7401,7 +7401,7 @@
         <v>1.1297</v>
       </c>
       <c r="D115" s="0" t="n">
-        <v>89.475898</v>
+        <v>956.604782</v>
       </c>
       <c r="E115" s="0" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="0" t="n">
-        <v>2</v>
+        <v>0.5669380000000001</v>
       </c>
       <c r="K115" s="0" t="n">
         <v>1</v>
@@ -7455,7 +7455,7 @@
         <v>1.6432</v>
       </c>
       <c r="D116" s="0" t="n">
-        <v>76.054513</v>
+        <v>813.114051</v>
       </c>
       <c r="E116" s="0" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>0</v>
       </c>
       <c r="J116" s="0" t="n">
-        <v>1</v>
+        <v>0.481897</v>
       </c>
       <c r="K116" s="0" t="n">
         <v>1</v>
@@ -7509,7 +7509,7 @@
         <v>1.027</v>
       </c>
       <c r="D117" s="0" t="n">
-        <v>139.940304</v>
+        <v>1496.129832</v>
       </c>
       <c r="E117" s="0" t="inlineStr">
         <is>
@@ -7531,7 +7531,7 @@
         <v>0.08</v>
       </c>
       <c r="J117" s="0" t="n">
-        <v>2</v>
+        <v>0.886691</v>
       </c>
       <c r="K117" s="0" t="n">
         <v>1</v>
@@ -7563,7 +7563,7 @@
         <v>1.07835</v>
       </c>
       <c r="D118" s="0" t="n">
-        <v>58.159333</v>
+        <v>621.793065</v>
       </c>
       <c r="E118" s="0" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="J118" s="0" t="n">
-        <v>1</v>
+        <v>0.368509</v>
       </c>
       <c r="K118" s="0" t="n">
         <v>1</v>
@@ -7617,7 +7617,7 @@
         <v>0.8216000000000001</v>
       </c>
       <c r="D119" s="0" t="n">
-        <v>167.319929</v>
+        <v>1788.850941</v>
       </c>
       <c r="E119" s="0" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>0.15</v>
       </c>
       <c r="J119" s="0" t="n">
-        <v>3</v>
+        <v>1.060175</v>
       </c>
       <c r="K119" s="0" t="n">
         <v>2</v>
@@ -7671,7 +7671,7 @@
         <v>1.027</v>
       </c>
       <c r="D120" s="0" t="n">
-        <v>139.940304</v>
+        <v>1496.129832</v>
       </c>
       <c r="E120" s="0" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>0.08</v>
       </c>
       <c r="J120" s="0" t="n">
-        <v>2</v>
+        <v>0.886691</v>
       </c>
       <c r="K120" s="0" t="n">
         <v>1</v>
@@ -7725,7 +7725,7 @@
         <v>1.027</v>
       </c>
       <c r="D121" s="0" t="n">
-        <v>139.940304</v>
+        <v>1496.129832</v>
       </c>
       <c r="E121" s="0" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>0.08</v>
       </c>
       <c r="J121" s="0" t="n">
-        <v>2</v>
+        <v>0.886691</v>
       </c>
       <c r="K121" s="0" t="n">
         <v>1</v>
@@ -7779,7 +7779,7 @@
         <v>1.16</v>
       </c>
       <c r="D122" s="0" t="n">
-        <v>61</v>
+        <v>440.659336</v>
       </c>
       <c r="E122" s="0" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>0</v>
       </c>
       <c r="J122" s="0" t="n">
-        <v>1</v>
+        <v>0.305528</v>
       </c>
       <c r="K122" s="0" t="n">
         <v>1</v>
@@ -7833,7 +7833,7 @@
         <v>1.16</v>
       </c>
       <c r="D123" s="0" t="n">
-        <v>61</v>
+        <v>440.659336</v>
       </c>
       <c r="E123" s="0" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>0</v>
       </c>
       <c r="J123" s="0" t="n">
-        <v>1</v>
+        <v>0.305528</v>
       </c>
       <c r="K123" s="0" t="n">
         <v>1</v>
@@ -7887,7 +7887,7 @@
         <v>1.16</v>
       </c>
       <c r="D124" s="0" t="n">
-        <v>61</v>
+        <v>440.659336</v>
       </c>
       <c r="E124" s="0" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>0</v>
       </c>
       <c r="J124" s="0" t="n">
-        <v>1</v>
+        <v>0.305528</v>
       </c>
       <c r="K124" s="0" t="n">
         <v>1</v>
@@ -7941,7 +7941,7 @@
         <v>1.13135</v>
       </c>
       <c r="D125" s="0" t="n">
-        <v>98.89997700000001</v>
+        <v>1071.668764</v>
       </c>
       <c r="E125" s="0" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="J125" s="0" t="n">
-        <v>2</v>
+        <v>0.569659</v>
       </c>
       <c r="K125" s="0" t="n">
         <v>1</v>
@@ -7995,7 +7995,7 @@
         <v>1.13135</v>
       </c>
       <c r="D126" s="0" t="n">
-        <v>98.89997700000001</v>
+        <v>1071.668764</v>
       </c>
       <c r="E126" s="0" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>0</v>
       </c>
       <c r="J126" s="0" t="n">
-        <v>2</v>
+        <v>0.569659</v>
       </c>
       <c r="K126" s="0" t="n">
         <v>1</v>
@@ -8049,7 +8049,7 @@
         <v>1.6456</v>
       </c>
       <c r="D127" s="0" t="n">
-        <v>84.064981</v>
+        <v>910.918491</v>
       </c>
       <c r="E127" s="0" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>0</v>
       </c>
       <c r="J127" s="0" t="n">
-        <v>1</v>
+        <v>0.484211</v>
       </c>
       <c r="K127" s="0" t="n">
         <v>1</v>
@@ -8103,7 +8103,7 @@
         <v>1.0285</v>
       </c>
       <c r="D128" s="0" t="n">
-        <v>154.679565</v>
+        <v>1676.090099</v>
       </c>
       <c r="E128" s="0" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>0.08</v>
       </c>
       <c r="J128" s="0" t="n">
-        <v>2</v>
+        <v>0.890948</v>
       </c>
       <c r="K128" s="0" t="n">
         <v>1</v>
@@ -8157,7 +8157,7 @@
         <v>1.079925</v>
       </c>
       <c r="D129" s="0" t="n">
-        <v>64.28498500000001</v>
+        <v>696.5847659999999</v>
       </c>
       <c r="E129" s="0" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>0</v>
       </c>
       <c r="J129" s="0" t="n">
-        <v>1</v>
+        <v>0.370278</v>
       </c>
       <c r="K129" s="0" t="n">
         <v>1</v>
@@ -8211,7 +8211,7 @@
         <v>0.8228</v>
       </c>
       <c r="D130" s="0" t="n">
-        <v>184.942958</v>
+        <v>2004.020664</v>
       </c>
       <c r="E130" s="0" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         <v>0.15</v>
       </c>
       <c r="J130" s="0" t="n">
-        <v>3</v>
+        <v>1.065263</v>
       </c>
       <c r="K130" s="0" t="n">
         <v>2</v>
@@ -8265,7 +8265,7 @@
         <v>1.0285</v>
       </c>
       <c r="D131" s="0" t="n">
-        <v>154.679565</v>
+        <v>1676.090099</v>
       </c>
       <c r="E131" s="0" t="inlineStr">
         <is>
@@ -8287,7 +8287,7 @@
         <v>0.08</v>
       </c>
       <c r="J131" s="0" t="n">
-        <v>2</v>
+        <v>0.890948</v>
       </c>
       <c r="K131" s="0" t="n">
         <v>1</v>
@@ -8319,7 +8319,7 @@
         <v>1.0285</v>
       </c>
       <c r="D132" s="0" t="n">
-        <v>154.679565</v>
+        <v>1676.090099</v>
       </c>
       <c r="E132" s="0" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>0.08</v>
       </c>
       <c r="J132" s="0" t="n">
-        <v>2</v>
+        <v>0.890948</v>
       </c>
       <c r="K132" s="0" t="n">
         <v>1</v>
@@ -8373,7 +8373,7 @@
         <v>1.15</v>
       </c>
       <c r="D133" s="0" t="n">
-        <v>98</v>
+        <v>491.257986</v>
       </c>
       <c r="E133" s="0" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>0</v>
       </c>
       <c r="J133" s="0" t="n">
-        <v>1</v>
+        <v>0.305942</v>
       </c>
       <c r="K133" s="0" t="n">
         <v>1</v>
@@ -8427,7 +8427,7 @@
         <v>1.15</v>
       </c>
       <c r="D134" s="0" t="n">
-        <v>98</v>
+        <v>491.257986</v>
       </c>
       <c r="E134" s="0" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>0</v>
       </c>
       <c r="J134" s="0" t="n">
-        <v>1</v>
+        <v>0.305942</v>
       </c>
       <c r="K134" s="0" t="n">
         <v>1</v>
@@ -8481,7 +8481,7 @@
         <v>1.15</v>
       </c>
       <c r="D135" s="0" t="n">
-        <v>98</v>
+        <v>491.257986</v>
       </c>
       <c r="E135" s="0" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="J135" s="0" t="n">
-        <v>1</v>
+        <v>0.305942</v>
       </c>
       <c r="K135" s="0" t="n">
         <v>1</v>
@@ -8535,7 +8535,7 @@
         <v>1.133</v>
       </c>
       <c r="D136" s="0" t="n">
-        <v>160.699914</v>
+        <v>1208.34367</v>
       </c>
       <c r="E136" s="0" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="J136" s="0" t="n">
-        <v>2</v>
+        <v>0.576933</v>
       </c>
       <c r="K136" s="0" t="n">
         <v>1</v>
@@ -8589,7 +8589,7 @@
         <v>1.133</v>
       </c>
       <c r="D137" s="0" t="n">
-        <v>160.699914</v>
+        <v>1208.34367</v>
       </c>
       <c r="E137" s="0" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>0</v>
       </c>
       <c r="J137" s="0" t="n">
-        <v>2</v>
+        <v>0.576933</v>
       </c>
       <c r="K137" s="0" t="n">
         <v>1</v>
@@ -8643,7 +8643,7 @@
         <v>1.648</v>
       </c>
       <c r="D138" s="0" t="n">
-        <v>136.594927</v>
+        <v>1027.091991</v>
       </c>
       <c r="E138" s="0" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>0</v>
       </c>
       <c r="J138" s="0" t="n">
-        <v>1</v>
+        <v>0.490393</v>
       </c>
       <c r="K138" s="0" t="n">
         <v>1</v>
@@ -8697,7 +8697,7 @@
         <v>1.03</v>
       </c>
       <c r="D139" s="0" t="n">
-        <v>251.334666</v>
+        <v>1889.84955</v>
       </c>
       <c r="E139" s="0" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>0.08</v>
       </c>
       <c r="J139" s="0" t="n">
-        <v>2</v>
+        <v>0.902324</v>
       </c>
       <c r="K139" s="0" t="n">
         <v>1</v>
@@ -8751,7 +8751,7 @@
         <v>1.0815</v>
       </c>
       <c r="D140" s="0" t="n">
-        <v>104.454944</v>
+        <v>785.423313</v>
       </c>
       <c r="E140" s="0" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="J140" s="0" t="n">
-        <v>1</v>
+        <v>0.375007</v>
       </c>
       <c r="K140" s="0" t="n">
         <v>1</v>
@@ -8805,7 +8805,7 @@
         <v>0.8240000000000001</v>
       </c>
       <c r="D141" s="0" t="n">
-        <v>300.50884</v>
+        <v>2259.602727</v>
       </c>
       <c r="E141" s="0" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>0.15</v>
       </c>
       <c r="J141" s="0" t="n">
-        <v>3</v>
+        <v>1.078866</v>
       </c>
       <c r="K141" s="0" t="n">
         <v>2</v>
@@ -8859,7 +8859,7 @@
         <v>1.03</v>
       </c>
       <c r="D142" s="0" t="n">
-        <v>251.334666</v>
+        <v>1889.84955</v>
       </c>
       <c r="E142" s="0" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>0.08</v>
       </c>
       <c r="J142" s="0" t="n">
-        <v>2</v>
+        <v>0.902324</v>
       </c>
       <c r="K142" s="0" t="n">
         <v>1</v>
@@ -8913,7 +8913,7 @@
         <v>1.03</v>
       </c>
       <c r="D143" s="0" t="n">
-        <v>251.334666</v>
+        <v>1889.84955</v>
       </c>
       <c r="E143" s="0" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>0.08</v>
       </c>
       <c r="J143" s="0" t="n">
-        <v>2</v>
+        <v>0.902324</v>
       </c>
       <c r="K143" s="0" t="n">
         <v>1</v>
@@ -8967,7 +8967,7 @@
         <v>1.0075</v>
       </c>
       <c r="D144" s="0" t="n">
-        <v>33.735969</v>
+        <v>437.159392</v>
       </c>
       <c r="E144" s="0" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>0.08</v>
       </c>
       <c r="J144" s="0" t="n">
-        <v>2</v>
+        <v>0.795717</v>
       </c>
       <c r="K144" s="0" t="n">
         <v>1</v>
@@ -9021,7 +9021,7 @@
         <v>1.04</v>
       </c>
       <c r="D145" s="0" t="n">
-        <v>12</v>
+        <v>116.812747</v>
       </c>
       <c r="E145" s="0" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>0</v>
       </c>
       <c r="J145" s="0" t="n">
-        <v>1</v>
+        <v>0.273623</v>
       </c>
       <c r="K145" s="0" t="n">
         <v>1</v>
@@ -9129,7 +9129,7 @@
         <v>1.06</v>
       </c>
       <c r="D147" s="0" t="n">
-        <v>16</v>
+        <v>155.335336</v>
       </c>
       <c r="E147" s="0" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>0</v>
       </c>
       <c r="J147" s="0" t="n">
-        <v>1</v>
+        <v>0.291206</v>
       </c>
       <c r="K147" s="0" t="n">
         <v>1</v>
@@ -9183,7 +9183,7 @@
         <v>1.1</v>
       </c>
       <c r="D148" s="0" t="n">
-        <v>18</v>
+        <v>174.600778</v>
       </c>
       <c r="E148" s="0" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>0</v>
       </c>
       <c r="J148" s="0" t="n">
-        <v>1</v>
+        <v>0.278464</v>
       </c>
       <c r="K148" s="0" t="n">
         <v>1</v>
@@ -9237,7 +9237,7 @@
         <v>1.12</v>
       </c>
       <c r="D149" s="0" t="n">
-        <v>32</v>
+        <v>243.503532</v>
       </c>
       <c r="E149" s="0" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>0</v>
       </c>
       <c r="J149" s="0" t="n">
-        <v>1</v>
+        <v>0.291707</v>
       </c>
       <c r="K149" s="0" t="n">
         <v>1</v>
@@ -9291,7 +9291,7 @@
         <v>1.05</v>
       </c>
       <c r="D150" s="0" t="n">
-        <v>26</v>
+        <v>213.254156</v>
       </c>
       <c r="E150" s="0" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>0</v>
       </c>
       <c r="J150" s="0" t="n">
-        <v>1</v>
+        <v>0.295922</v>
       </c>
       <c r="K150" s="0" t="n">
         <v>1</v>
@@ -9345,7 +9345,7 @@
         <v>1.1</v>
       </c>
       <c r="D151" s="0" t="n">
-        <v>31</v>
+        <v>252.748048</v>
       </c>
       <c r="E151" s="0" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>0</v>
       </c>
       <c r="J151" s="0" t="n">
-        <v>1</v>
+        <v>0.306392</v>
       </c>
       <c r="K151" s="0" t="n">
         <v>1</v>
@@ -9399,7 +9399,7 @@
         <v>1.14</v>
       </c>
       <c r="D152" s="0" t="n">
-        <v>35</v>
+        <v>286.206583</v>
       </c>
       <c r="E152" s="0" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>0</v>
       </c>
       <c r="J152" s="0" t="n">
-        <v>1</v>
+        <v>0.30235</v>
       </c>
       <c r="K152" s="0" t="n">
         <v>1</v>
@@ -9453,7 +9453,7 @@
         <v>1.13</v>
       </c>
       <c r="D153" s="0" t="n">
-        <v>56</v>
+        <v>357.952618</v>
       </c>
       <c r="E153" s="0" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>0</v>
       </c>
       <c r="J153" s="0" t="n">
-        <v>1</v>
+        <v>0.293343</v>
       </c>
       <c r="K153" s="0" t="n">
         <v>1</v>
@@ -9507,7 +9507,7 @@
         <v>1.08</v>
       </c>
       <c r="D154" s="0" t="n">
-        <v>90</v>
+        <v>541.11013</v>
       </c>
       <c r="E154" s="0" t="inlineStr">
         <is>
@@ -9529,7 +9529,7 @@
         <v>0</v>
       </c>
       <c r="J154" s="0" t="n">
-        <v>1</v>
+        <v>0.284338</v>
       </c>
       <c r="K154" s="0" t="n">
         <v>1</v>
@@ -9561,7 +9561,7 @@
         <v>1.08</v>
       </c>
       <c r="D155" s="0" t="n">
-        <v>90</v>
+        <v>541.11013</v>
       </c>
       <c r="E155" s="0" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>0</v>
       </c>
       <c r="J155" s="0" t="n">
-        <v>1</v>
+        <v>0.284338</v>
       </c>
       <c r="K155" s="0" t="n">
         <v>1</v>
@@ -9615,7 +9615,7 @@
         <v>1.08</v>
       </c>
       <c r="D156" s="0" t="n">
-        <v>90</v>
+        <v>541.11013</v>
       </c>
       <c r="E156" s="0" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>0</v>
       </c>
       <c r="J156" s="0" t="n">
-        <v>1</v>
+        <v>0.284338</v>
       </c>
       <c r="K156" s="0" t="n">
         <v>1</v>
@@ -9669,7 +9669,7 @@
         <v>1.13465</v>
       </c>
       <c r="D157" s="0" t="n">
-        <v>156.606868</v>
+        <v>1643.188181</v>
       </c>
       <c r="E157" s="0" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>0</v>
       </c>
       <c r="J157" s="0" t="n">
-        <v>2</v>
+        <v>0.568985</v>
       </c>
       <c r="K157" s="0" t="n">
         <v>1</v>
@@ -9723,7 +9723,7 @@
         <v>1.13465</v>
       </c>
       <c r="D158" s="0" t="n">
-        <v>156.606868</v>
+        <v>1643.188181</v>
       </c>
       <c r="E158" s="0" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>0</v>
       </c>
       <c r="J158" s="0" t="n">
-        <v>2</v>
+        <v>0.568985</v>
       </c>
       <c r="K158" s="0" t="n">
         <v>1</v>
@@ -9777,7 +9777,7 @@
         <v>1.6504</v>
       </c>
       <c r="D159" s="0" t="n">
-        <v>133.115837</v>
+        <v>1396.709925</v>
       </c>
       <c r="E159" s="0" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>0</v>
       </c>
       <c r="J159" s="0" t="n">
-        <v>1</v>
+        <v>0.483638</v>
       </c>
       <c r="K159" s="0" t="n">
         <v>1</v>
@@ -9831,7 +9831,7 @@
         <v>1.0315</v>
       </c>
       <c r="D160" s="0" t="n">
-        <v>244.933141</v>
+        <v>2569.946362</v>
       </c>
       <c r="E160" s="0" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>0.08</v>
       </c>
       <c r="J160" s="0" t="n">
-        <v>2</v>
+        <v>0.889894</v>
       </c>
       <c r="K160" s="0" t="n">
         <v>1</v>
@@ -9885,7 +9885,7 @@
         <v>1.083075</v>
       </c>
       <c r="D161" s="0" t="n">
-        <v>101.794464</v>
+        <v>1068.072345</v>
       </c>
       <c r="E161" s="0" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="J161" s="0" t="n">
-        <v>1</v>
+        <v>0.369841</v>
       </c>
       <c r="K161" s="0" t="n">
         <v>1</v>
@@ -9939,7 +9939,7 @@
         <v>0.8252000000000002</v>
       </c>
       <c r="D162" s="0" t="n">
-        <v>292.854842</v>
+        <v>3072.761643</v>
       </c>
       <c r="E162" s="0" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>0.15</v>
       </c>
       <c r="J162" s="0" t="n">
-        <v>3</v>
+        <v>1.064004</v>
       </c>
       <c r="K162" s="0" t="n">
         <v>2</v>
@@ -9993,7 +9993,7 @@
         <v>1.0315</v>
       </c>
       <c r="D163" s="0" t="n">
-        <v>244.933141</v>
+        <v>2569.946362</v>
       </c>
       <c r="E163" s="0" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>0.08</v>
       </c>
       <c r="J163" s="0" t="n">
-        <v>2</v>
+        <v>0.889894</v>
       </c>
       <c r="K163" s="0" t="n">
         <v>1</v>
@@ -10047,7 +10047,7 @@
         <v>1.0315</v>
       </c>
       <c r="D164" s="0" t="n">
-        <v>244.933141</v>
+        <v>2569.946362</v>
       </c>
       <c r="E164" s="0" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>0.08</v>
       </c>
       <c r="J164" s="0" t="n">
-        <v>2</v>
+        <v>0.889894</v>
       </c>
       <c r="K164" s="0" t="n">
         <v>1</v>
@@ -10101,7 +10101,7 @@
         <v>1.12</v>
       </c>
       <c r="D165" s="0" t="n">
-        <v>94</v>
+        <v>541.11013</v>
       </c>
       <c r="E165" s="0" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>0</v>
       </c>
       <c r="J165" s="0" t="n">
-        <v>1</v>
+        <v>0.3015</v>
       </c>
       <c r="K165" s="0" t="n">
         <v>1</v>
@@ -10155,7 +10155,7 @@
         <v>1.12</v>
       </c>
       <c r="D166" s="0" t="n">
-        <v>94</v>
+        <v>541.11013</v>
       </c>
       <c r="E166" s="0" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>0</v>
       </c>
       <c r="J166" s="0" t="n">
-        <v>1</v>
+        <v>0.3015</v>
       </c>
       <c r="K166" s="0" t="n">
         <v>1</v>
@@ -10209,7 +10209,7 @@
         <v>1.12</v>
       </c>
       <c r="D167" s="0" t="n">
-        <v>94</v>
+        <v>541.11013</v>
       </c>
       <c r="E167" s="0" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         <v>0</v>
       </c>
       <c r="J167" s="0" t="n">
-        <v>1</v>
+        <v>0.3015</v>
       </c>
       <c r="K167" s="0" t="n">
         <v>1</v>
@@ -10263,7 +10263,7 @@
         <v>1.1363</v>
       </c>
       <c r="D168" s="0" t="n">
-        <v>154.41697</v>
+        <v>1621.032822</v>
       </c>
       <c r="E168" s="0" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="J168" s="0" t="n">
-        <v>2</v>
+        <v>0.569578</v>
       </c>
       <c r="K168" s="0" t="n">
         <v>1</v>
@@ -10317,7 +10317,7 @@
         <v>1.1363</v>
       </c>
       <c r="D169" s="0" t="n">
-        <v>154.41697</v>
+        <v>1621.032822</v>
       </c>
       <c r="E169" s="0" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>0</v>
       </c>
       <c r="J169" s="0" t="n">
-        <v>2</v>
+        <v>0.569578</v>
       </c>
       <c r="K169" s="0" t="n">
         <v>1</v>
@@ -10371,7 +10371,7 @@
         <v>1.6528</v>
       </c>
       <c r="D170" s="0" t="n">
-        <v>131.254424</v>
+        <v>1377.877926</v>
       </c>
       <c r="E170" s="0" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>0</v>
       </c>
       <c r="J170" s="0" t="n">
-        <v>1</v>
+        <v>0.484141</v>
       </c>
       <c r="K170" s="0" t="n">
         <v>1</v>
@@ -10425,7 +10425,7 @@
         <v>1.033</v>
       </c>
       <c r="D171" s="0" t="n">
-        <v>241.508141</v>
+        <v>2535.29544</v>
       </c>
       <c r="E171" s="0" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>0.08</v>
       </c>
       <c r="J171" s="0" t="n">
-        <v>2</v>
+        <v>0.890819</v>
       </c>
       <c r="K171" s="0" t="n">
         <v>1</v>
@@ -10479,7 +10479,7 @@
         <v>1.08465</v>
       </c>
       <c r="D172" s="0" t="n">
-        <v>100.37103</v>
+        <v>1053.671307</v>
       </c>
       <c r="E172" s="0" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>0</v>
       </c>
       <c r="J172" s="0" t="n">
-        <v>1</v>
+        <v>0.370225</v>
       </c>
       <c r="K172" s="0" t="n">
         <v>1</v>
@@ -10533,7 +10533,7 @@
         <v>0.8264000000000001</v>
       </c>
       <c r="D173" s="0" t="n">
-        <v>288.759734</v>
+        <v>3031.331437</v>
       </c>
       <c r="E173" s="0" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>0.15</v>
       </c>
       <c r="J173" s="0" t="n">
-        <v>3</v>
+        <v>1.065109</v>
       </c>
       <c r="K173" s="0" t="n">
         <v>2</v>
@@ -10587,7 +10587,7 @@
         <v>1.033</v>
       </c>
       <c r="D174" s="0" t="n">
-        <v>241.508141</v>
+        <v>2535.29544</v>
       </c>
       <c r="E174" s="0" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>0.08</v>
       </c>
       <c r="J174" s="0" t="n">
-        <v>2</v>
+        <v>0.890819</v>
       </c>
       <c r="K174" s="0" t="n">
         <v>1</v>
@@ -10641,7 +10641,7 @@
         <v>1.033</v>
       </c>
       <c r="D175" s="0" t="n">
-        <v>241.508141</v>
+        <v>2535.29544</v>
       </c>
       <c r="E175" s="0" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>0.08</v>
       </c>
       <c r="J175" s="0" t="n">
-        <v>2</v>
+        <v>0.890819</v>
       </c>
       <c r="K175" s="0" t="n">
         <v>1</v>
@@ -10695,7 +10695,7 @@
         <v>1.18</v>
       </c>
       <c r="D176" s="0" t="n">
-        <v>96</v>
+        <v>541.11013</v>
       </c>
       <c r="E176" s="0" t="inlineStr">
         <is>
@@ -10717,7 +10717,7 @@
         <v>0</v>
       </c>
       <c r="J176" s="0" t="n">
-        <v>1</v>
+        <v>0.312182</v>
       </c>
       <c r="K176" s="0" t="n">
         <v>1</v>
@@ -10749,7 +10749,7 @@
         <v>1.18</v>
       </c>
       <c r="D177" s="0" t="n">
-        <v>96</v>
+        <v>541.11013</v>
       </c>
       <c r="E177" s="0" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>0</v>
       </c>
       <c r="J177" s="0" t="n">
-        <v>1</v>
+        <v>0.312182</v>
       </c>
       <c r="K177" s="0" t="n">
         <v>1</v>
@@ -10803,7 +10803,7 @@
         <v>1.18</v>
       </c>
       <c r="D178" s="0" t="n">
-        <v>96</v>
+        <v>541.11013</v>
       </c>
       <c r="E178" s="0" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>0</v>
       </c>
       <c r="J178" s="0" t="n">
-        <v>1</v>
+        <v>0.312182</v>
       </c>
       <c r="K178" s="0" t="n">
         <v>1</v>
@@ -10857,7 +10857,7 @@
         <v>1.13795</v>
       </c>
       <c r="D179" s="0" t="n">
-        <v>151.181683</v>
+        <v>1596.313053</v>
       </c>
       <c r="E179" s="0" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>0</v>
       </c>
       <c r="J179" s="0" t="n">
-        <v>2</v>
+        <v>0.565371</v>
       </c>
       <c r="K179" s="0" t="n">
         <v>1</v>
@@ -10911,7 +10911,7 @@
         <v>1.13795</v>
       </c>
       <c r="D180" s="0" t="n">
-        <v>151.181683</v>
+        <v>1596.313053</v>
       </c>
       <c r="E180" s="0" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>0</v>
       </c>
       <c r="J180" s="0" t="n">
-        <v>2</v>
+        <v>0.565371</v>
       </c>
       <c r="K180" s="0" t="n">
         <v>1</v>
@@ -10965,7 +10965,7 @@
         <v>1.6552</v>
       </c>
       <c r="D181" s="0" t="n">
-        <v>128.50443</v>
+        <v>1356.866053</v>
       </c>
       <c r="E181" s="0" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>0</v>
       </c>
       <c r="J181" s="0" t="n">
-        <v>1</v>
+        <v>0.480565</v>
       </c>
       <c r="K181" s="0" t="n">
         <v>1</v>
@@ -11019,7 +11019,7 @@
         <v>1.0345</v>
       </c>
       <c r="D182" s="0" t="n">
-        <v>236.448152</v>
+        <v>2496.63359</v>
       </c>
       <c r="E182" s="0" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>0.08</v>
       </c>
       <c r="J182" s="0" t="n">
-        <v>2</v>
+        <v>0.8842410000000001</v>
       </c>
       <c r="K182" s="0" t="n">
         <v>1</v>
@@ -11073,7 +11073,7 @@
         <v>1.086225</v>
       </c>
       <c r="D183" s="0" t="n">
-        <v>98.268094</v>
+        <v>1037.603526</v>
       </c>
       <c r="E183" s="0" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>0</v>
       </c>
       <c r="J183" s="0" t="n">
-        <v>1</v>
+        <v>0.367492</v>
       </c>
       <c r="K183" s="0" t="n">
         <v>1</v>
@@ -11127,7 +11127,7 @@
         <v>0.8276</v>
       </c>
       <c r="D184" s="0" t="n">
-        <v>282.709747</v>
+        <v>2985.105291</v>
       </c>
       <c r="E184" s="0" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>0.15</v>
       </c>
       <c r="J184" s="0" t="n">
-        <v>3</v>
+        <v>1.057244</v>
       </c>
       <c r="K184" s="0" t="n">
         <v>2</v>
@@ -11181,7 +11181,7 @@
         <v>1.0345</v>
       </c>
       <c r="D185" s="0" t="n">
-        <v>236.448152</v>
+        <v>2496.63359</v>
       </c>
       <c r="E185" s="0" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>0.08</v>
       </c>
       <c r="J185" s="0" t="n">
-        <v>2</v>
+        <v>0.8842410000000001</v>
       </c>
       <c r="K185" s="0" t="n">
         <v>1</v>
@@ -11235,7 +11235,7 @@
         <v>1.0345</v>
       </c>
       <c r="D186" s="0" t="n">
-        <v>236.448152</v>
+        <v>2496.63359</v>
       </c>
       <c r="E186" s="0" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>0.08</v>
       </c>
       <c r="J186" s="0" t="n">
-        <v>2</v>
+        <v>0.8842410000000001</v>
       </c>
       <c r="K186" s="0" t="n">
         <v>1</v>
@@ -11289,7 +11289,7 @@
         <v>1.1</v>
       </c>
       <c r="D187" s="0" t="n">
-        <v>92</v>
+        <v>541.11013</v>
       </c>
       <c r="E187" s="0" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="J187" s="0" t="n">
-        <v>1</v>
+        <v>0.296509</v>
       </c>
       <c r="K187" s="0" t="n">
         <v>1</v>
@@ -11343,7 +11343,7 @@
         <v>1.1</v>
       </c>
       <c r="D188" s="0" t="n">
-        <v>92</v>
+        <v>541.11013</v>
       </c>
       <c r="E188" s="0" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>0</v>
       </c>
       <c r="J188" s="0" t="n">
-        <v>1</v>
+        <v>0.296509</v>
       </c>
       <c r="K188" s="0" t="n">
         <v>1</v>
@@ -11397,7 +11397,7 @@
         <v>1.1</v>
       </c>
       <c r="D189" s="0" t="n">
-        <v>92</v>
+        <v>541.11013</v>
       </c>
       <c r="E189" s="0" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>0</v>
       </c>
       <c r="J189" s="0" t="n">
-        <v>1</v>
+        <v>0.296509</v>
       </c>
       <c r="K189" s="0" t="n">
         <v>1</v>
@@ -11451,7 +11451,7 @@
         <v>1.1396</v>
       </c>
       <c r="D190" s="0" t="n">
-        <v>155.455504</v>
+        <v>1684.680928</v>
       </c>
       <c r="E190" s="0" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>0</v>
       </c>
       <c r="J190" s="0" t="n">
-        <v>2</v>
+        <v>0.576174</v>
       </c>
       <c r="K190" s="0" t="n">
         <v>1</v>
@@ -11505,7 +11505,7 @@
         <v>1.1396</v>
       </c>
       <c r="D191" s="0" t="n">
-        <v>155.455504</v>
+        <v>1684.680928</v>
       </c>
       <c r="E191" s="0" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>0</v>
       </c>
       <c r="J191" s="0" t="n">
-        <v>2</v>
+        <v>0.576174</v>
       </c>
       <c r="K191" s="0" t="n">
         <v>1</v>
@@ -11559,7 +11559,7 @@
         <v>1.6576</v>
       </c>
       <c r="D192" s="0" t="n">
-        <v>132.137178</v>
+        <v>1431.978944</v>
       </c>
       <c r="E192" s="0" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         <v>0</v>
       </c>
       <c r="J192" s="0" t="n">
-        <v>1</v>
+        <v>0.489748</v>
       </c>
       <c r="K192" s="0" t="n">
         <v>1</v>
@@ -11613,7 +11613,7 @@
         <v>1.036</v>
       </c>
       <c r="D193" s="0" t="n">
-        <v>243.132408</v>
+        <v>2634.841089</v>
       </c>
       <c r="E193" s="0" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>0.08</v>
       </c>
       <c r="J193" s="0" t="n">
-        <v>2</v>
+        <v>0.901137</v>
       </c>
       <c r="K193" s="0" t="n">
         <v>1</v>
@@ -11667,7 +11667,7 @@
         <v>1.0878</v>
       </c>
       <c r="D194" s="0" t="n">
-        <v>101.046078</v>
+        <v>1095.042674</v>
       </c>
       <c r="E194" s="0" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>0</v>
       </c>
       <c r="J194" s="0" t="n">
-        <v>1</v>
+        <v>0.374514</v>
       </c>
       <c r="K194" s="0" t="n">
         <v>1</v>
@@ -11721,7 +11721,7 @@
         <v>0.8288000000000001</v>
       </c>
       <c r="D195" s="0" t="n">
-        <v>290.701793</v>
+        <v>3150.353434</v>
       </c>
       <c r="E195" s="0" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         <v>0.15</v>
       </c>
       <c r="J195" s="0" t="n">
-        <v>3</v>
+        <v>1.077445</v>
       </c>
       <c r="K195" s="0" t="n">
         <v>2</v>
@@ -11775,7 +11775,7 @@
         <v>1.036</v>
       </c>
       <c r="D196" s="0" t="n">
-        <v>243.132408</v>
+        <v>2634.841089</v>
       </c>
       <c r="E196" s="0" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>0.08</v>
       </c>
       <c r="J196" s="0" t="n">
-        <v>2</v>
+        <v>0.901137</v>
       </c>
       <c r="K196" s="0" t="n">
         <v>1</v>
@@ -11829,7 +11829,7 @@
         <v>1.036</v>
       </c>
       <c r="D197" s="0" t="n">
-        <v>243.132408</v>
+        <v>2634.841089</v>
       </c>
       <c r="E197" s="0" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>0.08</v>
       </c>
       <c r="J197" s="0" t="n">
-        <v>2</v>
+        <v>0.901137</v>
       </c>
       <c r="K197" s="0" t="n">
         <v>1</v>
@@ -11883,7 +11883,7 @@
         <v>1.12</v>
       </c>
       <c r="D198" s="0" t="n">
-        <v>168</v>
+        <v>541.11013</v>
       </c>
       <c r="E198" s="0" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>0</v>
       </c>
       <c r="J198" s="0" t="n">
-        <v>1</v>
+        <v>0.308244</v>
       </c>
       <c r="K198" s="0" t="n">
         <v>1</v>
@@ -11937,7 +11937,7 @@
         <v>1.12</v>
       </c>
       <c r="D199" s="0" t="n">
-        <v>168</v>
+        <v>541.11013</v>
       </c>
       <c r="E199" s="0" t="inlineStr">
         <is>
@@ -11959,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="J199" s="0" t="n">
-        <v>1</v>
+        <v>0.308244</v>
       </c>
       <c r="K199" s="0" t="n">
         <v>1</v>
@@ -11991,7 +11991,7 @@
         <v>1.12</v>
       </c>
       <c r="D200" s="0" t="n">
-        <v>168</v>
+        <v>541.11013</v>
       </c>
       <c r="E200" s="0" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>0</v>
       </c>
       <c r="J200" s="0" t="n">
-        <v>1</v>
+        <v>0.308244</v>
       </c>
       <c r="K200" s="0" t="n">
         <v>1</v>
@@ -12045,7 +12045,7 @@
         <v>1.14125</v>
       </c>
       <c r="D201" s="0" t="n">
-        <v>295.216958</v>
+        <v>2066.690079</v>
       </c>
       <c r="E201" s="0" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>0</v>
       </c>
       <c r="J201" s="0" t="n">
-        <v>2</v>
+        <v>0.622909</v>
       </c>
       <c r="K201" s="0" t="n">
         <v>1</v>
@@ -12099,7 +12099,7 @@
         <v>1.14125</v>
       </c>
       <c r="D202" s="0" t="n">
-        <v>295.216958</v>
+        <v>2066.690079</v>
       </c>
       <c r="E202" s="0" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>0</v>
       </c>
       <c r="J202" s="0" t="n">
-        <v>2</v>
+        <v>0.622909</v>
       </c>
       <c r="K202" s="0" t="n">
         <v>1</v>
@@ -12153,7 +12153,7 @@
         <v>1.66</v>
       </c>
       <c r="D203" s="0" t="n">
-        <v>250.934414</v>
+        <v>1756.686746</v>
       </c>
       <c r="E203" s="0" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>0</v>
       </c>
       <c r="J203" s="0" t="n">
-        <v>1</v>
+        <v>0.529473</v>
       </c>
       <c r="K203" s="0" t="n">
         <v>1</v>
@@ -12207,7 +12207,7 @@
         <v>1.0375</v>
       </c>
       <c r="D204" s="0" t="n">
-        <v>461.719322</v>
+        <v>3232.303514</v>
       </c>
       <c r="E204" s="0" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>0.08</v>
       </c>
       <c r="J204" s="0" t="n">
-        <v>2</v>
+        <v>0.974229</v>
       </c>
       <c r="K204" s="0" t="n">
         <v>1</v>
@@ -12261,7 +12261,7 @@
         <v>1.089375</v>
       </c>
       <c r="D205" s="0" t="n">
-        <v>191.891023</v>
+        <v>1343.348647</v>
       </c>
       <c r="E205" s="0" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>0</v>
       </c>
       <c r="J205" s="0" t="n">
-        <v>1</v>
+        <v>0.404891</v>
       </c>
       <c r="K205" s="0" t="n">
         <v>1</v>
@@ -12315,7 +12315,7 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="D206" s="0" t="n">
-        <v>552.055712</v>
+        <v>3864.710759</v>
       </c>
       <c r="E206" s="0" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>0.15</v>
       </c>
       <c r="J206" s="0" t="n">
-        <v>3</v>
+        <v>1.16484</v>
       </c>
       <c r="K206" s="0" t="n">
         <v>2</v>
@@ -12369,7 +12369,7 @@
         <v>1.0375</v>
       </c>
       <c r="D207" s="0" t="n">
-        <v>461.719322</v>
+        <v>3232.303514</v>
       </c>
       <c r="E207" s="0" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>0.08</v>
       </c>
       <c r="J207" s="0" t="n">
-        <v>2</v>
+        <v>0.974229</v>
       </c>
       <c r="K207" s="0" t="n">
         <v>1</v>
@@ -12423,7 +12423,7 @@
         <v>0.7781250000000001</v>
       </c>
       <c r="D208" s="0" t="n">
-        <v>1105.292291</v>
+        <v>7737.687837</v>
       </c>
       <c r="E208" s="0" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>0.22</v>
       </c>
       <c r="J208" s="0" t="n">
-        <v>6</v>
+        <v>2.33217</v>
       </c>
       <c r="K208" s="0" t="n">
         <v>2</v>
@@ -12477,7 +12477,7 @@
         <v>1.0375</v>
       </c>
       <c r="D209" s="0" t="n">
-        <v>461.719322</v>
+        <v>3232.303514</v>
       </c>
       <c r="E209" s="0" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>0.08</v>
       </c>
       <c r="J209" s="0" t="n">
-        <v>2</v>
+        <v>0.974229</v>
       </c>
       <c r="K209" s="0" t="n">
         <v>1</v>
@@ -12531,7 +12531,7 @@
         <v>1.12</v>
       </c>
       <c r="D210" s="0" t="n">
-        <v>32</v>
+        <v>243.503532</v>
       </c>
       <c r="E210" s="0" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>0</v>
       </c>
       <c r="J210" s="0" t="n">
-        <v>1</v>
+        <v>0.291707</v>
       </c>
       <c r="K210" s="0" t="n">
         <v>1</v>
@@ -12639,7 +12639,7 @@
         <v>1.12</v>
       </c>
       <c r="D212" s="0" t="n">
-        <v>16</v>
+        <v>154.175902</v>
       </c>
       <c r="E212" s="0" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>0</v>
       </c>
       <c r="J212" s="0" t="n">
-        <v>1</v>
+        <v>0.343035</v>
       </c>
       <c r="K212" s="0" t="n">
         <v>1</v>
@@ -12693,7 +12693,7 @@
         <v>1.06</v>
       </c>
       <c r="D213" s="0" t="n">
-        <v>16</v>
+        <v>155.335336</v>
       </c>
       <c r="E213" s="0" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>0</v>
       </c>
       <c r="J213" s="0" t="n">
-        <v>1</v>
+        <v>0.291206</v>
       </c>
       <c r="K213" s="0" t="n">
         <v>1</v>
@@ -12747,7 +12747,7 @@
         <v>1.1</v>
       </c>
       <c r="D214" s="0" t="n">
-        <v>18</v>
+        <v>174.600778</v>
       </c>
       <c r="E214" s="0" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
         <v>0</v>
       </c>
       <c r="J214" s="0" t="n">
-        <v>1</v>
+        <v>0.278464</v>
       </c>
       <c r="K214" s="0" t="n">
         <v>1</v>
@@ -13341,7 +13341,7 @@
         <v>1.08</v>
       </c>
       <c r="D225" s="0" t="n">
-        <v>13</v>
+        <v>112.304894</v>
       </c>
       <c r="E225" s="0" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>0</v>
       </c>
       <c r="J225" s="0" t="n">
-        <v>1</v>
+        <v>0.266631</v>
       </c>
       <c r="K225" s="0" t="n">
         <v>1</v>
@@ -13395,7 +13395,7 @@
         <v>1.08</v>
       </c>
       <c r="D226" s="0" t="n">
-        <v>13</v>
+        <v>112.304894</v>
       </c>
       <c r="E226" s="0" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="J226" s="0" t="n">
-        <v>1</v>
+        <v>0.266631</v>
       </c>
       <c r="K226" s="0" t="n">
         <v>1</v>
@@ -13611,7 +13611,7 @@
         <v>1.04</v>
       </c>
       <c r="D230" s="0" t="n">
-        <v>12</v>
+        <v>116.812747</v>
       </c>
       <c r="E230" s="0" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>0</v>
       </c>
       <c r="J230" s="0" t="n">
-        <v>1</v>
+        <v>0.273623</v>
       </c>
       <c r="K230" s="0" t="n">
         <v>1</v>
@@ -13665,7 +13665,7 @@
         <v>1.04</v>
       </c>
       <c r="D231" s="0" t="n">
-        <v>12</v>
+        <v>116.812747</v>
       </c>
       <c r="E231" s="0" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>0</v>
       </c>
       <c r="J231" s="0" t="n">
-        <v>1</v>
+        <v>0.273623</v>
       </c>
       <c r="K231" s="0" t="n">
         <v>1</v>
@@ -13719,7 +13719,7 @@
         <v>1.12</v>
       </c>
       <c r="D232" s="0" t="n">
-        <v>16</v>
+        <v>154.175902</v>
       </c>
       <c r="E232" s="0" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="J232" s="0" t="n">
-        <v>1</v>
+        <v>0.343035</v>
       </c>
       <c r="K232" s="0" t="n">
         <v>1</v>
@@ -13773,7 +13773,7 @@
         <v>1.12</v>
       </c>
       <c r="D233" s="0" t="n">
-        <v>16</v>
+        <v>154.175902</v>
       </c>
       <c r="E233" s="0" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>0</v>
       </c>
       <c r="J233" s="0" t="n">
-        <v>1</v>
+        <v>0.343035</v>
       </c>
       <c r="K233" s="0" t="n">
         <v>1</v>
@@ -13827,7 +13827,7 @@
         <v>1.06</v>
       </c>
       <c r="D234" s="0" t="n">
-        <v>16</v>
+        <v>155.335336</v>
       </c>
       <c r="E234" s="0" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>0</v>
       </c>
       <c r="J234" s="0" t="n">
-        <v>1</v>
+        <v>0.291206</v>
       </c>
       <c r="K234" s="0" t="n">
         <v>1</v>
@@ -13881,7 +13881,7 @@
         <v>1.06</v>
       </c>
       <c r="D235" s="0" t="n">
-        <v>16</v>
+        <v>155.335336</v>
       </c>
       <c r="E235" s="0" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>0</v>
       </c>
       <c r="J235" s="0" t="n">
-        <v>1</v>
+        <v>0.291206</v>
       </c>
       <c r="K235" s="0" t="n">
         <v>1</v>
@@ -13935,7 +13935,7 @@
         <v>1.1</v>
       </c>
       <c r="D236" s="0" t="n">
-        <v>18</v>
+        <v>174.600778</v>
       </c>
       <c r="E236" s="0" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>0</v>
       </c>
       <c r="J236" s="0" t="n">
-        <v>1</v>
+        <v>0.278464</v>
       </c>
       <c r="K236" s="0" t="n">
         <v>1</v>
@@ -13989,7 +13989,7 @@
         <v>1.1</v>
       </c>
       <c r="D237" s="0" t="n">
-        <v>18</v>
+        <v>174.600778</v>
       </c>
       <c r="E237" s="0" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>0</v>
       </c>
       <c r="J237" s="0" t="n">
-        <v>1</v>
+        <v>0.278464</v>
       </c>
       <c r="K237" s="0" t="n">
         <v>1</v>
@@ -14043,7 +14043,7 @@
         <v>1.12</v>
       </c>
       <c r="D238" s="0" t="n">
-        <v>32</v>
+        <v>243.503532</v>
       </c>
       <c r="E238" s="0" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>0</v>
       </c>
       <c r="J238" s="0" t="n">
-        <v>1</v>
+        <v>0.291707</v>
       </c>
       <c r="K238" s="0" t="n">
         <v>1</v>
@@ -14097,7 +14097,7 @@
         <v>1.12</v>
       </c>
       <c r="D239" s="0" t="n">
-        <v>32</v>
+        <v>243.503532</v>
       </c>
       <c r="E239" s="0" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>0</v>
       </c>
       <c r="J239" s="0" t="n">
-        <v>1</v>
+        <v>0.291707</v>
       </c>
       <c r="K239" s="0" t="n">
         <v>1</v>
@@ -14151,7 +14151,7 @@
         <v>1.08</v>
       </c>
       <c r="D240" s="0" t="n">
-        <v>27</v>
+        <v>220.75424</v>
       </c>
       <c r="E240" s="0" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>0</v>
       </c>
       <c r="J240" s="0" t="n">
-        <v>1</v>
+        <v>0.294259</v>
       </c>
       <c r="K240" s="0" t="n">
         <v>1</v>
@@ -14205,7 +14205,7 @@
         <v>1.08</v>
       </c>
       <c r="D241" s="0" t="n">
-        <v>27</v>
+        <v>220.75424</v>
       </c>
       <c r="E241" s="0" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>0</v>
       </c>
       <c r="J241" s="0" t="n">
-        <v>1</v>
+        <v>0.294259</v>
       </c>
       <c r="K241" s="0" t="n">
         <v>1</v>
@@ -14259,7 +14259,7 @@
         <v>1.08</v>
       </c>
       <c r="D242" s="0" t="n">
-        <v>27</v>
+        <v>220.75424</v>
       </c>
       <c r="E242" s="0" t="inlineStr">
         <is>
@@ -14281,7 +14281,7 @@
         <v>0</v>
       </c>
       <c r="J242" s="0" t="n">
-        <v>1</v>
+        <v>0.294259</v>
       </c>
       <c r="K242" s="0" t="n">
         <v>1</v>
@@ -14313,7 +14313,7 @@
         <v>1.08</v>
       </c>
       <c r="D243" s="0" t="n">
-        <v>27</v>
+        <v>220.75424</v>
       </c>
       <c r="E243" s="0" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>0</v>
       </c>
       <c r="J243" s="0" t="n">
-        <v>1</v>
+        <v>0.294259</v>
       </c>
       <c r="K243" s="0" t="n">
         <v>1</v>
@@ -14367,7 +14367,7 @@
         <v>1.08</v>
       </c>
       <c r="D244" s="0" t="n">
-        <v>27</v>
+        <v>220.75424</v>
       </c>
       <c r="E244" s="0" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>0</v>
       </c>
       <c r="J244" s="0" t="n">
-        <v>1</v>
+        <v>0.294259</v>
       </c>
       <c r="K244" s="0" t="n">
         <v>1</v>
@@ -14421,7 +14421,7 @@
         <v>1.05</v>
       </c>
       <c r="D245" s="0" t="n">
-        <v>26</v>
+        <v>213.254156</v>
       </c>
       <c r="E245" s="0" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>0</v>
       </c>
       <c r="J245" s="0" t="n">
-        <v>1</v>
+        <v>0.295922</v>
       </c>
       <c r="K245" s="0" t="n">
         <v>1</v>
@@ -14475,7 +14475,7 @@
         <v>1.05</v>
       </c>
       <c r="D246" s="0" t="n">
-        <v>26</v>
+        <v>213.254156</v>
       </c>
       <c r="E246" s="0" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>0</v>
       </c>
       <c r="J246" s="0" t="n">
-        <v>1</v>
+        <v>0.295922</v>
       </c>
       <c r="K246" s="0" t="n">
         <v>1</v>
@@ -14529,7 +14529,7 @@
         <v>1.1</v>
       </c>
       <c r="D247" s="0" t="n">
-        <v>31</v>
+        <v>252.748048</v>
       </c>
       <c r="E247" s="0" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="J247" s="0" t="n">
-        <v>1</v>
+        <v>0.306392</v>
       </c>
       <c r="K247" s="0" t="n">
         <v>1</v>
@@ -14583,7 +14583,7 @@
         <v>1.1</v>
       </c>
       <c r="D248" s="0" t="n">
-        <v>31</v>
+        <v>252.748048</v>
       </c>
       <c r="E248" s="0" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>0</v>
       </c>
       <c r="J248" s="0" t="n">
-        <v>1</v>
+        <v>0.306392</v>
       </c>
       <c r="K248" s="0" t="n">
         <v>1</v>
@@ -14637,7 +14637,7 @@
         <v>1.14</v>
       </c>
       <c r="D249" s="0" t="n">
-        <v>35</v>
+        <v>286.206583</v>
       </c>
       <c r="E249" s="0" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>0</v>
       </c>
       <c r="J249" s="0" t="n">
-        <v>1</v>
+        <v>0.30235</v>
       </c>
       <c r="K249" s="0" t="n">
         <v>1</v>
@@ -14691,7 +14691,7 @@
         <v>1.14</v>
       </c>
       <c r="D250" s="0" t="n">
-        <v>35</v>
+        <v>286.206583</v>
       </c>
       <c r="E250" s="0" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>0</v>
       </c>
       <c r="J250" s="0" t="n">
-        <v>1</v>
+        <v>0.30235</v>
       </c>
       <c r="K250" s="0" t="n">
         <v>1</v>
@@ -14745,7 +14745,7 @@
         <v>1.13</v>
       </c>
       <c r="D251" s="0" t="n">
-        <v>56</v>
+        <v>357.952618</v>
       </c>
       <c r="E251" s="0" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>0</v>
       </c>
       <c r="J251" s="0" t="n">
-        <v>1</v>
+        <v>0.293343</v>
       </c>
       <c r="K251" s="0" t="n">
         <v>1</v>
@@ -14799,7 +14799,7 @@
         <v>1.13</v>
       </c>
       <c r="D252" s="0" t="n">
-        <v>56</v>
+        <v>357.952618</v>
       </c>
       <c r="E252" s="0" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>0</v>
       </c>
       <c r="J252" s="0" t="n">
-        <v>1</v>
+        <v>0.293343</v>
       </c>
       <c r="K252" s="0" t="n">
         <v>1</v>
@@ -14853,7 +14853,7 @@
         <v>1.08</v>
       </c>
       <c r="D253" s="0" t="n">
-        <v>50</v>
+        <v>357.729993</v>
       </c>
       <c r="E253" s="0" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>0</v>
       </c>
       <c r="J253" s="0" t="n">
-        <v>1</v>
+        <v>0.271613</v>
       </c>
       <c r="K253" s="0" t="n">
         <v>1</v>
@@ -14907,7 +14907,7 @@
         <v>1.08</v>
       </c>
       <c r="D254" s="0" t="n">
-        <v>50</v>
+        <v>357.729993</v>
       </c>
       <c r="E254" s="0" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>0</v>
       </c>
       <c r="J254" s="0" t="n">
-        <v>1</v>
+        <v>0.271613</v>
       </c>
       <c r="K254" s="0" t="n">
         <v>1</v>
@@ -14961,7 +14961,7 @@
         <v>1.08</v>
       </c>
       <c r="D255" s="0" t="n">
-        <v>50</v>
+        <v>357.729993</v>
       </c>
       <c r="E255" s="0" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="J255" s="0" t="n">
-        <v>1</v>
+        <v>0.271613</v>
       </c>
       <c r="K255" s="0" t="n">
         <v>1</v>
@@ -15015,7 +15015,7 @@
         <v>1.08</v>
       </c>
       <c r="D256" s="0" t="n">
-        <v>50</v>
+        <v>357.729993</v>
       </c>
       <c r="E256" s="0" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>0</v>
       </c>
       <c r="J256" s="0" t="n">
-        <v>1</v>
+        <v>0.271613</v>
       </c>
       <c r="K256" s="0" t="n">
         <v>1</v>
@@ -15069,7 +15069,7 @@
         <v>1.08</v>
       </c>
       <c r="D257" s="0" t="n">
-        <v>50</v>
+        <v>357.729993</v>
       </c>
       <c r="E257" s="0" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         <v>0</v>
       </c>
       <c r="J257" s="0" t="n">
-        <v>1</v>
+        <v>0.271613</v>
       </c>
       <c r="K257" s="0" t="n">
         <v>1</v>
@@ -15123,7 +15123,7 @@
         <v>1.12</v>
       </c>
       <c r="D258" s="0" t="n">
-        <v>53</v>
+        <v>381.811017</v>
       </c>
       <c r="E258" s="0" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>0</v>
       </c>
       <c r="J258" s="0" t="n">
-        <v>1</v>
+        <v>0.300436</v>
       </c>
       <c r="K258" s="0" t="n">
         <v>1</v>
@@ -15177,7 +15177,7 @@
         <v>1.12</v>
       </c>
       <c r="D259" s="0" t="n">
-        <v>53</v>
+        <v>381.811017</v>
       </c>
       <c r="E259" s="0" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>0</v>
       </c>
       <c r="J259" s="0" t="n">
-        <v>1</v>
+        <v>0.300436</v>
       </c>
       <c r="K259" s="0" t="n">
         <v>1</v>
@@ -15231,7 +15231,7 @@
         <v>1.12</v>
       </c>
       <c r="D260" s="0" t="n">
-        <v>57</v>
+        <v>406.265625</v>
       </c>
       <c r="E260" s="0" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>0</v>
       </c>
       <c r="J260" s="0" t="n">
-        <v>1</v>
+        <v>0.314056</v>
       </c>
       <c r="K260" s="0" t="n">
         <v>1</v>
@@ -15285,7 +15285,7 @@
         <v>1.12</v>
       </c>
       <c r="D261" s="0" t="n">
-        <v>57</v>
+        <v>406.265625</v>
       </c>
       <c r="E261" s="0" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         <v>0</v>
       </c>
       <c r="J261" s="0" t="n">
-        <v>1</v>
+        <v>0.314056</v>
       </c>
       <c r="K261" s="0" t="n">
         <v>1</v>
@@ -15339,7 +15339,7 @@
         <v>1.16</v>
       </c>
       <c r="D262" s="0" t="n">
-        <v>61</v>
+        <v>440.659336</v>
       </c>
       <c r="E262" s="0" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>0</v>
       </c>
       <c r="J262" s="0" t="n">
-        <v>1</v>
+        <v>0.305528</v>
       </c>
       <c r="K262" s="0" t="n">
         <v>1</v>
@@ -15393,7 +15393,7 @@
         <v>1.16</v>
       </c>
       <c r="D263" s="0" t="n">
-        <v>61</v>
+        <v>440.659336</v>
       </c>
       <c r="E263" s="0" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>0</v>
       </c>
       <c r="J263" s="0" t="n">
-        <v>1</v>
+        <v>0.305528</v>
       </c>
       <c r="K263" s="0" t="n">
         <v>1</v>
@@ -15447,7 +15447,7 @@
         <v>1.15</v>
       </c>
       <c r="D264" s="0" t="n">
-        <v>98</v>
+        <v>491.257986</v>
       </c>
       <c r="E264" s="0" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>0</v>
       </c>
       <c r="J264" s="0" t="n">
-        <v>1</v>
+        <v>0.305942</v>
       </c>
       <c r="K264" s="0" t="n">
         <v>1</v>
@@ -15501,7 +15501,7 @@
         <v>1.15</v>
       </c>
       <c r="D265" s="0" t="n">
-        <v>98</v>
+        <v>491.257986</v>
       </c>
       <c r="E265" s="0" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>0</v>
       </c>
       <c r="J265" s="0" t="n">
-        <v>1</v>
+        <v>0.305942</v>
       </c>
       <c r="K265" s="0" t="n">
         <v>1</v>
@@ -15555,7 +15555,7 @@
         <v>1.08</v>
       </c>
       <c r="D266" s="0" t="n">
-        <v>90</v>
+        <v>541.11013</v>
       </c>
       <c r="E266" s="0" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>0</v>
       </c>
       <c r="J266" s="0" t="n">
-        <v>1</v>
+        <v>0.284338</v>
       </c>
       <c r="K266" s="0" t="n">
         <v>1</v>
@@ -15609,7 +15609,7 @@
         <v>1.08</v>
       </c>
       <c r="D267" s="0" t="n">
-        <v>90</v>
+        <v>541.11013</v>
       </c>
       <c r="E267" s="0" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>0</v>
       </c>
       <c r="J267" s="0" t="n">
-        <v>1</v>
+        <v>0.284338</v>
       </c>
       <c r="K267" s="0" t="n">
         <v>1</v>
@@ -15663,7 +15663,7 @@
         <v>1.12</v>
       </c>
       <c r="D268" s="0" t="n">
-        <v>94</v>
+        <v>541.11013</v>
       </c>
       <c r="E268" s="0" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>0</v>
       </c>
       <c r="J268" s="0" t="n">
-        <v>1</v>
+        <v>0.3015</v>
       </c>
       <c r="K268" s="0" t="n">
         <v>1</v>
@@ -15717,7 +15717,7 @@
         <v>1.12</v>
       </c>
       <c r="D269" s="0" t="n">
-        <v>94</v>
+        <v>541.11013</v>
       </c>
       <c r="E269" s="0" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="J269" s="0" t="n">
-        <v>1</v>
+        <v>0.3015</v>
       </c>
       <c r="K269" s="0" t="n">
         <v>1</v>
@@ -15771,7 +15771,7 @@
         <v>1.18</v>
       </c>
       <c r="D270" s="0" t="n">
-        <v>96</v>
+        <v>541.11013</v>
       </c>
       <c r="E270" s="0" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>0</v>
       </c>
       <c r="J270" s="0" t="n">
-        <v>1</v>
+        <v>0.312182</v>
       </c>
       <c r="K270" s="0" t="n">
         <v>1</v>
@@ -15825,7 +15825,7 @@
         <v>1.18</v>
       </c>
       <c r="D271" s="0" t="n">
-        <v>96</v>
+        <v>541.11013</v>
       </c>
       <c r="E271" s="0" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>0</v>
       </c>
       <c r="J271" s="0" t="n">
-        <v>1</v>
+        <v>0.312182</v>
       </c>
       <c r="K271" s="0" t="n">
         <v>1</v>
@@ -15879,7 +15879,7 @@
         <v>1.1</v>
       </c>
       <c r="D272" s="0" t="n">
-        <v>92</v>
+        <v>541.11013</v>
       </c>
       <c r="E272" s="0" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="J272" s="0" t="n">
-        <v>1</v>
+        <v>0.296509</v>
       </c>
       <c r="K272" s="0" t="n">
         <v>1</v>
@@ -15933,7 +15933,7 @@
         <v>1.1</v>
       </c>
       <c r="D273" s="0" t="n">
-        <v>92</v>
+        <v>541.11013</v>
       </c>
       <c r="E273" s="0" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>0</v>
       </c>
       <c r="J273" s="0" t="n">
-        <v>1</v>
+        <v>0.296509</v>
       </c>
       <c r="K273" s="0" t="n">
         <v>1</v>
@@ -15987,7 +15987,7 @@
         <v>1.12</v>
       </c>
       <c r="D274" s="0" t="n">
-        <v>168</v>
+        <v>541.11013</v>
       </c>
       <c r="E274" s="0" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>0</v>
       </c>
       <c r="J274" s="0" t="n">
-        <v>1</v>
+        <v>0.308244</v>
       </c>
       <c r="K274" s="0" t="n">
         <v>1</v>
@@ -16041,7 +16041,7 @@
         <v>1.12</v>
       </c>
       <c r="D275" s="0" t="n">
-        <v>168</v>
+        <v>541.11013</v>
       </c>
       <c r="E275" s="0" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>0</v>
       </c>
       <c r="J275" s="0" t="n">
-        <v>1</v>
+        <v>0.308244</v>
       </c>
       <c r="K275" s="0" t="n">
         <v>1</v>
